--- a/docs/sf3000-tracker.xlsx
+++ b/docs/sf3000-tracker.xlsx
@@ -535,7 +535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:C60"/>
+  <dimension ref="B1:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -648,7 +648,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Copy logs/runs.jsonl to Windows (scp) BEFORE reverting. A revert deletes it.</t>
+          <t>Copy logs/runs.jsonl into evidence/ (scp — see evidence/README.md) BEFORE reverting. A revert deletes it.</t>
         </is>
       </c>
     </row>
@@ -924,28 +924,6 @@
         </is>
       </c>
     </row>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B3:C3"/>
@@ -1131,7 +1109,7 @@
       </c>
       <c r="N2" s="8" t="inlineStr">
         <is>
-          <t>Healed 92% → 86% against a synthetic apt cache (916M of downloaded kernels). Never touches user data, so it cannot rescue a disk the user filled. The journal half runs first, so a held apt lock still banks it. DPkg::Lock::Timeout does NOT cover the archives lock — the engine reports 'blocked' instead. The sketch's autoremove --purge is not part of this fix.</t>
+          <t>Healed three times, always against a synthetic apt cache (916M of downloaded kernels): this command 92% → 86% (09-09), and two earlier versions 90% → 85% (both 09-08). Pushed to 95% it cannot get back under 90% (verify_failed, 09-08), so land at 91%. Never touches user data, so it cannot rescue a disk the user filled. The journal half runs first, so a held apt lock still banks it (it freed 11M on 09-09). DPkg::Lock::Timeout does NOT cover the archives lock — the engine reports 'blocked' instead. The sketch's autoremove --purge is not part of this fix.</t>
         </is>
       </c>
       <c r="O2" s="8" t="inlineStr">
@@ -1198,7 +1176,7 @@
       </c>
       <c r="K3" s="10" t="inlineStr">
         <is>
-          <t>apt-get autoremove --purge -y  (healed 2026-09-07). The playbook now adds -o DPkg::Lock::Timeout=60; that version has run (exit 0) but has not healed anything yet.</t>
+          <t>apt-get -o DPkg::Lock::Timeout=60 autoremove --purge -y  (healed 2026-09-08, 89% → 65%). Without the timeout it healed 2026-09-07 (100% → 76%).</t>
         </is>
       </c>
       <c r="L3" s="10" t="inlineStr">
@@ -1213,17 +1191,17 @@
       </c>
       <c r="N3" s="10" t="inlineStr">
         <is>
-          <t>Healed 100% → 76%, but the full /boot was INDUCED with a filler file — a 2G /boot doesn't fill naturally. Kept the running kernel + one fallback. autoremove is not kernel-scoped: the blast radius on a machine with more auto-installed packages is not vetted — simulate with -s first. Reports 0 when /boot is not a separate mount. The 09-09 re-run gave verify_failed because nothing was left to remove — correct behaviour.</t>
+          <t>Healed twice: 100% → 76% (09-07) and 89% → 65% (09-08). Both times /boot was INDUCED full with a filler file — a 2G /boot doesn't fill naturally. Kept the running kernel + one fallback. autoremove is not kernel-scoped: the blast radius on a machine with more auto-installed packages is not vetted — simulate with -s first. Reports 0 when /boot is not a separate mount. Three re-runs (09-09 twice, 09-10) gave verify_failed because nothing was left to remove — correct behaviour.</t>
         </is>
       </c>
       <c r="O3" s="10" t="inlineStr">
         <is>
-          <t>2026-09-09 · 26.04 · verify_failed (93% → 93%, nothing to remove)</t>
+          <t>2026-09-10 · 26.04 · verify_failed (93% → 93%, nothing to remove)</t>
         </is>
       </c>
       <c r="P3" s="10" t="inlineStr">
         <is>
-          <t>Re-prove the amended command on 24.04 with removable kernels present (Session 6).</t>
+          <t>Re-prove on 24.04 with removable kernels present (Session 6).</t>
         </is>
       </c>
     </row>
@@ -3399,10 +3377,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
@@ -3414,7 +3392,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="16" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Date (IST)</t>
         </is>
       </c>
       <c r="B1" s="16" t="inlineStr">
@@ -3448,10 +3426,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
+    <row r="2" ht="43" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-05 14:20</t>
         </is>
       </c>
       <c r="B2" s="8" t="inlineStr">
@@ -3481,14 +3459,14 @@
       </c>
       <c r="G2" s="8" t="inlineStr">
         <is>
-          <t>from notes — runs.jsonl not copied off yet</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
+          <t>Quoted from the VM's log in commit 541cb09. Not in a copied file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="43" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-05 16:17</t>
         </is>
       </c>
       <c r="B3" s="10" t="inlineStr">
@@ -3518,14 +3496,14 @@
       </c>
       <c r="G3" s="10" t="inlineStr">
         <is>
-          <t>from notes — runs.jsonl not copied off yet</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
+          <t>Quoted from the VM's log in commit 541cb09. Not in a copied file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="43" customHeight="1">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-05 16:18</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
@@ -3548,17 +3526,17 @@
           <t>healed</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr"/>
+      <c r="F4" s="8" t="n"/>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t>from notes — runs.jsonl not copied off yet</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
+          <t>Quoted from the VM's log in commit 541cb09. Not in a copied file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="43" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-07 21:29</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
@@ -3581,17 +3559,17 @@
           <t>rolled_back</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr"/>
+      <c r="F5" s="10" t="n"/>
       <c r="G5" s="10" t="inlineStr">
         <is>
-          <t>from notes — runs.jsonl not copied off yet</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
+          <t>Quoted from the VM's log in commit 541cb09. Not in a copied file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="43" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-07 21:30</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
@@ -3614,10 +3592,10 @@
           <t>healed</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr"/>
+      <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>from notes — runs.jsonl not copied off yet</t>
+          <t>Quoted from the VM's log in commit 541cb09. Not in a copied file.</t>
         </is>
       </c>
     </row>
@@ -3654,14 +3632,14 @@
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
-          <t>from notes — runs.jsonl not copied off yet</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
+          <t>Described in commit a42e25c. Not in a copied file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="43" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-07 23:35</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
@@ -3669,7 +3647,11 @@
           <t>26.04</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr"/>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>before 841625b</t>
+        </is>
+      </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
           <t>disk-root-near-full</t>
@@ -3682,19 +3664,19 @@
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>unattended-upgrades held the apt lock. First real fix_failed and reverse: none.</t>
+          <t>92%. unattended-upgrades held the apt lock (exit 100). First real fix_failed and reverse: none. This version ran apt first, so the journal half never ran.</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>from notes — runs.jsonl not copied off yet</t>
+          <t>evidence/ubuntu-26.04-2026-09-10.jsonl, line 1</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-08 00:44</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
@@ -3714,24 +3696,24 @@
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>fix_failed</t>
+          <t>healed</t>
         </is>
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
-          <t>Lock held on purpose (fcntl holder). The 'before' control: exit 100 in ~4s.</t>
+          <t>90% → 85%. The older command, apt-get clean first. Not recorded before 2026-10-03.</t>
         </is>
       </c>
       <c r="G9" s="10" t="inlineStr">
         <is>
-          <t>from notes — runs.jsonl not copied off yet</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
+          <t>evidence/ubuntu-26.04-2026-09-10.jsonl, line 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="43" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08 00:49</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
@@ -3741,7 +3723,7 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>841625b or later</t>
+          <t>before 841625b</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
@@ -3751,24 +3733,24 @@
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>blocked</t>
+          <t>verify_failed</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>Lock held 90s against a 60s DPkg::Lock::Timeout; apt failed instantly, so the timeout doesn't cover the archives lock.</t>
+          <t>95% → 93%. Pushed too far past 90% for the reclaim to bring it back (the sizing trap). The first real verify_failed. Not recorded before 2026-10-03.</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>from notes — runs.jsonl not copied off yet</t>
+          <t>evidence/ubuntu-26.04-2026-09-10.jsonl, line 3</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08 00:49</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
@@ -3776,7 +3758,11 @@
           <t>26.04</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr"/>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>before 841625b</t>
+        </is>
+      </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
           <t>disk-root-near-full</t>
@@ -3784,24 +3770,24 @@
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>healed</t>
+          <t>verify_failed</t>
         </is>
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
-          <t>92% → 86%. First completed run.</t>
+          <t>93% → 93%. Re-run 22 seconds later: nothing left to reclaim. Not recorded before 2026-10-03.</t>
         </is>
       </c>
       <c r="G11" s="10" t="inlineStr">
         <is>
-          <t>from notes — runs.jsonl not copied off yet</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
+          <t>evidence/ubuntu-26.04-2026-09-10.jsonl, line 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="43" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08 01:14</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
@@ -3809,32 +3795,36 @@
           <t>26.04</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr"/>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>before 841625b</t>
+        </is>
+      </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>boot-partition-full</t>
+          <t>disk-root-near-full</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>verify_failed</t>
+          <t>fix_failed</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>93% → 93%. Nothing left to remove.</t>
+          <t>91%. Lock held on purpose (fcntl holder). The 'before' control: exit 100 in ~4s (the timing is from notes). 841625b was committed 4 minutes later.</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>from notes — runs.jsonl not copied off yet</t>
+          <t>evidence/ubuntu-26.04-2026-09-10.jsonl, line 5</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08 11:21</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
@@ -3842,38 +3832,334 @@
           <t>26.04</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr"/>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>841625b</t>
+        </is>
+      </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
+          <t>disk-root-near-full</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>healed</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>90% → 85%. Journal first, with DPkg::Lock::Timeout=60. Not recorded before 2026-10-03.</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-26.04-2026-09-10.jsonl, line 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="43" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-08 11:59</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>26.04</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>841625b</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>boot-partition-full</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>healed</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>89% → 65%. The amended command (with DPkg::Lock::Timeout=60) healed; the docs had said it never had. Not recorded before 2026-10-03.</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-26.04-2026-09-10.jsonl, line 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="43" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-09 18:41</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>26.04</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>841625b</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>disk-root-near-full</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>92%. Lock held 90s against a 60s DPkg::Lock::Timeout; apt failed instantly, so the timeout doesn't cover the archives lock. The journal half ran first and still freed 11M.</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-26.04-2026-09-10.jsonl, line 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-09 18:57</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>26.04</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>55247f0</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>disk-root-near-full</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>healed</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>92% → 86%. First heal of the current command (no lock timeout).</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-26.04-2026-09-10.jsonl, line 9</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-09 18:58</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>26.04</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>55247f0</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
           <t>net-tools-missing</t>
         </is>
       </c>
-      <c r="E13" s="10" t="inlineStr">
+      <c r="E17" s="10" t="inlineStr">
         <is>
           <t>healed</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
-        <is>
-          <t>Twice. The reverse command was also run by hand: removed cleanly.</t>
-        </is>
-      </c>
-      <c r="G13" s="10" t="inlineStr">
-        <is>
-          <t>from notes — runs.jsonl not copied off yet</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="42" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>Rebuilt on 2026-10-02 from DESIGN.md, the playbooks' source: lines and session notes. The real records are logs/runs.jsonl on the VM. Once Session 0 copies them off, fill in the blank commits and replace 'from notes' with the evidence file name. Add one row per run from now on.</t>
+      <c r="F17" s="10" t="n"/>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-26.04-2026-09-10.jsonl, line 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="43" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-09 18:59</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>26.04</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>55247f0</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>net-tools-missing</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>healed</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>Second run. In between, the reverse command was run by hand and removed the package cleanly (from notes; by hand, so not in the log).</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-26.04-2026-09-10.jsonl, line 11</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="43" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-09 19:01</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>26.04</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>55247f0</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>boot-partition-full</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>verify_failed</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>93% → 93%. Nothing left to remove: the 09-08 run had taken every removable kernel, and autoremove can't touch the filler file.</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-26.04-2026-09-10.jsonl, line 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-09 19:01</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>26.04</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>55247f0</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>boot-partition-full</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>verify_failed</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>93% → 93%. Re-run 19 seconds later. Same result.</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-26.04-2026-09-10.jsonl, line 13</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-10 22:36</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>26.04</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>55247f0</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>boot-partition-full</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>verify_failed</t>
+        </is>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>93% → 93%. Same state, a day later. Not recorded before 2026-10-03.</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-26.04-2026-09-10.jsonl, line 14</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="56" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>Times are IST (UTC+05:30). The log itself records UTC. Rows from 2026-09-07 23:35 on are records in evidence/ubuntu-26.04-2026-09-10.jsonl, copied off the VM on 2026-10-03. The six rows before that come from commit messages: the VM's log was reset on the evening of 2026-09-07, before anyone copied it. Add one row per run from now on, pointing at its evidence file and line.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A23:G23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/sf3000-tracker.xlsx
+++ b/docs/sf3000-tracker.xlsx
@@ -535,7 +535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:C38"/>
+  <dimension ref="B2:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -543,7 +543,6 @@
     <col width="92" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -559,7 +558,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="B5" s="1" t="inlineStr">
         <is>
@@ -868,7 +866,6 @@
         </is>
       </c>
     </row>
-    <row r="33"/>
     <row r="34">
       <c r="B34" s="1" t="inlineStr">
         <is>
@@ -3377,7 +3374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -4150,16 +4147,238 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="56" customHeight="1">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>Times are IST (UTC+05:30). The log itself records UTC. Rows from 2026-09-07 23:35 on are records in evidence/ubuntu-26.04-2026-09-10.jsonl, copied off the VM on 2026-10-03. The six rows before that come from commit messages: the VM's log was reset on the evening of 2026-09-07, before anyone copied it. Add one row per run from now on, pointing at its evidence file and line.</t>
+    <row r="22" ht="56" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>26.04</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>69658de</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>snapshot-gate-proof</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>refused (exit 4)</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>Ran first, just before 00:23. Refused before running anything, and the marker file was never created. First real snapshot-gate refusal.</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>Terminal output, confirmed by the person who ran it. The gate writes no record by design.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-04 00:23</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>26.04</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>69658de</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>rollback-failed-proof</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>declined</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>Answered N. Nothing ran (fix_exit_code null) and the decline was logged with confirmed false. First real declined.</t>
+        </is>
+      </c>
+      <c r="G23" s="10" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-26.04-2026-10-04.jsonl, line 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="43" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-04 00:24</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>26.04</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>69658de</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>rollback-failed-proof</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>rollback_failed</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>Answered y. The fix (true) exited 0 but the check still read 1; the undo exited 7 on purpose. First real rollback_failed.</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-26.04-2026-10-04.jsonl, line 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="43" customHeight="1">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-04 00:25</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>26.04</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>69658de</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>verify-error-proof</t>
+        </is>
+      </c>
+      <c r="E25" s="10" t="inlineStr">
+        <is>
+          <t>rolled_back</t>
+        </is>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>Verify could not parse 'not-a-number': verify_error set, verify_after null, and the undo wrote 99 back. First real verify_error.</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-26.04-2026-10-04.jsonl, line 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-04 00:29</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>26.04</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>69658de</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>rollback-proof</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>rolled_back</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>cowsay installed (exit 0), check unchanged, cowsay removed again. First run of the marker detect.</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-26.04-2026-10-04.jsonl, line 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-04 00:30</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>26.04</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>69658de</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>rollback-proof</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>rolled_back</t>
+        </is>
+      </c>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>Second run, 41 seconds later, with no setup in between: it repeats.</t>
+        </is>
+      </c>
+      <c r="G27" s="10" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-26.04-2026-10-04.jsonl, line 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="68" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>Times are IST (UTC+05:30). The logs themselves record UTC. Rows from 2026-09-07 23:35 to 2026-09-10 are records in evidence/ubuntu-26.04-2026-09-10.jsonl, copied off the VM on 2026-10-03; rows from 2026-10-04 are in evidence/ubuntu-26.04-2026-10-04.jsonl. The six rows before 2026-09-07 23:35 come from commit messages: the VM's log was reset on the evening of 2026-09-07, before anyone copied it. Add one row per run from now on, pointing at its evidence file and line.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="A29:G29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/sf3000-tracker.xlsx
+++ b/docs/sf3000-tracker.xlsx
@@ -1240,31 +1240,56 @@
       </c>
       <c r="H4" s="8" t="inlineStr">
         <is>
-          <t>candidates/failed-systemd-units.yaml</t>
+          <t>playbooks/failed-systemd-units.yaml</t>
         </is>
       </c>
       <c r="I4" s="9" t="inlineStr">
         <is>
-          <t>Candidate</t>
-        </is>
-      </c>
-      <c r="J4" s="8" t="inlineStr"/>
-      <c r="K4" s="8" t="inlineStr"/>
-      <c r="L4" s="8" t="inlineStr"/>
-      <c r="M4" s="8" t="inlineStr"/>
+          <t>Proven</t>
+        </is>
+      </c>
+      <c r="J4" s="8" t="inlineStr">
+        <is>
+          <t>systemctl --failed --type=service --no-legend --plain |
+  awk '$2 == "loaded" {print $1}' |
+  while read -r u; do
+    [ "$(systemctl show -p Type --value "$u")" = oneshot ] || echo "$u"
+  done</t>
+        </is>
+      </c>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
+          <t>systemctl --failed --type=service --no-legend --plain |
+  awk '$2 == "loaded" {print $1}' |
+  while read -r u; do
+    [ "$(systemctl show -p Type --value "$u")" = oneshot ] || echo "$u"
+  done |
+  xargs -r systemctl restart</t>
+        </is>
+      </c>
+      <c r="L4" s="8" t="inlineStr">
+        <is>
+          <t>No undo (reverse: none) — the services were already down, so there is nothing to put back. The VM run reached this branch: 'nothing to undo'.</t>
+        </is>
+      </c>
+      <c r="M4" s="8" t="inlineStr">
+        <is>
+          <t>Ubuntu 26.04 LTS (resolute)</t>
+        </is>
+      </c>
       <c r="N4" s="8" t="inlineStr">
         <is>
-          <t>The old fix (systemctl reset-failed) cleared the very flag the detect counted, so it could report healed on a broken machine. Replaced 2026-10-02: restart the failed services (never oneshot), wait 30s, check once. Moved out of playbooks/ until a VM run proves it. Close to the sketch's 'inspect, then restart'.</t>
+          <t>Proven against three throwaway services (tests/systemd-proof/), not a real service failure. A service whose cause had gone healed after a restart and the 30s wait. One that crashed 10s after its restart was caught by the wait (verify_failed); checked at once, it would have read healed. A failed oneshot was never counted or restarted (VM journal). It restarts EVERY failed, loaded, non-oneshot service, not just the one the user means — the y/N box lists them. Known limits: a crash more than 30s after the restart reads as healed; a slow crash-loop never shows as failed; if one of several restarts fails, the outcome is fix_failed even if the others recovered. The old fix (reset-failed) was circular and was replaced on 2026-10-02.</t>
         </is>
       </c>
       <c r="O4" s="8" t="inlineStr">
         <is>
-          <t>never run</t>
+          <t>2026-10-06 · 26.04 · healed (proof A) and verify_failed (proof B, caught by the 30s wait)</t>
         </is>
       </c>
       <c r="P4" s="8" t="inlineStr">
         <is>
-          <t>Session 2 on 26.04 with tests/systemd-proof/ (three throwaway services).</t>
+          <t>Re-prove on 24.04 (Session 6).</t>
         </is>
       </c>
     </row>
@@ -3374,7 +3399,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -4369,16 +4394,127 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="68" customHeight="1">
-      <c r="A29" s="19" t="inlineStr">
-        <is>
-          <t>Times are IST (UTC+05:30). The logs themselves record UTC. Rows from 2026-09-07 23:35 to 2026-09-10 are records in evidence/ubuntu-26.04-2026-09-10.jsonl, copied off the VM on 2026-10-03; rows from 2026-10-04 are in evidence/ubuntu-26.04-2026-10-04.jsonl. The six rows before 2026-09-07 23:35 come from commit messages: the VM's log was reset on the evening of 2026-09-07, before anyone copied it. Add one row per run from now on, pointing at its evidence file and line.</t>
+    <row r="28" ht="56" customHeight="1">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-06 23:34</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>26.04</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>10cb1fd</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>failed-systemd-units</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>healed</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>Proof A: sf3000-recovers, whose cause had been removed. The restart exited 0, then the 30s wait, then 1 → 0. A failed oneshot was present and was neither counted nor restarted. First real settle_seconds wait.</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-26.04-2026-10-06.jsonl, line 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="56" customHeight="1">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-06 23:36</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>26.04</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>10cb1fd</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>failed-systemd-units</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>verify_failed</t>
+        </is>
+      </c>
+      <c r="F29" s="10" t="inlineStr">
+        <is>
+          <t>Proof B: sf3000-crashes-late. The restart exited 0 at 23:36:51 and the service crashed at 23:37:01 (VM journal). The check after the 30s wait read 1 → 1; checked at once, it would have read healed. reverse: none logged 'nothing to undo'.</t>
+        </is>
+      </c>
+      <c r="G29" s="10" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-26.04-2026-10-06.jsonl, line 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="56" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>26.04</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>10cb1fd</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>failed-systemd-units</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>refused (exit 3)</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>Run without sudo just before 23:50, after the two fix runs, while sf3000-crashes-late was failed. Refused before the check ran, and asked nothing. First real privilege refusal.</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
+        <is>
+          <t>Terminal output (screenshot), confirmed by the person who ran it. The refusal writes no record by design.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="80" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>Times are IST (UTC+05:30). The logs themselves record UTC. Rows from 2026-09-07 23:35 to 2026-09-10 are records in evidence/ubuntu-26.04-2026-09-10.jsonl, copied off the VM on 2026-10-03; rows from 2026-10-04 are in evidence/ubuntu-26.04-2026-10-04.jsonl, and rows from 2026-10-06 in evidence/ubuntu-26.04-2026-10-06.jsonl. Rows whose Evidence says 'Terminal output' have no record: the engine refuses before it logs anything. The six rows before 2026-09-07 23:35 come from commit messages: the VM's log was reset on the evening of 2026-09-07, before anyone copied it. Add one row per run from now on, pointing at its evidence file and line.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A32:G32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/sf3000-tracker.xlsx
+++ b/docs/sf3000-tracker.xlsx
@@ -1526,26 +1526,46 @@
       </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
-          <t>Candidate</t>
-        </is>
-      </c>
-      <c r="J8" s="8" t="inlineStr"/>
-      <c r="K8" s="8" t="inlineStr"/>
-      <c r="L8" s="8" t="inlineStr"/>
-      <c r="M8" s="8" t="inlineStr"/>
+          <t>Testing</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>The detect: block of candidates/eos-release-dead-repos.yaml, unchanged since 3c7adac. Too long for a cell (about 25 lines). Reads distro-info's EOL date, counts old-archive URLs in apt's sources, and asks archive.ubuntu.com (404) and old-releases (200). On 22.10 it found 20, and the sweep left sources.list's sha256 unchanged.</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
+          <t>for f in /etc/apt/sources.list /etc/apt/sources.list.d/*.list /etc/apt/sources.list.d/*.sources; do
+  [ -e "$f" ] || continue
+  cp -n "$f" "$f.sf3000.bak"
+  sed -i -E -e 's|https?://[a-z0-9.-]*archive\.ubuntu\.com/ubuntu|http://old-releases.ubuntu.com/ubuntu|g' -e 's|https?://security\.ubuntu\.com/ubuntu|http://old-releases.ubuntu.com/ubuntu|g' "$f"
+done</t>
+        </is>
+      </c>
+      <c r="L8" s="8" t="inlineStr">
+        <is>
+          <t>Yes: the reverse command moves each *.sf3000.bak back over its file. Run by hand on 22.10 (2026-10-07): sources.list's sha256 matched the original. Not yet through the engine's own rollback, which only runs when verify fails.</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="inlineStr">
+        <is>
+          <t>Ubuntu 22.10 (kinetic)</t>
+        </is>
+      </c>
       <c r="N8" s="8" t="inlineStr">
         <is>
-          <t>The origin story — the lab ran 22.10 (kinetic). Fixed 2026-10-02: the detect read the fix's own backup files (so it could never heal) and fired on any release past its EOL date, even ones still on the main archive (20.04, 25.04, 25.10), where the fix would have broken apt. It now asks both servers first. Verify proves the sources were rewritten, not that apt update works — check by hand.</t>
+          <t>The origin story — the lab ran 22.10 (kinetic). Fixed 2026-10-02: the detect read the fix's own backup files (so it could never heal) and fired on any release past its EOL date, even ones still on the main archive (20.04, 25.04, 25.10), where the fix would have broken apt. It now asks both servers first. Verify proves the sources were rewritten, not that apt update works — check by hand (it was clean after both 22.10 runs). The count includes commented-out lines: 22.10 has 10 deb lines plus 10 '# deb-src' twins, so it found 20. The fix rewrites both, so it still heals, but old URLs left only in comments would still read as a problem. Not yet seen: the deb822 format, the security.ubuntu.com branch, the HEALTHY branch.</t>
         </is>
       </c>
       <c r="O8" s="8" t="inlineStr">
         <is>
-          <t>never run (offline fake-root test only)</t>
+          <t>2026-10-07 · 22.10 · healed (twice; the undo run by hand in between)</t>
         </is>
       </c>
       <c r="P8" s="8" t="inlineStr">
         <is>
-          <t>Sessions 3 + 4: 22.10 and 24.10 must heal. Session 5: 20.04 and 25.04 must stay HEALTHY.</t>
+          <t>Session 4: 24.10 must heal (deb822 sources). Session 5: 20.04 and 25.04 must stay HEALTHY. Then it can move to playbooks/.</t>
         </is>
       </c>
     </row>
@@ -2981,7 +3001,7 @@
       </c>
       <c r="E3" s="10" t="inlineStr">
         <is>
-          <t>To build</t>
+          <t>Have it</t>
         </is>
       </c>
       <c r="F3" s="18" t="n">
@@ -2994,12 +3014,12 @@
       </c>
       <c r="H3" s="10" t="inlineStr">
         <is>
-          <t>https://old-releases.ubuntu.com/releases/22.10/ubuntu-22.10-live-server-amd64.iso</t>
+          <t>(installed: 'KineticServer', from https://old-releases.ubuntu.com/releases/22.10/ubuntu-22.10-live-server-amd64.iso)</t>
         </is>
       </c>
       <c r="I3" s="10" t="inlineStr">
         <is>
-          <t>Yes (Python 3.10)</t>
+          <t>Yes — proven (Python 3.10)</t>
         </is>
       </c>
     </row>
@@ -3377,10 +3397,10 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="42" customHeight="1">
+    <row r="15" ht="56" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
         <is>
-          <t>Each VM: 2 GB RAM, 2 CPUs, 25 GB disk in E:\VMs, NAT with its own SSH port bound to 127.0.0.1. Install end-of-life releases with the network cable unplugged, so the installed sources point at the dead archive — the state the lab machines were in. Python versions are each release's default python3.</t>
+          <t>Each new VM: 4 GB RAM, 1 CPU, 40 GB disk in E:\VMs, NAT with its own SSH port bound to 127.0.0.1. One CPU because VirtualBox runs on top of Hyper-V on this host, and the 22.10 VM stalled on every boot with 2. The 26.04 VM ('Ubuntu Server Test') is older: 2 GB RAM, 2 CPUs. Install end-of-life releases with the network cable unplugged, so the installed sources point at the dead archive — the state the lab machines were in. Python versions are each release's default python3.</t>
         </is>
       </c>
     </row>
@@ -3399,7 +3419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -4505,16 +4525,90 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="80" customHeight="1">
-      <c r="A32" s="19" t="inlineStr">
-        <is>
-          <t>Times are IST (UTC+05:30). The logs themselves record UTC. Rows from 2026-09-07 23:35 to 2026-09-10 are records in evidence/ubuntu-26.04-2026-09-10.jsonl, copied off the VM on 2026-10-03; rows from 2026-10-04 are in evidence/ubuntu-26.04-2026-10-04.jsonl, and rows from 2026-10-06 in evidence/ubuntu-26.04-2026-10-06.jsonl. Rows whose Evidence says 'Terminal output' have no record: the engine refuses before it logs anything. The six rows before 2026-09-07 23:35 come from commit messages: the VM's log was reset on the evening of 2026-09-07, before anyone copied it. Add one row per run from now on, pointing at its evidence file and line.</t>
+    <row r="31" ht="56" customHeight="1">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-07 11:10</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>22.10</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>4410bee</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>eos-release-dead-repos</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="inlineStr">
+        <is>
+          <t>healed</t>
+        </is>
+      </c>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>First run of this detect anywhere, and the first run on a release other than 26.04. Found 20 old-archive URLs (10 deb lines and their 10 commented '# deb-src' twins), rewrote them, found 0. The sweep before it left sources.list's sha256 unchanged; apt-get update failed before and was clean after.</t>
+        </is>
+      </c>
+      <c r="G31" s="10" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-22.10-2026-10-07.jsonl, line 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="56" customHeight="1">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-07 11:12</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>22.10</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>4410bee</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>eos-release-dead-repos</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>healed</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>After the playbook's reverse text was run by hand: sources.list's sha256 matched the original, and the detect found 20 again. 20 → 0, and apt-get update was clean.</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-22.10-2026-10-07.jsonl, line 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="95" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>Times are IST (UTC+05:30). The logs themselves record UTC. Rows from 2026-09-07 23:35 to 2026-09-10 are records in evidence/ubuntu-26.04-2026-09-10.jsonl, copied off the VM on 2026-10-03; rows from 2026-10-04 are in evidence/ubuntu-26.04-2026-10-04.jsonl, rows from 2026-10-06 in evidence/ubuntu-26.04-2026-10-06.jsonl, and rows from 2026-10-07 in evidence/ubuntu-22.10-2026-10-07.jsonl (the 22.10 VM, KineticServer). Rows whose Evidence says 'Terminal output' have no record: the engine refuses before it logs anything. The six rows before 2026-09-07 23:35 come from commit messages: the VM's log was reset on the evening of 2026-09-07, before anyone copied it. Add one row per run from now on, pointing at its evidence file and line.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A34:G34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/sf3000-tracker.xlsx
+++ b/docs/sf3000-tracker.xlsx
@@ -1531,7 +1531,7 @@
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>The detect: block of candidates/eos-release-dead-repos.yaml, unchanged since 3c7adac. Too long for a cell (about 25 lines). Reads distro-info's EOL date, counts old-archive URLs in apt's sources, and asks archive.ubuntu.com (404) and old-releases (200). On 22.10 it found 20, and the sweep left sources.list's sha256 unchanged.</t>
+          <t>Proven on 22.10: the detect: block of candidates/eos-release-dead-repos.yaml as of 4410bee (too long for a cell, about 25 lines). Reads distro-info's EOL date, counts old-archive URLs in apt's sources, and asks archive.ubuntu.com (404) and old-releases (200). It found 20, and the sweep left sources.list's sha256 unchanged. The current detect differs by one line (it skips comments) and has NOT run on a VM yet.</t>
         </is>
       </c>
       <c r="K8" s="8" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="N8" s="8" t="inlineStr">
         <is>
-          <t>The origin story — the lab ran 22.10 (kinetic). Fixed 2026-10-02: the detect read the fix's own backup files (so it could never heal) and fired on any release past its EOL date, even ones still on the main archive (20.04, 25.04, 25.10), where the fix would have broken apt. It now asks both servers first. Verify proves the sources were rewritten, not that apt update works — check by hand (it was clean after both 22.10 runs). The count includes commented-out lines: 22.10 has 10 deb lines plus 10 '# deb-src' twins, so it found 20. The fix rewrites both, so it still heals, but old URLs left only in comments would still read as a problem. Not yet seen: the deb822 format, the security.ubuntu.com branch, the HEALTHY branch.</t>
+          <t>The origin story — the lab ran 22.10 (kinetic). Fixed 2026-10-02: the detect read the fix's own backup files (so it could never heal) and fired on any release past its EOL date, even ones still on the main archive (20.04, 25.04, 25.10), where the fix would have broken apt. It now asks both servers first. Verify proves the sources were rewritten, not that apt update works — check by hand (it was clean after both 22.10 runs). On 22.10 the detect counted 20: 10 deb lines plus their 10 '# deb-src' twins. It healed anyway, since the fix rewrites both, but old URLs left only in comments read as a problem. Changed 2026-10-07 to skip comments (offline test: 20 → 10, and 10 → 0 for comments-only). Not yet seen: the deb822 format, the security.ubuntu.com branch, and HEALTHY on a release still on the main archive.</t>
         </is>
       </c>
       <c r="O8" s="8" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="P8" s="8" t="inlineStr">
         <is>
-          <t>Session 4: 24.10 must heal (deb822 sources). Session 5: 20.04 and 25.04 must stay HEALTHY. Then it can move to playbooks/.</t>
+          <t>Re-run 22.10 from clean-baseline with the comment-skipping detect: expect 10, not 20, and step 4b HEALTHY. Session 4: 24.10 must heal (deb822 sources). Session 5: 20.04 and 25.04 must stay HEALTHY. Then it can move to playbooks/.</t>
         </is>
       </c>
     </row>

--- a/docs/sf3000-tracker.xlsx
+++ b/docs/sf3000-tracker.xlsx
@@ -1531,7 +1531,7 @@
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>Proven on 22.10: the detect: block of candidates/eos-release-dead-repos.yaml as of 4410bee (too long for a cell, about 25 lines). Reads distro-info's EOL date, counts old-archive URLs in apt's sources, and asks archive.ubuntu.com (404) and old-releases (200). It found 20, and the sweep left sources.list's sha256 unchanged. The current detect differs by one line (it skips comments) and has NOT run on a VM yet.</t>
+          <t>Proven on 22.10 (2026-10-07, commit 0be2d76): the detect: block of candidates/eos-release-dead-repos.yaml (too long for a cell, about 25 lines). Reads distro-info's EOL date, counts old-archive URLs on apt's active lines (it drops everything after #), and asks archive.ubuntu.com (404) and old-releases (200). It found 10, and read HEALTHY when only the comments held old URLs. The first run's sweep left sources.list's sha256 unchanged.</t>
         </is>
       </c>
       <c r="K8" s="8" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="N8" s="8" t="inlineStr">
         <is>
-          <t>The origin story — the lab ran 22.10 (kinetic). Fixed 2026-10-02: the detect read the fix's own backup files (so it could never heal) and fired on any release past its EOL date, even ones still on the main archive (20.04, 25.04, 25.10), where the fix would have broken apt. It now asks both servers first. Verify proves the sources were rewritten, not that apt update works — check by hand (it was clean after both 22.10 runs). On 22.10 the detect counted 20: 10 deb lines plus their 10 '# deb-src' twins. It healed anyway, since the fix rewrites both, but old URLs left only in comments read as a problem. Changed 2026-10-07 to skip comments (offline test: 20 → 10, and 10 → 0 for comments-only). Not yet seen: the deb822 format, the security.ubuntu.com branch, and HEALTHY on a release still on the main archive.</t>
+          <t>The origin story — the lab ran 22.10 (kinetic). Fixed 2026-10-02: the detect read the fix's own backup files (so it could never heal) and fired on any release past its EOL date, even ones still on the main archive (20.04, 25.04, 25.10), where the fix would have broken apt. It now asks both servers first. Verify proves the sources were rewritten, not that apt update works — check by hand (it was clean after both 22.10 runs). On 22.10 the detect counted 20: 10 deb lines plus their 10 '# deb-src' twins. It healed anyway, since the fix rewrites both, but old URLs left only in comments read as a problem. Changed 2026-10-07 to skip comments, and re-run on 22.10 the same day: it found 10, and read HEALTHY with only the comments left old. Not yet seen: the deb822 format, the security.ubuntu.com branch, and HEALTHY on a release still on the main archive.</t>
         </is>
       </c>
       <c r="O8" s="8" t="inlineStr">
         <is>
-          <t>2026-10-07 · 22.10 · healed (twice; the undo run by hand in between)</t>
+          <t>2026-10-07 · 22.10 · healed ×4 (2 per detect version, the undo run by hand between each pair); HEALTHY with only comments left old</t>
         </is>
       </c>
       <c r="P8" s="8" t="inlineStr">
         <is>
-          <t>Re-run 22.10 from clean-baseline with the comment-skipping detect: expect 10, not 20, and step 4b HEALTHY. Session 4: 24.10 must heal (deb822 sources). Session 5: 20.04 and 25.04 must stay HEALTHY. Then it can move to playbooks/.</t>
+          <t>Session 4: 24.10 must heal (deb822 sources). Session 5: 20.04 and 25.04 must stay HEALTHY. Then it can move to playbooks/.</t>
         </is>
       </c>
     </row>
@@ -3419,7 +3419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -4599,16 +4599,128 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="95" customHeight="1">
-      <c r="A34" s="19" t="inlineStr">
-        <is>
-          <t>Times are IST (UTC+05:30). The logs themselves record UTC. Rows from 2026-09-07 23:35 to 2026-09-10 are records in evidence/ubuntu-26.04-2026-09-10.jsonl, copied off the VM on 2026-10-03; rows from 2026-10-04 are in evidence/ubuntu-26.04-2026-10-04.jsonl, rows from 2026-10-06 in evidence/ubuntu-26.04-2026-10-06.jsonl, and rows from 2026-10-07 in evidence/ubuntu-22.10-2026-10-07.jsonl (the 22.10 VM, KineticServer). Rows whose Evidence says 'Terminal output' have no record: the engine refuses before it logs anything. The six rows before 2026-09-07 23:35 come from commit messages: the VM's log was reset on the evening of 2026-09-07, before anyone copied it. Add one row per run from now on, pointing at its evidence file and line.</t>
+    <row r="33" ht="56" customHeight="1">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-07 12:13</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>22.10</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>0be2d76</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>eos-release-dead-repos</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t>healed</t>
+        </is>
+      </c>
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>Re-run from clean-baseline with the detect that skips commented-out lines. Found 10 (active lines only; the old detect found 20 on the same file), rewrote them, found 0.</t>
+        </is>
+      </c>
+      <c r="G33" s="10" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-22.10-2026-10-07-2.jsonl, line 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="56" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>22.10</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>0be2d76</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>eos-release-dead-repos</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>HEALTHY (sweep)</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>Step 4b, between the two runs: the active lines rewritten by hand, the 10 '# deb-src' comments left on the old address. The sweep read HEALTHY, measured=0. Before the detect change this read 10.</t>
+        </is>
+      </c>
+      <c r="G34" s="8" t="inlineStr">
+        <is>
+          <t>Terminal output (screenshot, 12:23), confirmed by the person who ran it. A sweep writes no record.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="56" customHeight="1">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-07 12:16</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>22.10</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>0be2d76</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>eos-release-dead-repos</t>
+        </is>
+      </c>
+      <c r="E35" s="10" t="inlineStr">
+        <is>
+          <t>healed</t>
+        </is>
+      </c>
+      <c r="F35" s="10" t="inlineStr">
+        <is>
+          <t>After the reverse text was run by hand and step 4b's copy put back: found 10 again, then 0.</t>
+        </is>
+      </c>
+      <c r="G35" s="10" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-22.10-2026-10-07-2.jsonl, line 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="36"/>
+    <row r="37" ht="105" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>Times are IST (UTC+05:30). The logs themselves record UTC. Rows from 2026-09-07 23:35 to 2026-09-10 are records in evidence/ubuntu-26.04-2026-09-10.jsonl, copied off the VM on 2026-10-03; rows from 2026-10-04 are in evidence/ubuntu-26.04-2026-10-04.jsonl, rows from 2026-10-06 in evidence/ubuntu-26.04-2026-10-06.jsonl, and rows from 2026-10-07 in evidence/ubuntu-22.10-2026-10-07.jsonl and, from 12:13, evidence/ubuntu-22.10-2026-10-07-2.jsonl (the 22.10 VM, KineticServer). Rows whose Evidence says 'Terminal output' have no record: the engine refuses before it logs anything, or the row is a sweep, which never logs. The six rows before 2026-09-07 23:35 come from commit messages: the VM's log was reset on the evening of 2026-09-07, before anyone copied it. Add one row per run from now on, pointing at its evidence file and line.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A37:G37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/sf3000-tracker.xlsx
+++ b/docs/sf3000-tracker.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Run log" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Ubuntu'!$A$1:$P$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Ubuntu'!$A$1:$P$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Windows'!$A$1:$P$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -935,7 +935,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P17"/>
+  <dimension ref="A1:P18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2079,13 +2079,79 @@
       <c r="O17" s="12" t="n"/>
       <c r="P17" s="12" t="n"/>
     </row>
+    <row r="18" ht="110" customHeight="1">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>release-upgrade-to-26.04</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>End-of-life release: upgrade in place to the current LTS (the lab's real goal)</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>Packages</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>Per step: VERSION_ID (as 2210, 2304, ...) and dpkg --audit; each step also requires the exact release it upgrades from</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>26.04 and no half-installed packages</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>A procedure, not a playbook: 22.10 → 23.04 → 23.10 (upgraders fetched from old-releases, signature checked) → 24.04 → 26.04 (do-release-upgrade), a reboot after each</t>
+        </is>
+      </c>
+      <c r="G18" s="13" t="inlineStr">
+        <is>
+          <t>destructive</t>
+        </is>
+      </c>
+      <c r="H18" s="12" t="inlineStr">
+        <is>
+          <t>candidates/procedures/release-upgrade-to-26.04.yaml</t>
+        </is>
+      </c>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>Candidate</t>
+        </is>
+      </c>
+      <c r="J18" s="12" t="n"/>
+      <c r="K18" s="12" t="n"/>
+      <c r="L18" s="12" t="n"/>
+      <c r="M18" s="12" t="n"/>
+      <c r="N18" s="12" t="inlineStr">
+        <is>
+          <t>Runs under the engine's procedure service (built 2026-10-07): one y/N, then it carries on across reboots. Needs a snapshot: --take-snapshot (Timeshift; restored by itself if a step fails, then checked) or --snapshot &lt;name&gt;. Precondition: apt works (eos-release-dead-repos healed). Written from the upgraders' source; plain do-release-upgrade would skip 23.04/23.10 and offer 24.04 directly from 22.10, which its upgrader is not built for.</t>
+        </is>
+      </c>
+      <c r="O18" s="12" t="inlineStr">
+        <is>
+          <t>never run (offline proof only: tests/procedure-proof/test_procedure.py)</t>
+        </is>
+      </c>
+      <c r="P18" s="12" t="inlineStr">
+        <is>
+          <t>On the 22.10 VM: tests/procedure-proof/ (runs A and B), then this from repos-fixed with --take-snapshot.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P17"/>
+  <autoFilter ref="A1:P18"/>
   <dataValidations count="2">
-    <dataValidation sqref="G2:G17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"safe,safe-moderate,moderate,moderate-destructive,destructive"</formula1>
     </dataValidation>
-    <dataValidation sqref="I2:I17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Not started,Candidate,Testing,Blocked,Proven,Has defect"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4710,7 +4776,6 @@
         </is>
       </c>
     </row>
-    <row r="36"/>
     <row r="37" ht="105" customHeight="1">
       <c r="A37" s="19" t="inlineStr">
         <is>

--- a/docs/sf3000-tracker.xlsx
+++ b/docs/sf3000-tracker.xlsx
@@ -2082,7 +2082,7 @@
     <row r="18" ht="110" customHeight="1">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>release-upgrade-to-26.04</t>
+          <t>release-upgrade-to-23.04, -23.10, -24.04, -26.04</t>
         </is>
       </c>
       <c r="B18" s="12" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>Per step: VERSION_ID (as 2210, 2304, ...) and dpkg --audit; each step also requires the exact release it upgrades from</t>
+          <t>Per procedure: VERSION_ID (as 2210, 2304, ...) and dpkg --audit; each also requires the exact release it upgrades from</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>26.04 and no half-installed packages</t>
+          <t>The next release (26.04 at the end) and no half-installed packages</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr">
         <is>
-          <t>A procedure, not a playbook: 22.10 → 23.04 → 23.10 (upgraders fetched from old-releases, signature checked) → 24.04 → 26.04 (do-release-upgrade), a reboot after each</t>
+          <t>Four procedures, one upgrade each, one per supervised visit: 22.10 → 23.04 → 23.10 (upgraders fetched from old-releases, signature checked) → 24.04 → 26.04 (do-release-upgrade), a reboot and the check after each</t>
         </is>
       </c>
       <c r="G18" s="13" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="H18" s="12" t="inlineStr">
         <is>
-          <t>candidates/procedures/release-upgrade-to-26.04.yaml</t>
+          <t>candidates/procedures/release-upgrade-to-*.yaml (README.md there)</t>
         </is>
       </c>
       <c r="I18" s="13" t="inlineStr">
@@ -2131,7 +2131,7 @@
       <c r="M18" s="12" t="n"/>
       <c r="N18" s="12" t="inlineStr">
         <is>
-          <t>Runs under the engine's procedure service (built 2026-10-07): one y/N, then it carries on across reboots. Needs a snapshot: --take-snapshot (Timeshift; restored by itself if a step fails, then checked) or --snapshot &lt;name&gt;. Precondition: apt works (eos-release-dead-repos healed). Written from the upgraders' source; plain do-release-upgrade would skip 23.04/23.10 and offer 24.04 directly from 22.10, which its upgrader is not built for.</t>
+          <t>Runs under the engine's procedure service: one y/N, then the upgrade, a reboot and the check. Since 2026-10-08: one upgrade per procedure and per visit (2-2.5 h lab slots, the person there); apt checked before the y/N; Timeshift installed by the engine if missing; /boot/efi left out of the snapshot (Windows' EFI partition on the lab's dual-boot machines); a step cut off by a power-off waits for the person (--run again offers the restore). Needs a snapshot: --take-snapshot (Timeshift; restored by itself if the upgrade fails, then checked) or --snapshot &lt;name&gt;. Precondition: apt works (eos-release-dead-repos healed). Written from the upgraders' source; plain do-release-upgrade would skip 23.04/23.10 and offer 24.04 directly from 22.10, which its upgrader is not built for.</t>
         </is>
       </c>
       <c r="O18" s="12" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="P18" s="12" t="inlineStr">
         <is>
-          <t>On the 22.10 VM: tests/procedure-proof/ (runs A and B), then this from repos-fixed with --take-snapshot.</t>
+          <t>On the 22.10 VM: tests/procedure-proof/ (runs A-D), then the four in order from repos-fixed with --take-snapshot; then an EFI desktop VM (the restore beside a shared EFI partition).</t>
         </is>
       </c>
     </row>

--- a/docs/sf3000-tracker.xlsx
+++ b/docs/sf3000-tracker.xlsx
@@ -646,7 +646,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Copy logs/runs.jsonl into evidence/ (scp — see evidence/README.md) BEFORE reverting. A revert deletes it.</t>
+          <t>Copy logs/runs.jsonl (for a procedure, /var/log/sf3000/runs.jsonl) into evidence/ (scp — see evidence/README.md) BEFORE reverting. A revert deletes it.</t>
         </is>
       </c>
     </row>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="I18" s="13" t="inlineStr">
         <is>
-          <t>Candidate</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="J18" s="12" t="n"/>
@@ -2131,17 +2131,17 @@
       <c r="M18" s="12" t="n"/>
       <c r="N18" s="12" t="inlineStr">
         <is>
-          <t>Runs under the engine's procedure service: one y/N, then the upgrade, a reboot and the check. Since 2026-10-08: one upgrade per procedure and per visit (2-2.5 h lab slots, the person there); apt checked before the y/N; Timeshift installed by the engine if missing; /boot/efi left out of the snapshot (Windows' EFI partition on the lab's dual-boot machines); a step cut off by a power-off waits for the person (--run again offers the restore). Needs a snapshot: --take-snapshot (Timeshift; restored by itself if the upgrade fails, then checked) or --snapshot &lt;name&gt;. Precondition: apt works (eos-release-dead-repos healed). Written from the upgraders' source; plain do-release-upgrade would skip 23.04/23.10 and offer 24.04 directly from 22.10, which its upgrader is not built for.</t>
+          <t>Runs under the engine's procedure service: one y/N, then the upgrade, a reboot and the check. Since 2026-10-08: one upgrade per procedure and per visit (2-2.5 h lab slots, the person there); apt checked before the y/N; Timeshift installed by the engine if missing; /boot/efi left out of the snapshot (Windows' EFI partition on the lab's dual-boot machines); a step cut off by a power-off waits for the person (--run again offers the restore). Needs a snapshot: --take-snapshot (Timeshift; restored by itself if the upgrade fails, then checked) or --snapshot &lt;name&gt;. Precondition: apt works (eos-release-dead-repos healed). Written from the upgraders' source; plain do-release-upgrade would skip 23.04/23.10 and offer 24.04 directly from 22.10, which its upgrader is not built for. Timeshift 22.06.5 to 24.01.1 refuse '--tags O', so the engine passes no tags (2b09c29).</t>
         </is>
       </c>
       <c r="O18" s="12" t="inlineStr">
         <is>
-          <t>never run (offline proof only: tests/procedure-proof/test_procedure.py)</t>
+          <t>2026-10-09 · 22.10 · the machinery passed: tests/procedure-proof Runs A-D (a reboot and its check, a time limit, Timeshift installed by the engine, its snapshot restored by itself, a power cut held for the person, the apt check's refusal). The four upgrades themselves: never run.</t>
         </is>
       </c>
       <c r="P18" s="12" t="inlineStr">
         <is>
-          <t>On the 22.10 VM: tests/procedure-proof/ (runs A-D), then the four in order from repos-fixed with --take-snapshot; then an EFI desktop VM (the restore beside a shared EFI partition).</t>
+          <t>Engine fixes first (sync after the snapshot; apt's lock held around the snapshot and the restore; every dead apt source named), then quick re-runs of Runs B and D. Then the four in order from repos-fixed with --take-snapshot, timed; then an EFI desktop VM (the restore beside a shared EFI partition).</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -4776,16 +4776,387 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="105" customHeight="1">
-      <c r="A37" s="19" t="inlineStr">
-        <is>
-          <t>Times are IST (UTC+05:30). The logs themselves record UTC. Rows from 2026-09-07 23:35 to 2026-09-10 are records in evidence/ubuntu-26.04-2026-09-10.jsonl, copied off the VM on 2026-10-03; rows from 2026-10-04 are in evidence/ubuntu-26.04-2026-10-04.jsonl, rows from 2026-10-06 in evidence/ubuntu-26.04-2026-10-06.jsonl, and rows from 2026-10-07 in evidence/ubuntu-22.10-2026-10-07.jsonl and, from 12:13, evidence/ubuntu-22.10-2026-10-07-2.jsonl (the 22.10 VM, KineticServer). Rows whose Evidence says 'Terminal output' have no record: the engine refuses before it logs anything, or the row is a sweep, which never logs. The six rows before 2026-09-07 23:35 come from commit messages: the VM's log was reset on the evening of 2026-09-07, before anyone copied it. Add one row per run from now on, pointing at its evidence file and line.</t>
+    <row r="36" ht="56" customHeight="1">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-08 19:56</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>22.10</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>1851179</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>procedure-proof/one</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>healed</t>
+        </is>
+      </c>
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>Run A, no snapshot. The first procedure step run on a VM: touched marker one, rebooted, and passed its check after the boot (verify_after 1).</t>
+        </is>
+      </c>
+      <c r="G36" s="10" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-22.10-2026-10-09.jsonl, line 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="56" customHeight="1">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-08 19:57</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>22.10</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>1851179</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>procedure-proof/two</t>
+        </is>
+      </c>
+      <c r="E37" s="10" t="inlineStr">
+        <is>
+          <t>healed</t>
+        </is>
+      </c>
+      <c r="F37" s="10" t="inlineStr">
+        <is>
+          <t>Run A: touched marker two, checked at once.</t>
+        </is>
+      </c>
+      <c r="G37" s="10" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-22.10-2026-10-09.jsonl, line 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="56" customHeight="1">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-08 19:57</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>22.10</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>1851179</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>procedure-proof/three</t>
+        </is>
+      </c>
+      <c r="E38" s="10" t="inlineStr">
+        <is>
+          <t>fix_failed</t>
+        </is>
+      </c>
+      <c r="F38" s="10" t="inlineStr">
+        <is>
+          <t>Run A: sleep 300 was stopped at its 1-minute limit (fix_exit_code null). With no snapshot, the procedure stopped there and the service removed itself. After a further sleep 300 the markers were still only one and two: the step really was killed.</t>
+        </is>
+      </c>
+      <c r="G38" s="10" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-22.10-2026-10-09.jsonl, line 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="56" customHeight="1">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 17:56</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>22.10</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>1851179</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>procedure-proof/install</t>
+        </is>
+      </c>
+      <c r="E39" s="10" t="inlineStr">
+        <is>
+          <t>installed</t>
+        </is>
+      </c>
+      <c r="F39" s="10" t="inlineStr">
+        <is>
+          <t>Run B: --take-snapshot installed Timeshift 22.06.5-1 with apt after the y (196 new packages, 86.8 MB in 42 s, exit 0). First time the engine installed what it needs.</t>
+        </is>
+      </c>
+      <c r="G39" s="10" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-22.10-2026-10-09.jsonl, line 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="56" customHeight="1">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 17:56</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>22.10</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t>1851179</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>procedure-proof/snapshot</t>
+        </is>
+      </c>
+      <c r="E40" s="10" t="inlineStr">
+        <is>
+          <t>snapshot_failed</t>
+        </is>
+      </c>
+      <c r="F40" s="10" t="inlineStr">
+        <is>
+          <t>Run B, first try: Timeshift 22.06.5 refused '--tags O' ("Unknown value"; its check leaves O out). No snapshot, so no step ran, and the service removed itself. Fixed in 2b09c29.</t>
+        </is>
+      </c>
+      <c r="G40" s="10" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-22.10-2026-10-09.jsonl, line 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="56" customHeight="1">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 18:39</t>
+        </is>
+      </c>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>22.10</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
+        <is>
+          <t>1ff0250</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>procedure-proof/one</t>
+        </is>
+      </c>
+      <c r="E41" s="10" t="inlineStr">
+        <is>
+          <t>healed</t>
+        </is>
+      </c>
+      <c r="F41" s="10" t="inlineStr">
+        <is>
+          <t>Run B again, after git pull. Timeshift snapshot 2026-10-09_13-07-11 (130 s, 8.2 GB), then one, a reboot, and its check after the boot.</t>
+        </is>
+      </c>
+      <c r="G41" s="10" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-22.10-2026-10-09.jsonl, line 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="56" customHeight="1">
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 18:39</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>22.10</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>1ff0250</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>procedure-proof/two</t>
+        </is>
+      </c>
+      <c r="E42" s="10" t="inlineStr">
+        <is>
+          <t>healed</t>
+        </is>
+      </c>
+      <c r="F42" s="10" t="inlineStr">
+        <is>
+          <t>Run B: checked at once.</t>
+        </is>
+      </c>
+      <c r="G42" s="10" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-22.10-2026-10-09.jsonl, line 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="56" customHeight="1">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 18:39</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>22.10</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>1ff0250</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>procedure-proof/three</t>
+        </is>
+      </c>
+      <c r="E43" s="10" t="inlineStr">
+        <is>
+          <t>rolled_back</t>
+        </is>
+      </c>
+      <c r="F43" s="10" t="inlineStr">
+        <is>
+          <t>Run B: three was stopped at its limit, and the engine restored its snapshot by itself. Timeshift deleted markers one and two, reinstalled GRUB and rebooted. The boot after matched the fingerprint: "ok: back to 22.10 packages:ec3d46dddee73727". First automatic restore on a real machine.</t>
+        </is>
+      </c>
+      <c r="G43" s="10" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-22.10-2026-10-09.jsonl, line 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="56" customHeight="1">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09 19:37</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>22.10</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="inlineStr">
+        <is>
+          <t>1ff0250</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>cut-off-proof/long</t>
+        </is>
+      </c>
+      <c r="E44" s="10" t="inlineStr">
+        <is>
+          <t>rolled_back</t>
+        </is>
+      </c>
+      <c r="F44" s="10" t="inlineStr">
+        <is>
+          <t>Run C: snapshot 2026-10-09_14-06-41 (23 s, linked to the last), then the VM was powered off mid-step. The boot after restored nothing (phase cut_off) and removed its service. The next --run offered the restore: n ("Nothing was done"), then y at 19:41. Timeshift deleted the started marker; the fingerprint matched. failure: interrupted.</t>
+        </is>
+      </c>
+      <c r="G44" s="10" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-22.10-2026-10-09.jsonl, line 9; the held boot from the journal (screenshot)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="56" customHeight="1">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>22.10</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t>1ff0250</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>procedure-proof</t>
+        </is>
+      </c>
+      <c r="E45" s="10" t="inlineStr">
+        <is>
+          <t>refused (exit 9)</t>
+        </is>
+      </c>
+      <c r="F45" s="10" t="inlineStr">
+        <is>
+          <t>Run D, just before 22:18: two dead sources added (a host under .invalid, a suite old-releases does not have). The apt check refused before the box; nothing was staged, and --status still showed Run C. It named only the missing suite: apt 2.5.3 prints no 'Failed to fetch' line once one source fails hard.</t>
+        </is>
+      </c>
+      <c r="G45" s="10" t="inlineStr">
+        <is>
+          <t>Terminal output (screenshot), confirmed by the person who ran it. The refusal writes no record by design.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46"/>
+    <row r="47" ht="120" customHeight="1">
+      <c r="A47" s="19" t="inlineStr">
+        <is>
+          <t>Times are IST (UTC+05:30). The logs themselves record UTC. Rows from 2026-09-07 23:35 to 2026-09-10 are records in evidence/ubuntu-26.04-2026-09-10.jsonl, copied off the VM on 2026-10-03; rows from 2026-10-04 are in evidence/ubuntu-26.04-2026-10-04.jsonl, rows from 2026-10-06 in evidence/ubuntu-26.04-2026-10-06.jsonl, and rows from 2026-10-07 in evidence/ubuntu-22.10-2026-10-07.jsonl and, from 12:13, evidence/ubuntu-22.10-2026-10-07-2.jsonl (the 22.10 VM, KineticServer). Rows from 2026-10-08 19:56 are the procedure runs, in evidence/ubuntu-22.10-2026-10-09.jsonl, copied from the service's own log, /var/log/sf3000/runs.jsonl. Rows whose Evidence says 'Terminal output' have no record: the engine refuses before it logs anything, or the row is a sweep, which never logs. The six rows before 2026-09-07 23:35 come from commit messages: the VM's log was reset on the evening of 2026-09-07, before anyone copied it. Add one row per run from now on, pointing at its evidence file and line.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A47:G47"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/sf3000-tracker.xlsx
+++ b/docs/sf3000-tracker.xlsx
@@ -2141,7 +2141,7 @@
       </c>
       <c r="P18" s="12" t="inlineStr">
         <is>
-          <t>Engine fixes first (sync after the snapshot; apt's lock held around the snapshot and the restore; every dead apt source named), then quick re-runs of Runs B and D. Then the four in order from repos-fixed with --take-snapshot, timed; then an EFI desktop VM (the restore beside a shared EFI partition).</t>
+          <t>Re-run Runs B and D on the 22.10 VM with the fixes (dpkg's lock held around the snapshot and the restore, the snapshot synced, every dead apt source named). Then the four in order from repos-fixed with --take-snapshot, timed; then an EFI desktop VM (the restore beside a shared EFI partition).</t>
         </is>
       </c>
     </row>
@@ -5146,7 +5146,6 @@
         </is>
       </c>
     </row>
-    <row r="46"/>
     <row r="47" ht="120" customHeight="1">
       <c r="A47" s="19" t="inlineStr">
         <is>

--- a/docs/sf3000-tracker.xlsx
+++ b/docs/sf3000-tracker.xlsx
@@ -2131,17 +2131,17 @@
       <c r="M18" s="12" t="n"/>
       <c r="N18" s="12" t="inlineStr">
         <is>
-          <t>Runs under the engine's procedure service: one y/N, then the upgrade, a reboot and the check. Since 2026-10-08: one upgrade per procedure and per visit (2-2.5 h lab slots, the person there); apt checked before the y/N; Timeshift installed by the engine if missing; /boot/efi left out of the snapshot (Windows' EFI partition on the lab's dual-boot machines); a step cut off by a power-off waits for the person (--run again offers the restore). Needs a snapshot: --take-snapshot (Timeshift; restored by itself if the upgrade fails, then checked) or --snapshot &lt;name&gt;. Precondition: apt works (eos-release-dead-repos healed). Written from the upgraders' source; plain do-release-upgrade would skip 23.04/23.10 and offer 24.04 directly from 22.10, which its upgrader is not built for. Timeshift 22.06.5 to 24.01.1 refuse '--tags O', so the engine passes no tags (2b09c29).</t>
+          <t>Runs under the engine's procedure service: one y/N, then the upgrade, a reboot and the check. Since 2026-10-08: one upgrade per procedure and per visit (2-2.5 h lab slots, the person there); apt checked before the y/N; Timeshift installed by the engine if missing; /boot/efi left out of the snapshot (Windows' EFI partition on the lab's dual-boot machines); a step cut off by a power-off waits for the person (--run again offers the restore). Needs a snapshot: --take-snapshot (Timeshift; restored by itself if the upgrade fails, then checked) or --snapshot &lt;name&gt;. Precondition: apt works (eos-release-dead-repos healed). Written from the upgraders' source; plain do-release-upgrade would skip 23.04/23.10 and offer 24.04 directly from 22.10, which its upgrader is not built for. Timeshift 22.06.5 to 24.01.1 refuse '--tags O', so the engine passes no tags (2b09c29). Since 2026-10-09: dpkg's lock is held around the snapshot and the restore, and the snapshot is synced to disk (74340e2).</t>
         </is>
       </c>
       <c r="O18" s="12" t="inlineStr">
         <is>
-          <t>2026-10-09 · 22.10 · the machinery passed: tests/procedure-proof Runs A-D (a reboot and its check, a time limit, Timeshift installed by the engine, its snapshot restored by itself, a power cut held for the person, the apt check's refusal). The four upgrades themselves: never run.</t>
+          <t>2026-10-10 · 22.10 · the machinery passed: tests/procedure-proof Runs A-D (a reboot and its check, a time limit, Timeshift installed by the engine, its snapshot restored by itself, a power cut held for the person, the apt check's refusal), then B and D again with the fixes (the engine waited for dpkg's lock while another program held it, then held it through the snapshot; both dead sources named). The four upgrades themselves: never run.</t>
         </is>
       </c>
       <c r="P18" s="12" t="inlineStr">
         <is>
-          <t>Re-run Runs B and D on the 22.10 VM with the fixes (dpkg's lock held around the snapshot and the restore, the snapshot synced, every dead apt source named). Then the four in order from repos-fixed with --take-snapshot, timed; then an EFI desktop VM (the restore beside a shared EFI partition).</t>
+          <t>The four in order from repos-fixed with --take-snapshot, timed; then an EFI desktop VM (the restore beside a shared EFI partition).</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -5112,7 +5112,7 @@
     <row r="45" ht="56" customHeight="1">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-09 22:03</t>
         </is>
       </c>
       <c r="B45" s="10" t="inlineStr">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
-          <t>Run D, just before 22:18: two dead sources added (a host under .invalid, a suite old-releases does not have). The apt check refused before the box; nothing was staged, and --status still showed Run C. It named only the missing suite: apt 2.5.3 prints no 'Failed to fetch' line once one source fails hard.</t>
+          <t>Run D: two dead sources added (a host under .invalid, a suite old-releases does not have). The apt check refused before the box; nothing was staged, and --status still showed Run C. It named only the missing suite: apt 2.5.3 prints no 'Failed to fetch' line once one source fails hard.</t>
         </is>
       </c>
       <c r="G45" s="10" t="inlineStr">
@@ -5146,16 +5146,165 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="120" customHeight="1">
-      <c r="A47" s="19" t="inlineStr">
-        <is>
-          <t>Times are IST (UTC+05:30). The logs themselves record UTC. Rows from 2026-09-07 23:35 to 2026-09-10 are records in evidence/ubuntu-26.04-2026-09-10.jsonl, copied off the VM on 2026-10-03; rows from 2026-10-04 are in evidence/ubuntu-26.04-2026-10-04.jsonl, rows from 2026-10-06 in evidence/ubuntu-26.04-2026-10-06.jsonl, and rows from 2026-10-07 in evidence/ubuntu-22.10-2026-10-07.jsonl and, from 12:13, evidence/ubuntu-22.10-2026-10-07-2.jsonl (the 22.10 VM, KineticServer). Rows from 2026-10-08 19:56 are the procedure runs, in evidence/ubuntu-22.10-2026-10-09.jsonl, copied from the service's own log, /var/log/sf3000/runs.jsonl. Rows whose Evidence says 'Terminal output' have no record: the engine refuses before it logs anything, or the row is a sweep, which never logs. The six rows before 2026-09-07 23:35 come from commit messages: the VM's log was reset on the evening of 2026-09-07, before anyone copied it. Add one row per run from now on, pointing at its evidence file and line.</t>
+    <row r="46" ht="56" customHeight="1">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-10 15:15</t>
+        </is>
+      </c>
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>22.10</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t>74340e2</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>procedure-proof/one</t>
+        </is>
+      </c>
+      <c r="E46" s="10" t="inlineStr">
+        <is>
+          <t>healed</t>
+        </is>
+      </c>
+      <c r="F46" s="10" t="inlineStr">
+        <is>
+          <t>Run B again, with the fixes. A second session held dpkg's lock first, and apt-get check was refused by it. The engine waited ('the package manager is busy', 15:13:29 and 15:14:29), took the lock at 15:15:29 once it was let go, and took snapshot 2026-10-10_09-45-29 (27 s, linked). During the snapshot apt-get check was refused again, naming the engine's own process (1312). Then 'writing the snapshot to disk', one, a reboot, and its check after the boot (verify_after 1).</t>
+        </is>
+      </c>
+      <c r="G46" s="10" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-22.10-2026-10-10.jsonl, line 10; the wait and both apt-get checks from the journal and the terminal (screenshot, 15:16)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="56" customHeight="1">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-10 15:16</t>
+        </is>
+      </c>
+      <c r="B47" s="10" t="inlineStr">
+        <is>
+          <t>22.10</t>
+        </is>
+      </c>
+      <c r="C47" s="10" t="inlineStr">
+        <is>
+          <t>74340e2</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t>procedure-proof/two</t>
+        </is>
+      </c>
+      <c r="E47" s="10" t="inlineStr">
+        <is>
+          <t>healed</t>
+        </is>
+      </c>
+      <c r="F47" s="10" t="inlineStr">
+        <is>
+          <t>Run B again: checked at once.</t>
+        </is>
+      </c>
+      <c r="G47" s="10" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-22.10-2026-10-10.jsonl, line 11</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="56" customHeight="1">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-10 15:16</t>
+        </is>
+      </c>
+      <c r="B48" s="10" t="inlineStr">
+        <is>
+          <t>22.10</t>
+        </is>
+      </c>
+      <c r="C48" s="10" t="inlineStr">
+        <is>
+          <t>74340e2</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>procedure-proof/three</t>
+        </is>
+      </c>
+      <c r="E48" s="10" t="inlineStr">
+        <is>
+          <t>rolled_back</t>
+        </is>
+      </c>
+      <c r="F48" s="10" t="inlineStr">
+        <is>
+          <t>Run B again: three was stopped at its limit, and the engine restored the snapshot at once; nothing held the lock then. Timeshift deleted markers one and two, reinstalled GRUB and rebooted; its log ends cleanly this time. The fingerprint matched: 'ok: back to 22.10 packages:ec3d46dddee73727'.</t>
+        </is>
+      </c>
+      <c r="G48" s="10" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-22.10-2026-10-10.jsonl, line 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="56" customHeight="1">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-10 15:21</t>
+        </is>
+      </c>
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>22.10</t>
+        </is>
+      </c>
+      <c r="C49" s="10" t="inlineStr">
+        <is>
+          <t>74340e2</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>procedure-proof</t>
+        </is>
+      </c>
+      <c r="E49" s="10" t="inlineStr">
+        <is>
+          <t>refused (exit 9)</t>
+        </is>
+      </c>
+      <c r="F49" s="10" t="inlineStr">
+        <is>
+          <t>Run D again, with the same two dead sources. The apt check refused before the box, and named both this time: the missing suite (E: ... does not have a Release file) and the dead host (Err:1 ... Could not resolve 'sf3000-no-such-host.invalid'). --status still showed Run B.</t>
+        </is>
+      </c>
+      <c r="G49" s="10" t="inlineStr">
+        <is>
+          <t>Terminal output, reported as expected by the person who ran it. The copied apt-check.log gives both lines through the engine's parser. The refusal writes no record by design.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50"/>
+    <row r="51" ht="120" customHeight="1">
+      <c r="A51" s="19" t="inlineStr">
+        <is>
+          <t>Times are IST (UTC+05:30). The logs themselves record UTC. Rows from 2026-09-07 23:35 to 2026-09-10 are records in evidence/ubuntu-26.04-2026-09-10.jsonl, copied off the VM on 2026-10-03; rows from 2026-10-04 are in evidence/ubuntu-26.04-2026-10-04.jsonl, rows from 2026-10-06 in evidence/ubuntu-26.04-2026-10-06.jsonl, and rows from 2026-10-07 in evidence/ubuntu-22.10-2026-10-07.jsonl and, from 12:13, evidence/ubuntu-22.10-2026-10-07-2.jsonl (the 22.10 VM, KineticServer). Rows from 2026-10-08 19:56 are the procedure runs, in evidence/ubuntu-22.10-2026-10-09.jsonl, copied from the service's own log, /var/log/sf3000/runs.jsonl. Rows from 2026-10-10 are lines 10 to 12 of evidence/ubuntu-22.10-2026-10-10.jsonl, whose first nine lines are the 2026-10-09 file again. Rows whose Evidence says 'Terminal output' have no record: the engine refuses before it logs anything, or the row is a sweep, which never logs. The six rows before 2026-09-07 23:35 come from commit messages: the VM's log was reset on the evening of 2026-09-07, before anyone copied it. Add one row per run from now on, pointing at its evidence file and line.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A47:G47"/>
+    <mergeCell ref="A51:G51"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/sf3000-tracker.xlsx
+++ b/docs/sf3000-tracker.xlsx
@@ -2131,7 +2131,7 @@
       <c r="M18" s="12" t="n"/>
       <c r="N18" s="12" t="inlineStr">
         <is>
-          <t>Runs under the engine's procedure service: one y/N, then the upgrade, a reboot and the check. Since 2026-10-08: one upgrade per procedure and per visit (2-2.5 h lab slots, the person there); apt checked before the y/N; Timeshift installed by the engine if missing; /boot/efi left out of the snapshot (Windows' EFI partition on the lab's dual-boot machines); a step cut off by a power-off waits for the person (--run again offers the restore). Needs a snapshot: --take-snapshot (Timeshift; restored by itself if the upgrade fails, then checked) or --snapshot &lt;name&gt;. Precondition: apt works (eos-release-dead-repos healed). Written from the upgraders' source; plain do-release-upgrade would skip 23.04/23.10 and offer 24.04 directly from 22.10, which its upgrader is not built for. Timeshift 22.06.5 to 24.01.1 refuse '--tags O', so the engine passes no tags (2b09c29). Since 2026-10-09: dpkg's lock is held around the snapshot and the restore, and the snapshot is synced to disk (74340e2).</t>
+          <t>Runs under the engine's procedure service: one y/N, then the upgrade, a reboot and the check. Since 2026-10-08: one upgrade per procedure and per visit (2-2.5 h lab slots, the person there); apt checked before the y/N; Timeshift installed by the engine if missing; /boot/efi left out of the snapshot (Windows' EFI partition on the lab's dual-boot machines); a step cut off by a power-off waits for the person (--run again offers the restore). Needs a snapshot: --take-snapshot (Timeshift; restored by itself if the upgrade fails, then checked) or --snapshot &lt;name&gt;. Precondition: apt works (eos-release-dead-repos healed). Written from the upgraders' source; plain do-release-upgrade would skip 23.04/23.10 and offer 24.04 directly from 22.10, which its upgrader is not built for. Timeshift 22.06.5 to 24.01.1 refuse '--tags O', so the engine passes no tags (2b09c29). Since 2026-10-09: dpkg's lock is held around the snapshot and the restore, and the snapshot is synced to disk (74340e2). Since 2026-10-10: /var/log/dist-upgrade is left out of the snapshot, so a failed upgrade's own logs survive the restore (main.log is the only place the non-interactive upgrader writes why it failed).</t>
         </is>
       </c>
       <c r="O18" s="12" t="inlineStr">
@@ -5294,7 +5294,6 @@
         </is>
       </c>
     </row>
-    <row r="50"/>
     <row r="51" ht="120" customHeight="1">
       <c r="A51" s="19" t="inlineStr">
         <is>

--- a/docs/sf3000-tracker.xlsx
+++ b/docs/sf3000-tracker.xlsx
@@ -2125,10 +2125,22 @@
           <t>Testing</t>
         </is>
       </c>
-      <c r="J18" s="12" t="n"/>
-      <c r="K18" s="12" t="n"/>
+      <c r="J18" s="12" t="inlineStr">
+        <is>
+          <t>Proven for release-upgrade-to-23.04 only (22.10 VM, 2026-10-10): its requires read kinetic, and its detect read 2210 before and 2304 after. -23.10, -24.04, -26.04: not yet run.</t>
+        </is>
+      </c>
+      <c r="K18" s="12" t="inlineStr">
+        <is>
+          <t>Proven for release-upgrade-to-23.04 only (22.10 VM, 2026-10-10): apt-get update; full-upgrade; the lunar upgrader from old-releases, checked with gpgv; ./lunar --mode=server --frontend=DistUpgradeViewNonInteractive. Healed in 34 min. The other three: not yet run.</t>
+        </is>
+      </c>
       <c r="L18" s="12" t="n"/>
-      <c r="M18" s="12" t="n"/>
+      <c r="M18" s="12" t="inlineStr">
+        <is>
+          <t>Ubuntu 22.10 (kinetic) → 23.04 (lunar): visit 1 only</t>
+        </is>
+      </c>
       <c r="N18" s="12" t="inlineStr">
         <is>
           <t>Runs under the engine's procedure service: one y/N, then the upgrade, a reboot and the check. Since 2026-10-08: one upgrade per procedure and per visit (2-2.5 h lab slots, the person there); apt checked before the y/N; Timeshift installed by the engine if missing; /boot/efi left out of the snapshot (Windows' EFI partition on the lab's dual-boot machines); a step cut off by a power-off waits for the person (--run again offers the restore). Needs a snapshot: --take-snapshot (Timeshift; restored by itself if the upgrade fails, then checked) or --snapshot &lt;name&gt;. Precondition: apt works (eos-release-dead-repos healed). Written from the upgraders' source; plain do-release-upgrade would skip 23.04/23.10 and offer 24.04 directly from 22.10, which its upgrader is not built for. Timeshift 22.06.5 to 24.01.1 refuse '--tags O', so the engine passes no tags (2b09c29). Since 2026-10-09: dpkg's lock is held around the snapshot and the restore, and the snapshot is synced to disk (74340e2). Since 2026-10-10: /var/log/dist-upgrade is left out of the snapshot, so a failed upgrade's own logs survive the restore (main.log is the only place the non-interactive upgrader writes why it failed).</t>
@@ -2136,12 +2148,12 @@
       </c>
       <c r="O18" s="12" t="inlineStr">
         <is>
-          <t>2026-10-10 · 22.10 · the machinery passed: tests/procedure-proof Runs A-D (a reboot and its check, a time limit, Timeshift installed by the engine, its snapshot restored by itself, a power cut held for the person, the apt check's refusal), then B and D again with the fixes (the engine waited for dpkg's lock while another program held it, then held it through the snapshot; both dead sources named). The four upgrades themselves: never run.</t>
+          <t>2026-10-10 · 22.10 → 23.04 · visit 1 healed in 34 min (from repos-fixed, automatic updates on). Before it, the machinery passed tests/procedure-proof Runs A-D, then B and D again with the lock and apt check fixes.</t>
         </is>
       </c>
       <c r="P18" s="12" t="inlineStr">
         <is>
-          <t>The four in order from repos-fixed with --take-snapshot, timed; then an EFI desktop VM (the restore beside a shared EFI partition).</t>
+          <t>Visit 2 (23.04 → 23.10) on the same VM, then visits 3 and 4. The VM's 27.9 GB root cannot hold every visit's snapshot, so delete the one before (the lab's ~820 GB free can). Then an EFI desktop VM: the restore beside a shared EFI partition, and the upgrader's ESP check.</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -5294,16 +5306,90 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="120" customHeight="1">
-      <c r="A51" s="19" t="inlineStr">
-        <is>
-          <t>Times are IST (UTC+05:30). The logs themselves record UTC. Rows from 2026-09-07 23:35 to 2026-09-10 are records in evidence/ubuntu-26.04-2026-09-10.jsonl, copied off the VM on 2026-10-03; rows from 2026-10-04 are in evidence/ubuntu-26.04-2026-10-04.jsonl, rows from 2026-10-06 in evidence/ubuntu-26.04-2026-10-06.jsonl, and rows from 2026-10-07 in evidence/ubuntu-22.10-2026-10-07.jsonl and, from 12:13, evidence/ubuntu-22.10-2026-10-07-2.jsonl (the 22.10 VM, KineticServer). Rows from 2026-10-08 19:56 are the procedure runs, in evidence/ubuntu-22.10-2026-10-09.jsonl, copied from the service's own log, /var/log/sf3000/runs.jsonl. Rows from 2026-10-10 are lines 10 to 12 of evidence/ubuntu-22.10-2026-10-10.jsonl, whose first nine lines are the 2026-10-09 file again. Rows whose Evidence says 'Terminal output' have no record: the engine refuses before it logs anything, or the row is a sweep, which never logs. The six rows before 2026-09-07 23:35 come from commit messages: the VM's log was reset on the evening of 2026-09-07, before anyone copied it. Add one row per run from now on, pointing at its evidence file and line.</t>
+    <row r="50" ht="56" customHeight="1">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:33</t>
+        </is>
+      </c>
+      <c r="B50" s="10" t="inlineStr">
+        <is>
+          <t>22.10</t>
+        </is>
+      </c>
+      <c r="C50" s="10" t="inlineStr">
+        <is>
+          <t>768cb37</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="inlineStr">
+        <is>
+          <t>release-upgrade-to-23.04/install</t>
+        </is>
+      </c>
+      <c r="E50" s="10" t="inlineStr">
+        <is>
+          <t>installed</t>
+        </is>
+      </c>
+      <c r="F50" s="10" t="inlineStr">
+        <is>
+          <t>Visit 1 of the upgrade, from repos-fixed (restored 16:26), with the automatic updates on. After the y the engine installed Timeshift with apt: 196 new and 2 upgraded, 87.6 MB in 43 s.</t>
+        </is>
+      </c>
+      <c r="G50" s="10" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-22.10-2026-10-10-2.jsonl, line 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="56" customHeight="1">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:35</t>
+        </is>
+      </c>
+      <c r="B51" s="10" t="inlineStr">
+        <is>
+          <t>22.10 → 23.04</t>
+        </is>
+      </c>
+      <c r="C51" s="10" t="inlineStr">
+        <is>
+          <t>768cb37</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="inlineStr">
+        <is>
+          <t>release-upgrade-to-23.04/to-23.04</t>
+        </is>
+      </c>
+      <c r="E51" s="10" t="inlineStr">
+        <is>
+          <t>healed</t>
+        </is>
+      </c>
+      <c r="F51" s="10" t="inlineStr">
+        <is>
+          <t>Visit 1: the first real upgrade. Snapshot 2026-10-10_11-03-25 (133 s, no lock wait). Then full-upgrade (137 upgraded, 5 new, 493 MB) and the 23.04 upgrader from old-releases (gpgv: good signature), 16:45 to 17:04. Exit 0 at the first attempt, a reboot, and the check read 2304 (23.04, dpkg --audit empty). 34 minutes from the apt check to the end of the upgrader. Its 'ERROR No valid mirror found' is the expected path: the non-interactive yes moved all ten apt lines to lunar on old-releases.</t>
+        </is>
+      </c>
+      <c r="G51" s="10" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-22.10-2026-10-10-2.jsonl, line 2; the upgrader's main.log and the step's log, copied off</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="120" customHeight="1">
+      <c r="A53" s="19" t="inlineStr">
+        <is>
+          <t>Times are IST (UTC+05:30). The logs themselves record UTC. Rows from 2026-09-07 23:35 to 2026-09-10 are records in evidence/ubuntu-26.04-2026-09-10.jsonl, copied off the VM on 2026-10-03; rows from 2026-10-04 are in evidence/ubuntu-26.04-2026-10-04.jsonl, rows from 2026-10-06 in evidence/ubuntu-26.04-2026-10-06.jsonl, and rows from 2026-10-07 in evidence/ubuntu-22.10-2026-10-07.jsonl and, from 12:13, evidence/ubuntu-22.10-2026-10-07-2.jsonl (the 22.10 VM, KineticServer). Rows from 2026-10-08 19:56 are the procedure runs, in evidence/ubuntu-22.10-2026-10-09.jsonl, copied from the service's own log, /var/log/sf3000/runs.jsonl. Rows from 2026-10-10 15:15 and 15:16 are lines 10 to 12 of evidence/ubuntu-22.10-2026-10-10.jsonl, whose first nine lines are the 2026-10-09 file again. Rows from 2026-10-10 16:33 are visit 1 of the upgrade, in evidence/ubuntu-22.10-2026-10-10-2.jsonl. Rows whose Evidence says 'Terminal output' have no record: the engine refuses before it logs anything, or the row is a sweep, which never logs. The six rows before 2026-09-07 23:35 come from commit messages: the VM's log was reset on the evening of 2026-09-07, before anyone copied it. Add one row per run from now on, pointing at its evidence file and line.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A51:G51"/>
+    <mergeCell ref="A53:G53"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/sf3000-tracker.xlsx
+++ b/docs/sf3000-tracker.xlsx
@@ -2127,18 +2127,18 @@
       </c>
       <c r="J18" s="12" t="inlineStr">
         <is>
-          <t>Proven for release-upgrade-to-23.04 only (22.10 VM, 2026-10-10): its requires read kinetic, and its detect read 2210 before and 2304 after. -23.10, -24.04, -26.04: not yet run.</t>
+          <t>Proven for release-upgrade-to-23.04 and -23.10 (22.10 VM, 2026-10-10): their requires read kinetic and lunar, and their detects read 2210 then 2304, and 2304 then 2310. -24.04, -26.04: not yet run.</t>
         </is>
       </c>
       <c r="K18" s="12" t="inlineStr">
         <is>
-          <t>Proven for release-upgrade-to-23.04 only (22.10 VM, 2026-10-10): apt-get update; full-upgrade; the lunar upgrader from old-releases, checked with gpgv; ./lunar --mode=server --frontend=DistUpgradeViewNonInteractive. Healed in 34 min. The other three: not yet run.</t>
+          <t>Proven for release-upgrade-to-23.04 and -23.10 (22.10 VM, 2026-10-10): apt-get update; full-upgrade; the next release's upgrader from old-releases, checked with gpgv; ./lunar or ./mantic --mode=server --frontend=DistUpgradeViewNonInteractive. Healed in 34 and 20 min. -24.04, -26.04: not yet run.</t>
         </is>
       </c>
       <c r="L18" s="12" t="n"/>
       <c r="M18" s="12" t="inlineStr">
         <is>
-          <t>Ubuntu 22.10 (kinetic) → 23.04 (lunar): visit 1 only</t>
+          <t>Ubuntu 22.10 (kinetic) → 23.04 (lunar) → 23.10 (mantic): visits 1 and 2</t>
         </is>
       </c>
       <c r="N18" s="12" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O18" s="12" t="inlineStr">
         <is>
-          <t>2026-10-10 · 22.10 → 23.04 · visit 1 healed in 34 min (from repos-fixed, automatic updates on). Before it, the machinery passed tests/procedure-proof Runs A-D, then B and D again with the lock and apt check fixes.</t>
+          <t>2026-10-10 · 23.04 → 23.10 · visit 2 healed in 20 min, straight after visit 1 (22.10 → 23.04, 34 min, from repos-fixed, automatic updates on). Before them, the machinery passed tests/procedure-proof Runs A-D, then B and D again with the lock and apt check fixes.</t>
         </is>
       </c>
       <c r="P18" s="12" t="inlineStr">
         <is>
-          <t>Visit 2 (23.04 → 23.10) on the same VM, then visits 3 and 4. The VM's 27.9 GB root cannot hold every visit's snapshot, so delete the one before (the lab's ~820 GB free can). Then an EFI desktop VM: the restore beside a shared EFI partition, and the upgrader's ESP check.</t>
+          <t>Visit 3 (23.10 → 24.04, do-release-upgrade) on the same VM, then visit 4. The VM's 27.9 GB root cannot hold every visit's snapshot, so delete the one before (the lab's ~820 GB free can). Then an EFI desktop VM: the restore beside a shared EFI partition, and the upgrader's ESP check.</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -5380,16 +5380,54 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="120" customHeight="1">
-      <c r="A53" s="19" t="inlineStr">
-        <is>
-          <t>Times are IST (UTC+05:30). The logs themselves record UTC. Rows from 2026-09-07 23:35 to 2026-09-10 are records in evidence/ubuntu-26.04-2026-09-10.jsonl, copied off the VM on 2026-10-03; rows from 2026-10-04 are in evidence/ubuntu-26.04-2026-10-04.jsonl, rows from 2026-10-06 in evidence/ubuntu-26.04-2026-10-06.jsonl, and rows from 2026-10-07 in evidence/ubuntu-22.10-2026-10-07.jsonl and, from 12:13, evidence/ubuntu-22.10-2026-10-07-2.jsonl (the 22.10 VM, KineticServer). Rows from 2026-10-08 19:56 are the procedure runs, in evidence/ubuntu-22.10-2026-10-09.jsonl, copied from the service's own log, /var/log/sf3000/runs.jsonl. Rows from 2026-10-10 15:15 and 15:16 are lines 10 to 12 of evidence/ubuntu-22.10-2026-10-10.jsonl, whose first nine lines are the 2026-10-09 file again. Rows from 2026-10-10 16:33 are visit 1 of the upgrade, in evidence/ubuntu-22.10-2026-10-10-2.jsonl. Rows whose Evidence says 'Terminal output' have no record: the engine refuses before it logs anything, or the row is a sweep, which never logs. The six rows before 2026-09-07 23:35 come from commit messages: the VM's log was reset on the evening of 2026-09-07, before anyone copied it. Add one row per run from now on, pointing at its evidence file and line.</t>
+    <row r="52" ht="56" customHeight="1">
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-10 18:40</t>
+        </is>
+      </c>
+      <c r="B52" s="10" t="inlineStr">
+        <is>
+          <t>23.04 → 23.10</t>
+        </is>
+      </c>
+      <c r="C52" s="10" t="inlineStr">
+        <is>
+          <t>1050e99</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="inlineStr">
+        <is>
+          <t>release-upgrade-to-23.10/to-23.10</t>
+        </is>
+      </c>
+      <c r="E52" s="10" t="inlineStr">
+        <is>
+          <t>healed</t>
+        </is>
+      </c>
+      <c r="F52" s="10" t="inlineStr">
+        <is>
+          <t>Visit 2, straight after visit 1, with no restore between. Timeshift was already there, so there is no install row. Snapshot 2026-10-10_13-08-30 (129 s, no lock wait). full-upgrade had nothing to do; the 23.10 upgrader from old-releases (gpgv: good signature) ran 18:40 to 18:57. Exit 0 at the first attempt, a reboot, and the check read 2310 (23.10, dpkg --audit empty). 20 minutes from the apt check to the end of the upgrader. The same expected 'ERROR No valid mirror found': all ten apt lines moved to mantic on old-releases.</t>
+        </is>
+      </c>
+      <c r="G52" s="10" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-22.10-2026-10-10-3.jsonl, line 3; the upgrader's main.log and the step's log, copied off</t>
+        </is>
+      </c>
+    </row>
+    <row r="53"/>
+    <row r="54" ht="120" customHeight="1">
+      <c r="A54" s="19" t="inlineStr">
+        <is>
+          <t>Times are IST (UTC+05:30). The logs themselves record UTC. Rows from 2026-09-07 23:35 to 2026-09-10 are records in evidence/ubuntu-26.04-2026-09-10.jsonl, copied off the VM on 2026-10-03; rows from 2026-10-04 are in evidence/ubuntu-26.04-2026-10-04.jsonl, rows from 2026-10-06 in evidence/ubuntu-26.04-2026-10-06.jsonl, and rows from 2026-10-07 in evidence/ubuntu-22.10-2026-10-07.jsonl and, from 12:13, evidence/ubuntu-22.10-2026-10-07-2.jsonl (the 22.10 VM, KineticServer). Rows from 2026-10-08 19:56 are the procedure runs, in evidence/ubuntu-22.10-2026-10-09.jsonl, copied from the service's own log, /var/log/sf3000/runs.jsonl. Rows from 2026-10-10 15:15 and 15:16 are lines 10 to 12 of evidence/ubuntu-22.10-2026-10-10.jsonl, whose first nine lines are the 2026-10-09 file again. Rows from 2026-10-10 16:33 are visit 1 of the upgrade, in evidence/ubuntu-22.10-2026-10-10-2.jsonl. The row from 18:40 is visit 2, line 3 of evidence/ubuntu-22.10-2026-10-10-3.jsonl, whose first two lines are visit 1's file again. Rows whose Evidence says 'Terminal output' have no record: the engine refuses before it logs anything, or the row is a sweep, which never logs. The six rows before 2026-09-07 23:35 come from commit messages: the VM's log was reset on the evening of 2026-09-07, before anyone copied it. Add one row per run from now on, pointing at its evidence file and line.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A53:G53"/>
+    <mergeCell ref="A54:G54"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/sf3000-tracker.xlsx
+++ b/docs/sf3000-tracker.xlsx
@@ -2127,18 +2127,18 @@
       </c>
       <c r="J18" s="12" t="inlineStr">
         <is>
-          <t>Proven for release-upgrade-to-23.04 and -23.10 (22.10 VM, 2026-10-10): their requires read kinetic and lunar, and their detects read 2210 then 2304, and 2304 then 2310. -24.04, -26.04: not yet run.</t>
+          <t>Proven for release-upgrade-to-23.04, -23.10 and -24.04 (22.10 VM, 2026-10-10): their requires read kinetic, lunar and mantic, and their detects read 2210 then 2304, 2304 then 2310, and 2310 then 2404. -26.04: not yet run.</t>
         </is>
       </c>
       <c r="K18" s="12" t="inlineStr">
         <is>
-          <t>Proven for release-upgrade-to-23.04 and -23.10 (22.10 VM, 2026-10-10): apt-get update; full-upgrade; the next release's upgrader from old-releases, checked with gpgv; ./lunar or ./mantic --mode=server --frontend=DistUpgradeViewNonInteractive. Healed in 34 and 20 min. -24.04, -26.04: not yet run.</t>
+          <t>Proven for release-upgrade-to-23.04, -23.10 and -24.04 (22.10 VM, 2026-10-10): apt-get update; full-upgrade; then for 23.04 and 23.10 the next release's upgrader from old-releases, checked with gpgv, run as ./lunar or ./mantic --mode=server --frontend=DistUpgradeViewNonInteractive, and for 24.04 do-release-upgrade -f DistUpgradeViewNonInteractive. Healed in 34, 20 and 27 min. -26.04: not yet run.</t>
         </is>
       </c>
       <c r="L18" s="12" t="n"/>
       <c r="M18" s="12" t="inlineStr">
         <is>
-          <t>Ubuntu 22.10 (kinetic) → 23.04 (lunar) → 23.10 (mantic): visits 1 and 2</t>
+          <t>Ubuntu 22.10 (kinetic) → 23.04 (lunar) → 23.10 (mantic) → 24.04 (noble): visits 1 to 3</t>
         </is>
       </c>
       <c r="N18" s="12" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O18" s="12" t="inlineStr">
         <is>
-          <t>2026-10-10 · 23.04 → 23.10 · visit 2 healed in 20 min, straight after visit 1 (22.10 → 23.04, 34 min, from repos-fixed, automatic updates on). Before them, the machinery passed tests/procedure-proof Runs A-D, then B and D again with the lock and apt check fixes.</t>
+          <t>2026-10-10 · 23.10 → 24.04 · visit 3 healed in 27 min, straight after visits 1 (22.10 → 23.04, 34 min, from repos-fixed, automatic updates on) and 2 (23.04 → 23.10, 20 min). apt left old-releases by itself. Before them, the machinery passed tests/procedure-proof Runs A-D, then B and D again with the lock and apt check fixes.</t>
         </is>
       </c>
       <c r="P18" s="12" t="inlineStr">
         <is>
-          <t>Visit 3 (23.10 → 24.04, do-release-upgrade) on the same VM, then visit 4. The VM's 27.9 GB root cannot hold every visit's snapshot, so delete the one before (the lab's ~820 GB free can). Then an EFI desktop VM: the restore beside a shared EFI partition, and the upgrader's ESP check.</t>
+          <t>Before visit 4: split release-upgrade-to-26.04 into updates + reboot, then do-release-upgrade (it refuses while a kernel or libc6 update waits for a reboot); a reserve file so the engine can still restore on a full disk; then make an upgrade fail on the VM (disk full: before the download, and mid-install) from a VirtualBox snapshot. Then visit 4 (24.04 → 26.04), then an EFI desktop VM.</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -5417,17 +5417,54 @@
         </is>
       </c>
     </row>
-    <row r="53"/>
-    <row r="54" ht="120" customHeight="1">
-      <c r="A54" s="19" t="inlineStr">
-        <is>
-          <t>Times are IST (UTC+05:30). The logs themselves record UTC. Rows from 2026-09-07 23:35 to 2026-09-10 are records in evidence/ubuntu-26.04-2026-09-10.jsonl, copied off the VM on 2026-10-03; rows from 2026-10-04 are in evidence/ubuntu-26.04-2026-10-04.jsonl, rows from 2026-10-06 in evidence/ubuntu-26.04-2026-10-06.jsonl, and rows from 2026-10-07 in evidence/ubuntu-22.10-2026-10-07.jsonl and, from 12:13, evidence/ubuntu-22.10-2026-10-07-2.jsonl (the 22.10 VM, KineticServer). Rows from 2026-10-08 19:56 are the procedure runs, in evidence/ubuntu-22.10-2026-10-09.jsonl, copied from the service's own log, /var/log/sf3000/runs.jsonl. Rows from 2026-10-10 15:15 and 15:16 are lines 10 to 12 of evidence/ubuntu-22.10-2026-10-10.jsonl, whose first nine lines are the 2026-10-09 file again. Rows from 2026-10-10 16:33 are visit 1 of the upgrade, in evidence/ubuntu-22.10-2026-10-10-2.jsonl. The row from 18:40 is visit 2, line 3 of evidence/ubuntu-22.10-2026-10-10-3.jsonl, whose first two lines are visit 1's file again. Rows whose Evidence says 'Terminal output' have no record: the engine refuses before it logs anything, or the row is a sweep, which never logs. The six rows before 2026-09-07 23:35 come from commit messages: the VM's log was reset on the evening of 2026-09-07, before anyone copied it. Add one row per run from now on, pointing at its evidence file and line.</t>
+    <row r="53" ht="56" customHeight="1">
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-10 20:00</t>
+        </is>
+      </c>
+      <c r="B53" s="10" t="inlineStr">
+        <is>
+          <t>23.10 → 24.04</t>
+        </is>
+      </c>
+      <c r="C53" s="10" t="inlineStr">
+        <is>
+          <t>83d21f6</t>
+        </is>
+      </c>
+      <c r="D53" s="10" t="inlineStr">
+        <is>
+          <t>release-upgrade-to-24.04/to-24.04</t>
+        </is>
+      </c>
+      <c r="E53" s="10" t="inlineStr">
+        <is>
+          <t>healed</t>
+        </is>
+      </c>
+      <c r="F53" s="10" t="inlineStr">
+        <is>
+          <t>Visit 3, straight after visit 2, with no restore between: the first upgrade through plain do-release-upgrade. Snapshot 2026-10-10_14-28-46 (124 s, no lock wait). full-upgrade had nothing to do; the 24.04 upgrader (24.04.29) ran 20:01 to 20:25 and moved all ten apt lines from old-releases to gb.archive.ubuntu.com, then to ubuntu.sources (deb822). Exit 0 at the first attempt, a reboot, and the check read 2404 (24.04, dpkg --audit empty). 27 minutes from the apt check to the end of the upgrader. No ERROR; one config-file prompt (fwupd.conf) answered 'keep yours'. It removed Python 3.11 under the running engine, which still reached its reboot.</t>
+        </is>
+      </c>
+      <c r="G53" s="10" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-22.10-2026-10-10-4.jsonl, line 4; the upgrader's main.log and the step's log, copied off</t>
+        </is>
+      </c>
+    </row>
+    <row r="54"/>
+    <row r="55" ht="135" customHeight="1">
+      <c r="A55" s="19" t="inlineStr">
+        <is>
+          <t>Times are IST (UTC+05:30). The logs themselves record UTC. Rows from 2026-09-07 23:35 to 2026-09-10 are records in evidence/ubuntu-26.04-2026-09-10.jsonl, copied off the VM on 2026-10-03; rows from 2026-10-04 are in evidence/ubuntu-26.04-2026-10-04.jsonl, rows from 2026-10-06 in evidence/ubuntu-26.04-2026-10-06.jsonl, and rows from 2026-10-07 in evidence/ubuntu-22.10-2026-10-07.jsonl and, from 12:13, evidence/ubuntu-22.10-2026-10-07-2.jsonl (the 22.10 VM, KineticServer). Rows from 2026-10-08 19:56 are the procedure runs, in evidence/ubuntu-22.10-2026-10-09.jsonl, copied from the service's own log, /var/log/sf3000/runs.jsonl. Rows from 2026-10-10 15:15 and 15:16 are lines 10 to 12 of evidence/ubuntu-22.10-2026-10-10.jsonl, whose first nine lines are the 2026-10-09 file again. Rows from 2026-10-10 16:33 are visit 1 of the upgrade, in evidence/ubuntu-22.10-2026-10-10-2.jsonl. The row from 18:40 is visit 2, line 3 of evidence/ubuntu-22.10-2026-10-10-3.jsonl, whose first two lines are visit 1's file again. The row from 20:00 is visit 3, line 4 of evidence/ubuntu-22.10-2026-10-10-4.jsonl, whose first three lines are visit 2's file again. Rows whose Evidence says 'Terminal output' have no record: the engine refuses before it logs anything, or the row is a sweep, which never logs. The six rows before 2026-09-07 23:35 come from commit messages: the VM's log was reset on the evening of 2026-09-07, before anyone copied it. Add one row per run from now on, pointing at its evidence file and line.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A54:G54"/>
+    <mergeCell ref="A55:G55"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/sf3000-tracker.xlsx
+++ b/docs/sf3000-tracker.xlsx
@@ -2143,7 +2143,7 @@
       </c>
       <c r="N18" s="12" t="inlineStr">
         <is>
-          <t>Runs under the engine's procedure service: one y/N, then the upgrade, a reboot and the check. Since 2026-10-08: one upgrade per procedure and per visit (2-2.5 h lab slots, the person there); apt checked before the y/N; Timeshift installed by the engine if missing; /boot/efi left out of the snapshot (Windows' EFI partition on the lab's dual-boot machines); a step cut off by a power-off waits for the person (--run again offers the restore). Needs a snapshot: --take-snapshot (Timeshift; restored by itself if the upgrade fails, then checked) or --snapshot &lt;name&gt;. Precondition: apt works (eos-release-dead-repos healed). Written from the upgraders' source; plain do-release-upgrade would skip 23.04/23.10 and offer 24.04 directly from 22.10, which its upgrader is not built for. Timeshift 22.06.5 to 24.01.1 refuse '--tags O', so the engine passes no tags (2b09c29). Since 2026-10-09: dpkg's lock is held around the snapshot and the restore, and the snapshot is synced to disk (74340e2). Since 2026-10-10: /var/log/dist-upgrade is left out of the snapshot, so a failed upgrade's own logs survive the restore (main.log is the only place the non-interactive upgrader writes why it failed).</t>
+          <t>Runs under the engine's procedure service: one y/N, then the upgrade, a reboot and the check. Since 2026-10-08: one upgrade per procedure and per visit (2-2.5 h lab slots, the person there); apt checked before the y/N; Timeshift installed by the engine if missing; /boot/efi left out of the snapshot (Windows' EFI partition on the lab's dual-boot machines); a step cut off by a power-off waits for the person (--run again offers the restore). Needs a snapshot: --take-snapshot (Timeshift; restored by itself if the upgrade fails, then checked) or --snapshot &lt;name&gt;. Precondition: apt works (eos-release-dead-repos healed). Written from the upgraders' source; plain do-release-upgrade would skip 23.04/23.10 and offer 24.04 directly from 22.10, which its upgrader is not built for. Timeshift 22.06.5 to 24.01.1 refuse '--tags O', so the engine passes no tags (2b09c29). Since 2026-10-09: dpkg's lock is held around the snapshot and the restore, and the snapshot is synced to disk (74340e2). Since 2026-10-10: /var/log/dist-upgrade is left out of the snapshot, so a failed upgrade's own logs survive the restore (main.log is the only place the non-interactive upgrader writes why it failed). Also since 2026-10-10 (offline only): the engine keeps 256 MB set aside while a procedure runs and frees it first when a step fails, so a full disk cannot stop the restore; and -26.04 is two steps, updates + reboot, then do-release-upgrade, which refuses while a kernel or libc6 update waits for a reboot.</t>
         </is>
       </c>
       <c r="O18" s="12" t="inlineStr">
@@ -2153,7 +2153,7 @@
       </c>
       <c r="P18" s="12" t="inlineStr">
         <is>
-          <t>Before visit 4: split release-upgrade-to-26.04 into updates + reboot, then do-release-upgrade (it refuses while a kernel or libc6 update waits for a reboot); a reserve file so the engine can still restore on a full disk; then make an upgrade fail on the VM (disk full: before the download, and mid-install) from a VirtualBox snapshot. Then visit 4 (24.04 → 26.04), then an EFI desktop VM.</t>
+          <t>Runs E and F in tests/procedure-proof (offline: built and passing): make the 26.04 upgrade fail on the VM from a VirtualBox snapshot at 24.04, first at the upgrader's space check, then with the disk full mid-install. Both should end rolled_back. Then visit 4 (24.04 → 26.04, two steps), then an EFI desktop VM.</t>
         </is>
       </c>
     </row>
@@ -5454,7 +5454,6 @@
         </is>
       </c>
     </row>
-    <row r="54"/>
     <row r="55" ht="135" customHeight="1">
       <c r="A55" s="19" t="inlineStr">
         <is>

--- a/docs/sf3000-tracker.xlsx
+++ b/docs/sf3000-tracker.xlsx
@@ -2127,33 +2127,33 @@
       </c>
       <c r="J18" s="12" t="inlineStr">
         <is>
-          <t>Proven for release-upgrade-to-23.04, -23.10 and -24.04 (22.10 VM, 2026-10-10): their requires read kinetic, lunar and mantic, and their detects read 2210 then 2304, 2304 then 2310, and 2310 then 2404. -26.04: not yet run.</t>
+          <t>Proven for release-upgrade-to-23.04, -23.10 and -24.04 (22.10 VM, 2026-10-10): their requires read kinetic, lunar and mantic, and their detects read 2210 then 2304, 2304 then 2310, and 2310 then 2404. -26.04 ran twice, made to fail (Runs E and F, 2026-10-10): its requires read noble; step 1's check (apt-get -s full-upgrade, plus a waiting reboot) read 0 both times, so step 1 was skipped; step 2's detect read 2404 before. Not yet healed.</t>
         </is>
       </c>
       <c r="K18" s="12" t="inlineStr">
         <is>
-          <t>Proven for release-upgrade-to-23.04, -23.10 and -24.04 (22.10 VM, 2026-10-10): apt-get update; full-upgrade; then for 23.04 and 23.10 the next release's upgrader from old-releases, checked with gpgv, run as ./lunar or ./mantic --mode=server --frontend=DistUpgradeViewNonInteractive, and for 24.04 do-release-upgrade -f DistUpgradeViewNonInteractive. Healed in 34, 20 and 27 min. -26.04: not yet run.</t>
+          <t>Proven for release-upgrade-to-23.04, -23.10 and -24.04 (22.10 VM, 2026-10-10): apt-get update; full-upgrade; then for 23.04 and 23.10 the next release's upgrader from old-releases, checked with gpgv, run as ./lunar or ./mantic --mode=server --frontend=DistUpgradeViewNonInteractive, and for 24.04 do-release-upgrade -f DistUpgradeViewNonInteractive. Healed in 34, 20 and 27 min. -26.04's do-release-upgrade -f DistUpgradeViewNonInteractive ran twice, made to fail (Runs E and F); the engine restored 24.04 both times. Not yet healed.</t>
         </is>
       </c>
       <c r="L18" s="12" t="n"/>
       <c r="M18" s="12" t="inlineStr">
         <is>
-          <t>Ubuntu 22.10 (kinetic) → 23.04 (lunar) → 23.10 (mantic) → 24.04 (noble): visits 1 to 3</t>
+          <t>Ubuntu 22.10 (kinetic) → 23.04 (lunar) → 23.10 (mantic) → 24.04 (noble): visits 1 to 3; 24.04 → 26.04 (resolute) made to fail twice: Runs E and F</t>
         </is>
       </c>
       <c r="N18" s="12" t="inlineStr">
         <is>
-          <t>Runs under the engine's procedure service: one y/N, then the upgrade, a reboot and the check. Since 2026-10-08: one upgrade per procedure and per visit (2-2.5 h lab slots, the person there); apt checked before the y/N; Timeshift installed by the engine if missing; /boot/efi left out of the snapshot (Windows' EFI partition on the lab's dual-boot machines); a step cut off by a power-off waits for the person (--run again offers the restore). Needs a snapshot: --take-snapshot (Timeshift; restored by itself if the upgrade fails, then checked) or --snapshot &lt;name&gt;. Precondition: apt works (eos-release-dead-repos healed). Written from the upgraders' source; plain do-release-upgrade would skip 23.04/23.10 and offer 24.04 directly from 22.10, which its upgrader is not built for. Timeshift 22.06.5 to 24.01.1 refuse '--tags O', so the engine passes no tags (2b09c29). Since 2026-10-09: dpkg's lock is held around the snapshot and the restore, and the snapshot is synced to disk (74340e2). Since 2026-10-10: /var/log/dist-upgrade is left out of the snapshot, so a failed upgrade's own logs survive the restore (main.log is the only place the non-interactive upgrader writes why it failed). Also since 2026-10-10 (offline only): the engine keeps 256 MB set aside while a procedure runs and frees it first when a step fails, so a full disk cannot stop the restore; and -26.04 is two steps, updates + reboot, then do-release-upgrade, which refuses while a kernel or libc6 update waits for a reboot.</t>
+          <t>Runs under the engine's procedure service: one y/N, then the upgrade, a reboot and the check. Since 2026-10-08: one upgrade per procedure and per visit (2-2.5 h lab slots, the person there); apt checked before the y/N; Timeshift installed by the engine if missing; /boot/efi left out of the snapshot (Windows' EFI partition on the lab's dual-boot machines); a step cut off by a power-off waits for the person (--run again offers the restore). Needs a snapshot: --take-snapshot (Timeshift; restored by itself if the upgrade fails, then checked) or --snapshot &lt;name&gt;. Precondition: apt works (eos-release-dead-repos healed). Written from the upgraders' source; plain do-release-upgrade would skip 23.04/23.10 and offer 24.04 directly from 22.10, which its upgrader is not built for. Timeshift 22.06.5 to 24.01.1 refuse '--tags O', so the engine passes no tags (2b09c29). Since 2026-10-09: dpkg's lock is held around the snapshot and the restore, and the snapshot is synced to disk (74340e2). Since 2026-10-10: /var/log/dist-upgrade is left out of the snapshot, so a failed upgrade's own logs survive the restore (main.log is the only place the non-interactive upgrader writes why it failed). Also since 2026-10-10: the engine keeps 256 MB set aside while a procedure runs and frees it first when a step fails, so a full disk cannot stop the restore (seen in Run F); and -26.04 is two steps, updates + reboot, then do-release-upgrade, which refuses while a kernel or libc6 update waits for a reboot. Run F found: the upgrader can exit while a dpkg it started still runs, and the engine, which waits only for dpkg's frontend lock, then starts the restore with that dpkg running. Open: DESIGN §15.</t>
         </is>
       </c>
       <c r="O18" s="12" t="inlineStr">
         <is>
-          <t>2026-10-10 · 23.10 → 24.04 · visit 3 healed in 27 min, straight after visits 1 (22.10 → 23.04, 34 min, from repos-fixed, automatic updates on) and 2 (23.04 → 23.10, 20 min). apt left old-releases by itself. Before them, the machinery passed tests/procedure-proof Runs A-D, then B and D again with the lock and apt check fixes.</t>
+          <t>2026-10-10 · 24.04 → 26.04 · Runs E and F made the upgrade fail with a filled disk: first at the upgrader's space check, then mid-install. Both rolled_back to 24.04, the second on a full disk, from a half-upgraded machine. Before them, visits 1 to 3 healed (34, 20 and 27 min, one after the other, from repos-fixed, automatic updates on), after the machinery passed tests/procedure-proof Runs A-D.</t>
         </is>
       </c>
       <c r="P18" s="12" t="inlineStr">
         <is>
-          <t>Runs E and F in tests/procedure-proof (offline: built and passing): make the 26.04 upgrade fail on the VM from a VirtualBox snapshot at 24.04, first at the upgrader's space check, then with the disk full mid-install. Both should end rolled_back. Then visit 4 (24.04 → 26.04, two steps), then an EFI desktop VM.</t>
+          <t>Decide DESIGN §15's question: before a restore, stop what a failed step left running, and wait for dpkg's inner lock too. Then visit 4 (24.04 → 26.04, two steps) on the VM as Run F left it, then an EFI desktop VM.</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -5454,16 +5454,90 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="135" customHeight="1">
-      <c r="A55" s="19" t="inlineStr">
-        <is>
-          <t>Times are IST (UTC+05:30). The logs themselves record UTC. Rows from 2026-09-07 23:35 to 2026-09-10 are records in evidence/ubuntu-26.04-2026-09-10.jsonl, copied off the VM on 2026-10-03; rows from 2026-10-04 are in evidence/ubuntu-26.04-2026-10-04.jsonl, rows from 2026-10-06 in evidence/ubuntu-26.04-2026-10-06.jsonl, and rows from 2026-10-07 in evidence/ubuntu-22.10-2026-10-07.jsonl and, from 12:13, evidence/ubuntu-22.10-2026-10-07-2.jsonl (the 22.10 VM, KineticServer). Rows from 2026-10-08 19:56 are the procedure runs, in evidence/ubuntu-22.10-2026-10-09.jsonl, copied from the service's own log, /var/log/sf3000/runs.jsonl. Rows from 2026-10-10 15:15 and 15:16 are lines 10 to 12 of evidence/ubuntu-22.10-2026-10-10.jsonl, whose first nine lines are the 2026-10-09 file again. Rows from 2026-10-10 16:33 are visit 1 of the upgrade, in evidence/ubuntu-22.10-2026-10-10-2.jsonl. The row from 18:40 is visit 2, line 3 of evidence/ubuntu-22.10-2026-10-10-3.jsonl, whose first two lines are visit 1's file again. The row from 20:00 is visit 3, line 4 of evidence/ubuntu-22.10-2026-10-10-4.jsonl, whose first three lines are visit 2's file again. Rows whose Evidence says 'Terminal output' have no record: the engine refuses before it logs anything, or the row is a sweep, which never logs. The six rows before 2026-09-07 23:35 come from commit messages: the VM's log was reset on the evening of 2026-09-07, before anyone copied it. Add one row per run from now on, pointing at its evidence file and line.</t>
+    <row r="54" ht="56" customHeight="1">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-10 23:26</t>
+        </is>
+      </c>
+      <c r="B54" s="10" t="inlineStr">
+        <is>
+          <t>24.04 → 26.04</t>
+        </is>
+      </c>
+      <c r="C54" s="10" t="inlineStr">
+        <is>
+          <t>584199a</t>
+        </is>
+      </c>
+      <c r="D54" s="10" t="inlineStr">
+        <is>
+          <t>release-upgrade-to-26.04/to-26.04</t>
+        </is>
+      </c>
+      <c r="E54" s="10" t="inlineStr">
+        <is>
+          <t>rolled_back</t>
+        </is>
+      </c>
+      <c r="F54" s="10" t="inlineStr">
+        <is>
+          <t>Run E of tests/procedure-proof: the last upgrade made to fail on purpose. fill-disk.py left 500 MB free for ordinary users once step 2 began. Step 1 (updates) found nothing waiting and was skipped. Snapshot 2026-10-10_17-53-28 (186 s, a full copy). The 26.04 upgrader (26.04.25) found 365 MB free on / and needed 2,734 MB: 'Not enough free disk space'. It put the apt sources back and exited 1, before any download. failure fix_failed; the engine restored the snapshot (158 MB sent) and rebooted, and the check matched: 'ok: back to 24.04 packages:d778793cbf7390c2'. 5 minutes from the apt check to the restore. The upgrader's main.log survived the restore.</t>
+        </is>
+      </c>
+      <c r="G54" s="10" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-22.10-2026-10-10-5.jsonl, line 5; the upgrader's main.log (folder 20261010-1812), the step's log and restore.log, copied off</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="56" customHeight="1">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-10 23:42</t>
+        </is>
+      </c>
+      <c r="B55" s="10" t="inlineStr">
+        <is>
+          <t>24.04 → 26.04</t>
+        </is>
+      </c>
+      <c r="C55" s="10" t="inlineStr">
+        <is>
+          <t>584199a</t>
+        </is>
+      </c>
+      <c r="D55" s="10" t="inlineStr">
+        <is>
+          <t>release-upgrade-to-26.04/to-26.04</t>
+        </is>
+      </c>
+      <c r="E55" s="10" t="inlineStr">
+        <is>
+          <t>rolled_back</t>
+        </is>
+      </c>
+      <c r="F55" s="10" t="inlineStr">
+        <is>
+          <t>Run F of tests/procedure-proof: fill-disk.py filled the disk, root's share too, a minute into dpkg's install. Step 1 skipped again. Snapshot 2026-10-10_18-11-25 (41 s, linked to Run E's). The upgrader downloaded 1.4 GB in 12 min. dpkg unpacked 140 packages, 26.04's libc6 among them, then failed 31 in a row: 'No space left on device'. The upgrader exited 1; failure fix_failed. The engine freed its 256 MB reserve on the full disk and restored a half-upgraded machine (4,260 deletions, about 7,000 files rewritten). The check matched: 'ok: back to 24.04 packages:d778793cbf7390c2'. Found: the upgrader exited while a dpkg it started ran on. That dpkg ended a second into the restore, and 9 s into it the upgrader's install process retried, stopped by the engine's hold on dpkg's frontend lock (DESIGN §15).</t>
+        </is>
+      </c>
+      <c r="G55" s="10" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-22.10-2026-10-10-5.jsonl, line 6; the upgrader's main.log and apt-term.log, the step's log and restore.log, copied off</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="150" customHeight="1">
+      <c r="A57" s="19" t="inlineStr">
+        <is>
+          <t>Times are IST (UTC+05:30). The logs themselves record UTC. Rows from 2026-09-07 23:35 to 2026-09-10 are records in evidence/ubuntu-26.04-2026-09-10.jsonl, copied off the VM on 2026-10-03; rows from 2026-10-04 are in evidence/ubuntu-26.04-2026-10-04.jsonl, rows from 2026-10-06 in evidence/ubuntu-26.04-2026-10-06.jsonl, and rows from 2026-10-07 in evidence/ubuntu-22.10-2026-10-07.jsonl and, from 12:13, evidence/ubuntu-22.10-2026-10-07-2.jsonl (the 22.10 VM, KineticServer). Rows from 2026-10-08 19:56 are the procedure runs, in evidence/ubuntu-22.10-2026-10-09.jsonl, copied from the service's own log, /var/log/sf3000/runs.jsonl. Rows from 2026-10-10 15:15 and 15:16 are lines 10 to 12 of evidence/ubuntu-22.10-2026-10-10.jsonl, whose first nine lines are the 2026-10-09 file again. Rows from 2026-10-10 16:33 are visit 1 of the upgrade, in evidence/ubuntu-22.10-2026-10-10-2.jsonl. The row from 18:40 is visit 2, line 3 of evidence/ubuntu-22.10-2026-10-10-3.jsonl, whose first two lines are visit 1's file again. The row from 20:00 is visit 3, line 4 of evidence/ubuntu-22.10-2026-10-10-4.jsonl, whose first three lines are visit 2's file again. The rows from 23:26 and 23:42 are Runs E and F, lines 5 and 6 of evidence/ubuntu-22.10-2026-10-10-5.jsonl, whose first four lines are visit 3's file again. Rows whose Evidence says 'Terminal output' have no record: the engine refuses before it logs anything, or the row is a sweep, which never logs. The six rows before 2026-09-07 23:35 come from commit messages: the VM's log was reset on the evening of 2026-09-07, before anyone copied it. Add one row per run from now on, pointing at its evidence file and line.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A55:G55"/>
+    <mergeCell ref="A57:G57"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/sf3000-tracker.xlsx
+++ b/docs/sf3000-tracker.xlsx
@@ -2143,7 +2143,7 @@
       </c>
       <c r="N18" s="12" t="inlineStr">
         <is>
-          <t>Runs under the engine's procedure service: one y/N, then the upgrade, a reboot and the check. Since 2026-10-08: one upgrade per procedure and per visit (2-2.5 h lab slots, the person there); apt checked before the y/N; Timeshift installed by the engine if missing; /boot/efi left out of the snapshot (Windows' EFI partition on the lab's dual-boot machines); a step cut off by a power-off waits for the person (--run again offers the restore). Needs a snapshot: --take-snapshot (Timeshift; restored by itself if the upgrade fails, then checked) or --snapshot &lt;name&gt;. Precondition: apt works (eos-release-dead-repos healed). Written from the upgraders' source; plain do-release-upgrade would skip 23.04/23.10 and offer 24.04 directly from 22.10, which its upgrader is not built for. Timeshift 22.06.5 to 24.01.1 refuse '--tags O', so the engine passes no tags (2b09c29). Since 2026-10-09: dpkg's lock is held around the snapshot and the restore, and the snapshot is synced to disk (74340e2). Since 2026-10-10: /var/log/dist-upgrade is left out of the snapshot, so a failed upgrade's own logs survive the restore (main.log is the only place the non-interactive upgrader writes why it failed). Also since 2026-10-10: the engine keeps 256 MB set aside while a procedure runs and frees it first when a step fails, so a full disk cannot stop the restore (seen in Run F); and -26.04 is two steps, updates + reboot, then do-release-upgrade, which refuses while a kernel or libc6 update waits for a reboot. Run F found: the upgrader can exit while a dpkg it started still runs, and the engine, which waits only for dpkg's frontend lock, then starts the restore with that dpkg running. Open: DESIGN §15.</t>
+          <t>Runs under the engine's procedure service: one y/N, then the upgrade, a reboot and the check. Since 2026-10-08: one upgrade per procedure and per visit (2-2.5 h lab slots, the person there); apt checked before the y/N; Timeshift installed by the engine if missing; /boot/efi left out of the snapshot (Windows' EFI partition on the lab's dual-boot machines); a step cut off by a power-off waits for the person (--run again offers the restore). Needs a snapshot: --take-snapshot (Timeshift; restored by itself if the upgrade fails, then checked) or --snapshot &lt;name&gt;. Precondition: apt works (eos-release-dead-repos healed). Written from the upgraders' source; plain do-release-upgrade would skip 23.04/23.10 and offer 24.04 directly from 22.10, which its upgrader is not built for. Timeshift 22.06.5 to 24.01.1 refuse '--tags O', so the engine passes no tags (2b09c29). Since 2026-10-09: dpkg's lock is held around the snapshot and the restore, and the snapshot is synced to disk (74340e2). Since 2026-10-10: /var/log/dist-upgrade is left out of the snapshot, so a failed upgrade's own logs survive the restore (main.log is the only place the non-interactive upgrader writes why it failed). Also since 2026-10-10: the engine keeps 256 MB set aside while a procedure runs and frees it first when a step fails, so a full disk cannot stop the restore (seen in Run F); and -26.04 is two steps, updates + reboot, then do-release-upgrade, which refuses while a kernel or libc6 update waits for a reboot. Run F found: the upgrader can exit while a dpkg it started still runs, and the engine, which then waited only for dpkg's frontend lock, started the restore with that dpkg running. Since 2026-10-11 (offline only): before a restore the engine kills every other process in its service's cgroup (named in the record, leftovers_stopped), and it holds dpkg's own lock as well as the frontend's.</t>
         </is>
       </c>
       <c r="O18" s="12" t="inlineStr">
@@ -2153,7 +2153,7 @@
       </c>
       <c r="P18" s="12" t="inlineStr">
         <is>
-          <t>Decide DESIGN §15's question: before a restore, stop what a failed step left running, and wait for dpkg's inner lock too. Then visit 4 (24.04 → 26.04, two steps) on the VM as Run F left it, then an EFI desktop VM.</t>
+          <t>Run G in tests/procedure-proof (offline: built and passing): a fixture step leaves a process holding dpkg's own lock, then fails; the engine must stop it before the restore. Also a wait for dpkg's own lock before the snapshot. Then visit 4 (24.04 → 26.04, two steps) on the VM as Run F left it, then an EFI desktop VM.</t>
         </is>
       </c>
     </row>

--- a/docs/sf3000-tracker.xlsx
+++ b/docs/sf3000-tracker.xlsx
@@ -2143,17 +2143,17 @@
       </c>
       <c r="N18" s="12" t="inlineStr">
         <is>
-          <t>Runs under the engine's procedure service: one y/N, then the upgrade, a reboot and the check. Since 2026-10-08: one upgrade per procedure and per visit (2-2.5 h lab slots, the person there); apt checked before the y/N; Timeshift installed by the engine if missing; /boot/efi left out of the snapshot (Windows' EFI partition on the lab's dual-boot machines); a step cut off by a power-off waits for the person (--run again offers the restore). Needs a snapshot: --take-snapshot (Timeshift; restored by itself if the upgrade fails, then checked) or --snapshot &lt;name&gt;. Precondition: apt works (eos-release-dead-repos healed). Written from the upgraders' source; plain do-release-upgrade would skip 23.04/23.10 and offer 24.04 directly from 22.10, which its upgrader is not built for. Timeshift 22.06.5 to 24.01.1 refuse '--tags O', so the engine passes no tags (2b09c29). Since 2026-10-09: dpkg's lock is held around the snapshot and the restore, and the snapshot is synced to disk (74340e2). Since 2026-10-10: /var/log/dist-upgrade is left out of the snapshot, so a failed upgrade's own logs survive the restore (main.log is the only place the non-interactive upgrader writes why it failed). Also since 2026-10-10: the engine keeps 256 MB set aside while a procedure runs and frees it first when a step fails, so a full disk cannot stop the restore (seen in Run F); and -26.04 is two steps, updates + reboot, then do-release-upgrade, which refuses while a kernel or libc6 update waits for a reboot. Run F found: the upgrader can exit while a dpkg it started still runs, and the engine, which then waited only for dpkg's frontend lock, started the restore with that dpkg running. Since 2026-10-11 (offline only): before a restore the engine kills every other process in its service's cgroup (named in the record, leftovers_stopped), and it holds dpkg's own lock as well as the frontend's.</t>
+          <t>Runs under the engine's procedure service: one y/N, then the upgrade, a reboot and the check. Since 2026-10-08: one upgrade per procedure and per visit (2-2.5 h lab slots, the person there); apt checked before the y/N; Timeshift installed by the engine if missing; /boot/efi left out of the snapshot (Windows' EFI partition on the lab's dual-boot machines); a step cut off by a power-off waits for the person (--run again offers the restore). Needs a snapshot: --take-snapshot (Timeshift; restored by itself if the upgrade fails, then checked) or --snapshot &lt;name&gt;. Precondition: apt works (eos-release-dead-repos healed). Written from the upgraders' source; plain do-release-upgrade would skip 23.04/23.10 and offer 24.04 directly from 22.10, which its upgrader is not built for. Timeshift 22.06.5 to 24.01.1 refuse '--tags O', so the engine passes no tags (2b09c29). Since 2026-10-09: dpkg's lock is held around the snapshot and the restore, and the snapshot is synced to disk (74340e2). Since 2026-10-10: /var/log/dist-upgrade is left out of the snapshot, so a failed upgrade's own logs survive the restore (main.log is the only place the non-interactive upgrader writes why it failed). Also since 2026-10-10: the engine keeps 256 MB set aside while a procedure runs and frees it first when a step fails, so a full disk cannot stop the restore (seen in Run F); and -26.04 is two steps, updates + reboot, then do-release-upgrade, which refuses while a kernel or libc6 update waits for a reboot. Run F found: the upgrader can exit while a dpkg it started still runs, and the engine, which then waited only for dpkg's frontend lock, started the restore with that dpkg running. Since 2026-10-11 (seen in Run G): before a restore the engine kills every other process in its service's cgroup (named in the record, leftovers_stopped), and it holds dpkg's own lock as well as the frontend's.</t>
         </is>
       </c>
       <c r="O18" s="12" t="inlineStr">
         <is>
-          <t>2026-10-10 · 24.04 → 26.04 · Runs E and F made the upgrade fail with a filled disk: first at the upgrader's space check, then mid-install. Both rolled_back to 24.04, the second on a full disk, from a half-upgraded machine. Before them, visits 1 to 3 healed (34, 20 and 27 min, one after the other, from repos-fixed, automatic updates on), after the machinery passed tests/procedure-proof Runs A-D.</t>
+          <t>2026-10-11 · 24.04 · Run G (a test procedure): a failed step's leftover, holding dpkg's own lock, was stopped before the restore and named in the record; the engine waited for dpkg's own lock before its snapshot; rolled_back. Before it: 2026-10-10 · 24.04 → 26.04 · Runs E and F made the upgrade fail with a filled disk: first at the upgrader's space check, then mid-install. Both rolled_back to 24.04, the second on a full disk, from a half-upgraded machine. Before them, visits 1 to 3 healed (34, 20 and 27 min, one after the other, from repos-fixed, automatic updates on), after the machinery passed tests/procedure-proof Runs A-D.</t>
         </is>
       </c>
       <c r="P18" s="12" t="inlineStr">
         <is>
-          <t>Run G in tests/procedure-proof (offline: built and passing): a fixture step leaves a process holding dpkg's own lock, then fails; the engine must stop it before the restore. Also a wait for dpkg's own lock before the snapshot. Then visit 4 (24.04 → 26.04, two steps) on the VM as Run F left it, then an EFI desktop VM.</t>
+          <t>Visit 4 (24.04 → 26.04, two steps) on the VM as Run G left it. Then an EFI desktop VM.</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -5528,16 +5528,54 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="150" customHeight="1">
-      <c r="A57" s="19" t="inlineStr">
-        <is>
-          <t>Times are IST (UTC+05:30). The logs themselves record UTC. Rows from 2026-09-07 23:35 to 2026-09-10 are records in evidence/ubuntu-26.04-2026-09-10.jsonl, copied off the VM on 2026-10-03; rows from 2026-10-04 are in evidence/ubuntu-26.04-2026-10-04.jsonl, rows from 2026-10-06 in evidence/ubuntu-26.04-2026-10-06.jsonl, and rows from 2026-10-07 in evidence/ubuntu-22.10-2026-10-07.jsonl and, from 12:13, evidence/ubuntu-22.10-2026-10-07-2.jsonl (the 22.10 VM, KineticServer). Rows from 2026-10-08 19:56 are the procedure runs, in evidence/ubuntu-22.10-2026-10-09.jsonl, copied from the service's own log, /var/log/sf3000/runs.jsonl. Rows from 2026-10-10 15:15 and 15:16 are lines 10 to 12 of evidence/ubuntu-22.10-2026-10-10.jsonl, whose first nine lines are the 2026-10-09 file again. Rows from 2026-10-10 16:33 are visit 1 of the upgrade, in evidence/ubuntu-22.10-2026-10-10-2.jsonl. The row from 18:40 is visit 2, line 3 of evidence/ubuntu-22.10-2026-10-10-3.jsonl, whose first two lines are visit 1's file again. The row from 20:00 is visit 3, line 4 of evidence/ubuntu-22.10-2026-10-10-4.jsonl, whose first three lines are visit 2's file again. The rows from 23:26 and 23:42 are Runs E and F, lines 5 and 6 of evidence/ubuntu-22.10-2026-10-10-5.jsonl, whose first four lines are visit 3's file again. Rows whose Evidence says 'Terminal output' have no record: the engine refuses before it logs anything, or the row is a sweep, which never logs. The six rows before 2026-09-07 23:35 come from commit messages: the VM's log was reset on the evening of 2026-09-07, before anyone copied it. Add one row per run from now on, pointing at its evidence file and line.</t>
+    <row r="56" ht="56" customHeight="1">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-11 01:13</t>
+        </is>
+      </c>
+      <c r="B56" s="10" t="inlineStr">
+        <is>
+          <t>24.04</t>
+        </is>
+      </c>
+      <c r="C56" s="10" t="inlineStr">
+        <is>
+          <t>40564b9</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="inlineStr">
+        <is>
+          <t>leftover-proof/leave</t>
+        </is>
+      </c>
+      <c r="E56" s="10" t="inlineStr">
+        <is>
+          <t>rolled_back</t>
+        </is>
+      </c>
+      <c r="F56" s="10" t="inlineStr">
+        <is>
+          <t>Run G of tests/procedure-proof, the check of the fix for what Run F found. A second session held dpkg's own lock before the --run; the snapshot (2026-10-10_19-40-44, 158 s, a full copy) began after it let go, 2 min 25 s after the apt check. The fixture's step left a process in a session of its own holding dpkg's own lock, then exited 1. failure fix_failed; the engine stopped that process first (leftovers_stopped: ['2040 python3']), freed its reserve and restored, about 0.2 s after the step ended, with no wait for the lock. After the reboot the check matched: 'ok: back to 24.04 packages:d778793cbf7390c2'.</t>
+        </is>
+      </c>
+      <c r="G56" s="10" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-22.10-2026-10-11.jsonl, line 7; snapshot.log and restore.log, copied off</t>
+        </is>
+      </c>
+    </row>
+    <row r="57"/>
+    <row r="58" ht="165" customHeight="1">
+      <c r="A58" s="19" t="inlineStr">
+        <is>
+          <t>Times are IST (UTC+05:30). The logs themselves record UTC. Rows from 2026-09-07 23:35 to 2026-09-10 are records in evidence/ubuntu-26.04-2026-09-10.jsonl, copied off the VM on 2026-10-03; rows from 2026-10-04 are in evidence/ubuntu-26.04-2026-10-04.jsonl, rows from 2026-10-06 in evidence/ubuntu-26.04-2026-10-06.jsonl, and rows from 2026-10-07 in evidence/ubuntu-22.10-2026-10-07.jsonl and, from 12:13, evidence/ubuntu-22.10-2026-10-07-2.jsonl (the 22.10 VM, KineticServer). Rows from 2026-10-08 19:56 are the procedure runs, in evidence/ubuntu-22.10-2026-10-09.jsonl, copied from the service's own log, /var/log/sf3000/runs.jsonl. Rows from 2026-10-10 15:15 and 15:16 are lines 10 to 12 of evidence/ubuntu-22.10-2026-10-10.jsonl, whose first nine lines are the 2026-10-09 file again. Rows from 2026-10-10 16:33 are visit 1 of the upgrade, in evidence/ubuntu-22.10-2026-10-10-2.jsonl. The row from 18:40 is visit 2, line 3 of evidence/ubuntu-22.10-2026-10-10-3.jsonl, whose first two lines are visit 1's file again. The row from 20:00 is visit 3, line 4 of evidence/ubuntu-22.10-2026-10-10-4.jsonl, whose first three lines are visit 2's file again. The rows from 23:26 and 23:42 are Runs E and F, lines 5 and 6 of evidence/ubuntu-22.10-2026-10-10-5.jsonl, whose first four lines are visit 3's file again. The row from 2026-10-11 01:13 is Run G, line 7 of evidence/ubuntu-22.10-2026-10-11.jsonl, whose first six lines are the 2026-10-10 -5 file again. Rows whose Evidence says 'Terminal output' have no record: the engine refuses before it logs anything, or the row is a sweep, which never logs. The six rows before 2026-09-07 23:35 come from commit messages: the VM's log was reset on the evening of 2026-09-07, before anyone copied it. Add one row per run from now on, pointing at its evidence file and line.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A57:G57"/>
+    <mergeCell ref="A58:G58"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/sf3000-tracker.xlsx
+++ b/docs/sf3000-tracker.xlsx
@@ -2127,33 +2127,33 @@
       </c>
       <c r="J18" s="12" t="inlineStr">
         <is>
-          <t>Proven for release-upgrade-to-23.04, -23.10 and -24.04 (22.10 VM, 2026-10-10): their requires read kinetic, lunar and mantic, and their detects read 2210 then 2304, 2304 then 2310, and 2310 then 2404. -26.04 ran twice, made to fail (Runs E and F, 2026-10-10): its requires read noble; step 1's check (apt-get -s full-upgrade, plus a waiting reboot) read 0 both times, so step 1 was skipped; step 2's detect read 2404 before. Not yet healed.</t>
+          <t>Proven for release-upgrade-to-23.04, -23.10 and -24.04 (22.10 VM, 2026-10-10): their requires read kinetic, lunar and mantic, and their detects read 2210 then 2304, 2304 then 2310, and 2310 then 2404. -26.04 ran twice, made to fail (Runs E and F, 2026-10-10): its requires read noble; step 1's check (apt-get -s full-upgrade, plus a waiting reboot) read 0 both times, so step 1 was skipped; step 2's detect read 2404 before. Not yet healed. On 2026-10-14 (visit 4), -26.04's step 1 check read 19 (18 updates and a faked waiting kernel), then 0 after its reboot: the first time it ran.</t>
         </is>
       </c>
       <c r="K18" s="12" t="inlineStr">
         <is>
-          <t>Proven for release-upgrade-to-23.04, -23.10 and -24.04 (22.10 VM, 2026-10-10): apt-get update; full-upgrade; then for 23.04 and 23.10 the next release's upgrader from old-releases, checked with gpgv, run as ./lunar or ./mantic --mode=server --frontend=DistUpgradeViewNonInteractive, and for 24.04 do-release-upgrade -f DistUpgradeViewNonInteractive. Healed in 34, 20 and 27 min. -26.04's do-release-upgrade -f DistUpgradeViewNonInteractive ran twice, made to fail (Runs E and F); the engine restored 24.04 both times. Not yet healed.</t>
+          <t>Proven for release-upgrade-to-23.04, -23.10 and -24.04 (22.10 VM, 2026-10-10): apt-get update; full-upgrade; then for 23.04 and 23.10 the next release's upgrader from old-releases, checked with gpgv, run as ./lunar or ./mantic --mode=server --frontend=DistUpgradeViewNonInteractive, and for 24.04 do-release-upgrade -f DistUpgradeViewNonInteractive. Healed in 34, 20 and 27 min. -26.04's do-release-upgrade -f DistUpgradeViewNonInteractive ran twice, made to fail (Runs E and F); the engine restored 24.04 both times. Visit 4 (2026-10-14): step 1's apt-get full-upgrade installed 18 updates and healed; step 2's do-release-upgrade stopped at once on unattended-upgrades' lock, and the engine restored 24.04. Not yet healed.</t>
         </is>
       </c>
       <c r="L18" s="12" t="n"/>
       <c r="M18" s="12" t="inlineStr">
         <is>
-          <t>Ubuntu 22.10 (kinetic) → 23.04 (lunar) → 23.10 (mantic) → 24.04 (noble): visits 1 to 3; 24.04 → 26.04 (resolute) made to fail twice: Runs E and F</t>
+          <t>Ubuntu 22.10 (kinetic) → 23.04 (lunar) → 23.10 (mantic) → 24.04 (noble): visits 1 to 3; 24.04 → 26.04 (resolute) made to fail twice: Runs E and F; visit 4 restored after a held lock (2026-10-14)</t>
         </is>
       </c>
       <c r="N18" s="12" t="inlineStr">
         <is>
-          <t>Runs under the engine's procedure service: one y/N, then the upgrade, a reboot and the check. Since 2026-10-08: one upgrade per procedure and per visit (2-2.5 h lab slots, the person there); apt checked before the y/N; Timeshift installed by the engine if missing; /boot/efi left out of the snapshot (Windows' EFI partition on the lab's dual-boot machines); a step cut off by a power-off waits for the person (--run again offers the restore). Needs a snapshot: --take-snapshot (Timeshift; restored by itself if the upgrade fails, then checked) or --snapshot &lt;name&gt;. Precondition: apt works (eos-release-dead-repos healed). Written from the upgraders' source; plain do-release-upgrade would skip 23.04/23.10 and offer 24.04 directly from 22.10, which its upgrader is not built for. Timeshift 22.06.5 to 24.01.1 refuse '--tags O', so the engine passes no tags (2b09c29). Since 2026-10-09: dpkg's lock is held around the snapshot and the restore, and the snapshot is synced to disk (74340e2). Since 2026-10-10: /var/log/dist-upgrade is left out of the snapshot, so a failed upgrade's own logs survive the restore (main.log is the only place the non-interactive upgrader writes why it failed). Also since 2026-10-10: the engine keeps 256 MB set aside while a procedure runs and frees it first when a step fails, so a full disk cannot stop the restore (seen in Run F); and -26.04 is two steps, updates + reboot, then do-release-upgrade, which refuses while a kernel or libc6 update waits for a reboot. Run F found: the upgrader can exit while a dpkg it started still runs, and the engine, which then waited only for dpkg's frontend lock, started the restore with that dpkg running. Since 2026-10-11 (seen in Run G): before a restore the engine kills every other process in its service's cgroup (named in the record, leftovers_stopped), and it holds dpkg's own lock as well as the frontend's.</t>
+          <t>Runs under the engine's procedure service: one y/N, then the upgrade, a reboot and the check. Since 2026-10-08: one upgrade per procedure and per visit (2-2.5 h lab slots, the person there); apt checked before the y/N; Timeshift installed by the engine if missing; /boot/efi left out of the snapshot (Windows' EFI partition on the lab's dual-boot machines); a step cut off by a power-off waits for the person (--run again offers the restore). Needs a snapshot: --take-snapshot (Timeshift; restored by itself if the upgrade fails, then checked) or --snapshot &lt;name&gt;. Precondition: apt works (eos-release-dead-repos healed). Written from the upgraders' source; plain do-release-upgrade would skip 23.04/23.10 and offer 24.04 directly from 22.10, which its upgrader is not built for. Timeshift 22.06.5 to 24.01.1 refuse '--tags O', so the engine passes no tags (2b09c29). Since 2026-10-09: dpkg's lock is held around the snapshot and the restore, and the snapshot is synced to disk (74340e2). Since 2026-10-10: /var/log/dist-upgrade is left out of the snapshot, so a failed upgrade's own logs survive the restore (main.log is the only place the non-interactive upgrader writes why it failed). Also since 2026-10-10: the engine keeps 256 MB set aside while a procedure runs and frees it first when a step fails, so a full disk cannot stop the restore (seen in Run F); and -26.04 is two steps, updates + reboot, then do-release-upgrade, which refuses while a kernel or libc6 update waits for a reboot. Run F found: the upgrader can exit while a dpkg it started still runs, and the engine, which then waited only for dpkg's frontend lock, started the restore with that dpkg running. Since 2026-10-11 (seen in Run G): before a restore the engine kills every other process in its service's cgroup (named in the record, leftovers_stopped), and it holds dpkg's own lock as well as the frontend's. Visit 4 (2026-10-14) found: the non-interactive upgrader says why it stopped only in its main.log, so a held dpkg lock read as a failed upgrade and was restored. Since then each upgrade step prints the end of that log when the upgrader fails, so the engine waits and retries instead (DESIGN §16; offline only).</t>
         </is>
       </c>
       <c r="O18" s="12" t="inlineStr">
         <is>
-          <t>2026-10-11 · 24.04 · Run G (a test procedure): a failed step's leftover, holding dpkg's own lock, was stopped before the restore and named in the record; the engine waited for dpkg's own lock before its snapshot; rolled_back. Before it: 2026-10-10 · 24.04 → 26.04 · Runs E and F made the upgrade fail with a filled disk: first at the upgrader's space check, then mid-install. Both rolled_back to 24.04, the second on a full disk, from a half-upgraded machine. Before them, visits 1 to 3 healed (34, 20 and 27 min, one after the other, from repos-fixed, automatic updates on), after the machinery passed tests/procedure-proof Runs A-D.</t>
+          <t>2026-10-14 · 24.04 → 26.04 · Visit 4: step 1 installed 18 updates and rebooted (healed); step 2 stopped at once because unattended-upgrades held dpkg's lock, and the engine restored 24.04 (rolled_back), needlessly. Its snapshot was the first incremental one (52 s). Before it: 2026-10-11 · 24.04 · Run G (a test procedure): a failed step's leftover, holding dpkg's own lock, was stopped before the restore and named in the record; the engine waited for dpkg's own lock before its snapshot; rolled_back. Before it: 2026-10-10 · 24.04 → 26.04 · Runs E and F made the upgrade fail with a filled disk: first at the upgrader's space check, then mid-install. Both rolled_back to 24.04, the second on a full disk, from a half-upgraded machine. Before them, visits 1 to 3 healed (34, 20 and 27 min, one after the other, from repos-fixed, automatic updates on), after the machinery passed tests/procedure-proof Runs A-D.</t>
         </is>
       </c>
       <c r="P18" s="12" t="inlineStr">
         <is>
-          <t>Visit 4 (24.04 → 26.04, two steps) on the VM as Run G left it. Then an EFI desktop VM.</t>
+          <t>Run H (tests/procedure-proof): visit 4 again with dpkg's lock held on purpose; expect two waits, then healed. Then an EFI desktop VM.</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -5565,17 +5565,91 @@
         </is>
       </c>
     </row>
-    <row r="57"/>
-    <row r="58" ht="165" customHeight="1">
-      <c r="A58" s="19" t="inlineStr">
-        <is>
-          <t>Times are IST (UTC+05:30). The logs themselves record UTC. Rows from 2026-09-07 23:35 to 2026-09-10 are records in evidence/ubuntu-26.04-2026-09-10.jsonl, copied off the VM on 2026-10-03; rows from 2026-10-04 are in evidence/ubuntu-26.04-2026-10-04.jsonl, rows from 2026-10-06 in evidence/ubuntu-26.04-2026-10-06.jsonl, and rows from 2026-10-07 in evidence/ubuntu-22.10-2026-10-07.jsonl and, from 12:13, evidence/ubuntu-22.10-2026-10-07-2.jsonl (the 22.10 VM, KineticServer). Rows from 2026-10-08 19:56 are the procedure runs, in evidence/ubuntu-22.10-2026-10-09.jsonl, copied from the service's own log, /var/log/sf3000/runs.jsonl. Rows from 2026-10-10 15:15 and 15:16 are lines 10 to 12 of evidence/ubuntu-22.10-2026-10-10.jsonl, whose first nine lines are the 2026-10-09 file again. Rows from 2026-10-10 16:33 are visit 1 of the upgrade, in evidence/ubuntu-22.10-2026-10-10-2.jsonl. The row from 18:40 is visit 2, line 3 of evidence/ubuntu-22.10-2026-10-10-3.jsonl, whose first two lines are visit 1's file again. The row from 20:00 is visit 3, line 4 of evidence/ubuntu-22.10-2026-10-10-4.jsonl, whose first three lines are visit 2's file again. The rows from 23:26 and 23:42 are Runs E and F, lines 5 and 6 of evidence/ubuntu-22.10-2026-10-10-5.jsonl, whose first four lines are visit 3's file again. The row from 2026-10-11 01:13 is Run G, line 7 of evidence/ubuntu-22.10-2026-10-11.jsonl, whose first six lines are the 2026-10-10 -5 file again. Rows whose Evidence says 'Terminal output' have no record: the engine refuses before it logs anything, or the row is a sweep, which never logs. The six rows before 2026-09-07 23:35 come from commit messages: the VM's log was reset on the evening of 2026-09-07, before anyone copied it. Add one row per run from now on, pointing at its evidence file and line.</t>
+    <row r="57" ht="56" customHeight="1">
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-14 17:09</t>
+        </is>
+      </c>
+      <c r="B57" s="10" t="inlineStr">
+        <is>
+          <t>24.04</t>
+        </is>
+      </c>
+      <c r="C57" s="10" t="inlineStr">
+        <is>
+          <t>01df9d9</t>
+        </is>
+      </c>
+      <c r="D57" s="10" t="inlineStr">
+        <is>
+          <t>release-upgrade-to-26.04/updates</t>
+        </is>
+      </c>
+      <c r="E57" s="10" t="inlineStr">
+        <is>
+          <t>healed</t>
+        </is>
+      </c>
+      <c r="F57" s="10" t="inlineStr">
+        <is>
+          <t>Visit 4, on the VM as Run G left it, with Run G's snapshot kept. A waiting kernel was faked in /var/run/reboot-required.pkgs, so step 1 would run whatever waited. Snapshot 2026-10-14_11-38-22 (52 s, linked to Run G's: the first incremental engine snapshot). Step 1's check read 19 (18 updates and the fake). apt-get full-upgrade: 11 upgraded, 7 new (kernel 6.8.0-147 among them), 2 deferred by phasing. A reboot, then the check read 0. The first step 1 to install anything.</t>
+        </is>
+      </c>
+      <c r="G57" s="10" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-22.10-2026-10-14.jsonl, line 8; the step's log and snapshot.log, copied off</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="56" customHeight="1">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-14 17:13</t>
+        </is>
+      </c>
+      <c r="B58" s="10" t="inlineStr">
+        <is>
+          <t>24.04 → 26.04</t>
+        </is>
+      </c>
+      <c r="C58" s="10" t="inlineStr">
+        <is>
+          <t>01df9d9</t>
+        </is>
+      </c>
+      <c r="D58" s="10" t="inlineStr">
+        <is>
+          <t>release-upgrade-to-26.04/to-26.04</t>
+        </is>
+      </c>
+      <c r="E58" s="10" t="inlineStr">
+        <is>
+          <t>rolled_back</t>
+        </is>
+      </c>
+      <c r="F58" s="10" t="inlineStr">
+        <is>
+          <t>Visit 4's upgrade, at the boot after step 1. unattended-upgrades (PID 1019) held dpkg's frontend lock: its timer was catching up after four days with the VM off. The 26.04 upgrader (26.04.27) tried the lock 21 times in 2 s, then exited 1. It wrote why only to its main.log; the step's output had no lock message, so failure fix_failed, and the engine restored. The restore began 60 s later: one wait for the lock, from the timing. The check matched: 'ok: back to 24.04 packages:d778793cbf7390c2', step 1's updates undone too. The phased updates did not stop do-release-upgrade. The fix: each upgrade step now prints the upgrader's log when it fails (DESIGN §16, 2026-10-14).</t>
+        </is>
+      </c>
+      <c r="G58" s="10" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-22.10-2026-10-14.jsonl, line 9; the upgrader's main.log (top level of /var/log/dist-upgrade), the step's log and restore.log, copied off</t>
+        </is>
+      </c>
+    </row>
+    <row r="59"/>
+    <row r="60" ht="165" customHeight="1">
+      <c r="A60" s="19" t="inlineStr">
+        <is>
+          <t>Times are IST (UTC+05:30). The logs themselves record UTC. Rows from 2026-09-07 23:35 to 2026-09-10 are records in evidence/ubuntu-26.04-2026-09-10.jsonl, copied off the VM on 2026-10-03; rows from 2026-10-04 are in evidence/ubuntu-26.04-2026-10-04.jsonl, rows from 2026-10-06 in evidence/ubuntu-26.04-2026-10-06.jsonl, and rows from 2026-10-07 in evidence/ubuntu-22.10-2026-10-07.jsonl and, from 12:13, evidence/ubuntu-22.10-2026-10-07-2.jsonl (the 22.10 VM, KineticServer). Rows from 2026-10-08 19:56 are the procedure runs, in evidence/ubuntu-22.10-2026-10-09.jsonl, copied from the service's own log, /var/log/sf3000/runs.jsonl. Rows from 2026-10-10 15:15 and 15:16 are lines 10 to 12 of evidence/ubuntu-22.10-2026-10-10.jsonl, whose first nine lines are the 2026-10-09 file again. Rows from 2026-10-10 16:33 are visit 1 of the upgrade, in evidence/ubuntu-22.10-2026-10-10-2.jsonl. The row from 18:40 is visit 2, line 3 of evidence/ubuntu-22.10-2026-10-10-3.jsonl, whose first two lines are visit 1's file again. The row from 20:00 is visit 3, line 4 of evidence/ubuntu-22.10-2026-10-10-4.jsonl, whose first three lines are visit 2's file again. The rows from 23:26 and 23:42 are Runs E and F, lines 5 and 6 of evidence/ubuntu-22.10-2026-10-10-5.jsonl, whose first four lines are visit 3's file again. The row from 2026-10-11 01:13 is Run G, line 7 of evidence/ubuntu-22.10-2026-10-11.jsonl, whose first six lines are the 2026-10-10 -5 file again. The rows from 2026-10-14 17:09 and 17:13 are visit 4, lines 8 and 9 of evidence/ubuntu-22.10-2026-10-14.jsonl, whose first seven lines are the 2026-10-11 file again. Rows whose Evidence says 'Terminal output' have no record: the engine refuses before it logs anything, or the row is a sweep, which never logs. The six rows before 2026-09-07 23:35 come from commit messages: the VM's log was reset on the evening of 2026-09-07, before anyone copied it. Add one row per run from now on, pointing at its evidence file and line.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A58:G58"/>
+    <mergeCell ref="A60:G60"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/sf3000-tracker.xlsx
+++ b/docs/sf3000-tracker.xlsx
@@ -2127,33 +2127,33 @@
       </c>
       <c r="J18" s="12" t="inlineStr">
         <is>
-          <t>Proven for release-upgrade-to-23.04, -23.10 and -24.04 (22.10 VM, 2026-10-10): their requires read kinetic, lunar and mantic, and their detects read 2210 then 2304, 2304 then 2310, and 2310 then 2404. -26.04 ran twice, made to fail (Runs E and F, 2026-10-10): its requires read noble; step 1's check (apt-get -s full-upgrade, plus a waiting reboot) read 0 both times, so step 1 was skipped; step 2's detect read 2404 before. Not yet healed. On 2026-10-14 (visit 4), -26.04's step 1 check read 19 (18 updates and a faked waiting kernel), then 0 after its reboot: the first time it ran.</t>
+          <t>Proven for release-upgrade-to-23.04, -23.10 and -24.04 (22.10 VM, 2026-10-10): their requires read kinetic, lunar and mantic, and their detects read 2210 then 2304, 2304 then 2310, and 2310 then 2404. -26.04 ran twice, made to fail (Runs E and F, 2026-10-10): its requires read noble; step 1's check (apt-get -s full-upgrade, plus a waiting reboot) read 0 both times, so step 1 was skipped; step 2's detect read 2404 before. Not yet healed. On 2026-10-14 (visit 4), -26.04's step 1 check read 19 (18 updates and a faked waiting kernel), then 0 after its reboot: the first time it ran. In Run H (2026-10-14), -26.04's step 1 check read 6 (new security updates), then 0 after its reboot; step 2's detect read 2404, then 2604 after its reboot.</t>
         </is>
       </c>
       <c r="K18" s="12" t="inlineStr">
         <is>
-          <t>Proven for release-upgrade-to-23.04, -23.10 and -24.04 (22.10 VM, 2026-10-10): apt-get update; full-upgrade; then for 23.04 and 23.10 the next release's upgrader from old-releases, checked with gpgv, run as ./lunar or ./mantic --mode=server --frontend=DistUpgradeViewNonInteractive, and for 24.04 do-release-upgrade -f DistUpgradeViewNonInteractive. Healed in 34, 20 and 27 min. -26.04's do-release-upgrade -f DistUpgradeViewNonInteractive ran twice, made to fail (Runs E and F); the engine restored 24.04 both times. Visit 4 (2026-10-14): step 1's apt-get full-upgrade installed 18 updates and healed; step 2's do-release-upgrade stopped at once on unattended-upgrades' lock, and the engine restored 24.04. Not yet healed.</t>
+          <t>Proven for release-upgrade-to-23.04, -23.10 and -24.04 (22.10 VM, 2026-10-10): apt-get update; full-upgrade; then for 23.04 and 23.10 the next release's upgrader from old-releases, checked with gpgv, run as ./lunar or ./mantic --mode=server --frontend=DistUpgradeViewNonInteractive, and for 24.04 do-release-upgrade -f DistUpgradeViewNonInteractive. Healed in 34, 20 and 27 min. -26.04's do-release-upgrade -f DistUpgradeViewNonInteractive ran twice, made to fail (Runs E and F); the engine restored 24.04 both times. Visit 4 (2026-10-14): step 1's apt-get full-upgrade installed 18 updates and healed; step 2's do-release-upgrade stopped at once on unattended-upgrades' lock, and the engine restored 24.04. Run H, visit 4's second try (2026-10-14): step 1's apt-get full-upgrade waited out a dpkg lock held on purpose, twice, then installed 6 updates and healed; step 2's do-release-upgrade, now printing the upgrader's log on a failure, upgraded 24.04 to 26.04 in 24 min and healed. That print has not run on a VM: the upgrader did not fail.</t>
         </is>
       </c>
       <c r="L18" s="12" t="n"/>
       <c r="M18" s="12" t="inlineStr">
         <is>
-          <t>Ubuntu 22.10 (kinetic) → 23.04 (lunar) → 23.10 (mantic) → 24.04 (noble): visits 1 to 3; 24.04 → 26.04 (resolute) made to fail twice: Runs E and F; visit 4 restored after a held lock (2026-10-14)</t>
+          <t>Ubuntu 22.10 (kinetic) → 23.04 (lunar) → 23.10 (mantic) → 24.04 (noble): visits 1 to 3; 24.04 → 26.04 (resolute) made to fail twice: Runs E and F; visit 4 restored after a held lock (2026-10-14); visit 4 healed at its second try (Run H, 2026-10-14)</t>
         </is>
       </c>
       <c r="N18" s="12" t="inlineStr">
         <is>
-          <t>Runs under the engine's procedure service: one y/N, then the upgrade, a reboot and the check. Since 2026-10-08: one upgrade per procedure and per visit (2-2.5 h lab slots, the person there); apt checked before the y/N; Timeshift installed by the engine if missing; /boot/efi left out of the snapshot (Windows' EFI partition on the lab's dual-boot machines); a step cut off by a power-off waits for the person (--run again offers the restore). Needs a snapshot: --take-snapshot (Timeshift; restored by itself if the upgrade fails, then checked) or --snapshot &lt;name&gt;. Precondition: apt works (eos-release-dead-repos healed). Written from the upgraders' source; plain do-release-upgrade would skip 23.04/23.10 and offer 24.04 directly from 22.10, which its upgrader is not built for. Timeshift 22.06.5 to 24.01.1 refuse '--tags O', so the engine passes no tags (2b09c29). Since 2026-10-09: dpkg's lock is held around the snapshot and the restore, and the snapshot is synced to disk (74340e2). Since 2026-10-10: /var/log/dist-upgrade is left out of the snapshot, so a failed upgrade's own logs survive the restore (main.log is the only place the non-interactive upgrader writes why it failed). Also since 2026-10-10: the engine keeps 256 MB set aside while a procedure runs and frees it first when a step fails, so a full disk cannot stop the restore (seen in Run F); and -26.04 is two steps, updates + reboot, then do-release-upgrade, which refuses while a kernel or libc6 update waits for a reboot. Run F found: the upgrader can exit while a dpkg it started still runs, and the engine, which then waited only for dpkg's frontend lock, started the restore with that dpkg running. Since 2026-10-11 (seen in Run G): before a restore the engine kills every other process in its service's cgroup (named in the record, leftovers_stopped), and it holds dpkg's own lock as well as the frontend's. Visit 4 (2026-10-14) found: the non-interactive upgrader says why it stopped only in its main.log, so a held dpkg lock read as a failed upgrade and was restored. Since then each upgrade step prints the end of that log when the upgrader fails, so the engine waits and retries instead (DESIGN §16; offline only).</t>
+          <t>Runs under the engine's procedure service: one y/N, then the upgrade, a reboot and the check. Since 2026-10-08: one upgrade per procedure and per visit (2-2.5 h lab slots, the person there); apt checked before the y/N; Timeshift installed by the engine if missing; /boot/efi left out of the snapshot (Windows' EFI partition on the lab's dual-boot machines); a step cut off by a power-off waits for the person (--run again offers the restore). Needs a snapshot: --take-snapshot (Timeshift; restored by itself if the upgrade fails, then checked) or --snapshot &lt;name&gt;. Precondition: apt works (eos-release-dead-repos healed). Written from the upgraders' source; plain do-release-upgrade would skip 23.04/23.10 and offer 24.04 directly from 22.10, which its upgrader is not built for. Timeshift 22.06.5 to 24.01.1 refuse '--tags O', so the engine passes no tags (2b09c29). Since 2026-10-09: dpkg's lock is held around the snapshot and the restore, and the snapshot is synced to disk (74340e2). Since 2026-10-10: /var/log/dist-upgrade is left out of the snapshot, so a failed upgrade's own logs survive the restore (main.log is the only place the non-interactive upgrader writes why it failed). Also since 2026-10-10: the engine keeps 256 MB set aside while a procedure runs and frees it first when a step fails, so a full disk cannot stop the restore (seen in Run F); and -26.04 is two steps, updates + reboot, then do-release-upgrade, which refuses while a kernel or libc6 update waits for a reboot. Run F found: the upgrader can exit while a dpkg it started still runs, and the engine, which then waited only for dpkg's frontend lock, started the restore with that dpkg running. Since 2026-10-11 (seen in Run G): before a restore the engine kills every other process in its service's cgroup (named in the record, leftovers_stopped), and it holds dpkg's own lock as well as the frontend's. Visit 4 (2026-10-14) found: the non-interactive upgrader says why it stopped only in its main.log, so a held dpkg lock read as a failed upgrade and was restored. Since then each upgrade step prints the end of that log when the upgrader fails, so the engine waits and retries instead (DESIGN §16; offline only). Run H (2026-10-14) found: the box before the y is worked out before the apt check, from apt's lists as they were, so on 24.04 it can say step 1 is done when new updates wait. Step 1 then runs anyway, since its own check finds them, and adds a reboot.</t>
         </is>
       </c>
       <c r="O18" s="12" t="inlineStr">
         <is>
-          <t>2026-10-14 · 24.04 → 26.04 · Visit 4: step 1 installed 18 updates and rebooted (healed); step 2 stopped at once because unattended-upgrades held dpkg's lock, and the engine restored 24.04 (rolled_back), needlessly. Its snapshot was the first incremental one (52 s). Before it: 2026-10-11 · 24.04 · Run G (a test procedure): a failed step's leftover, holding dpkg's own lock, was stopped before the restore and named in the record; the engine waited for dpkg's own lock before its snapshot; rolled_back. Before it: 2026-10-10 · 24.04 → 26.04 · Runs E and F made the upgrade fail with a filled disk: first at the upgrader's space check, then mid-install. Both rolled_back to 24.04, the second on a full disk, from a half-upgraded machine. Before them, visits 1 to 3 healed (34, 20 and 27 min, one after the other, from repos-fixed, automatic updates on), after the machinery passed tests/procedure-proof Runs A-D.</t>
+          <t>2026-10-14 · 24.04 → 26.04 · Run H, visit 4's second try: step 1 found 6 new security updates, waited out a dpkg lock held on purpose twice (the first step retry seen on a VM), installed them and rebooted (healed); step 2 upgraded to 26.04 in 24 min (healed). The lock never reached the upgrader. Before it: 2026-10-14 · 24.04 → 26.04 · Visit 4: step 1 installed 18 updates and rebooted (healed); step 2 stopped at once because unattended-upgrades held dpkg's lock, and the engine restored 24.04 (rolled_back), needlessly. Its snapshot was the first incremental one (52 s). Before it: 2026-10-11 · 24.04 · Run G (a test procedure): a failed step's leftover, holding dpkg's own lock, was stopped before the restore and named in the record; the engine waited for dpkg's own lock before its snapshot; rolled_back. Before it: 2026-10-10 · 24.04 → 26.04 · Runs E and F made the upgrade fail with a filled disk: first at the upgrader's space check, then mid-install. Both rolled_back to 24.04, the second on a full disk, from a half-upgraded machine. Before them, visits 1 to 3 healed (34, 20 and 27 min, one after the other, from repos-fixed, automatic updates on), after the machinery passed tests/procedure-proof Runs A-D.</t>
         </is>
       </c>
       <c r="P18" s="12" t="inlineStr">
         <is>
-          <t>Run H (tests/procedure-proof): visit 4 again with dpkg's lock held on purpose; expect two waits, then healed. Then an EFI desktop VM.</t>
+          <t>An EFI desktop VM (22.10 desktop): the upgrades as the lab will run them. Still offline only: a lock that only the upgrader's log names.</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -5639,17 +5639,91 @@
         </is>
       </c>
     </row>
-    <row r="59"/>
-    <row r="60" ht="165" customHeight="1">
-      <c r="A60" s="19" t="inlineStr">
-        <is>
-          <t>Times are IST (UTC+05:30). The logs themselves record UTC. Rows from 2026-09-07 23:35 to 2026-09-10 are records in evidence/ubuntu-26.04-2026-09-10.jsonl, copied off the VM on 2026-10-03; rows from 2026-10-04 are in evidence/ubuntu-26.04-2026-10-04.jsonl, rows from 2026-10-06 in evidence/ubuntu-26.04-2026-10-06.jsonl, and rows from 2026-10-07 in evidence/ubuntu-22.10-2026-10-07.jsonl and, from 12:13, evidence/ubuntu-22.10-2026-10-07-2.jsonl (the 22.10 VM, KineticServer). Rows from 2026-10-08 19:56 are the procedure runs, in evidence/ubuntu-22.10-2026-10-09.jsonl, copied from the service's own log, /var/log/sf3000/runs.jsonl. Rows from 2026-10-10 15:15 and 15:16 are lines 10 to 12 of evidence/ubuntu-22.10-2026-10-10.jsonl, whose first nine lines are the 2026-10-09 file again. Rows from 2026-10-10 16:33 are visit 1 of the upgrade, in evidence/ubuntu-22.10-2026-10-10-2.jsonl. The row from 18:40 is visit 2, line 3 of evidence/ubuntu-22.10-2026-10-10-3.jsonl, whose first two lines are visit 1's file again. The row from 20:00 is visit 3, line 4 of evidence/ubuntu-22.10-2026-10-10-4.jsonl, whose first three lines are visit 2's file again. The rows from 23:26 and 23:42 are Runs E and F, lines 5 and 6 of evidence/ubuntu-22.10-2026-10-10-5.jsonl, whose first four lines are visit 3's file again. The row from 2026-10-11 01:13 is Run G, line 7 of evidence/ubuntu-22.10-2026-10-11.jsonl, whose first six lines are the 2026-10-10 -5 file again. The rows from 2026-10-14 17:09 and 17:13 are visit 4, lines 8 and 9 of evidence/ubuntu-22.10-2026-10-14.jsonl, whose first seven lines are the 2026-10-11 file again. Rows whose Evidence says 'Terminal output' have no record: the engine refuses before it logs anything, or the row is a sweep, which never logs. The six rows before 2026-09-07 23:35 come from commit messages: the VM's log was reset on the evening of 2026-09-07, before anyone copied it. Add one row per run from now on, pointing at its evidence file and line.</t>
+    <row r="59" ht="56" customHeight="1">
+      <c r="A59" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-14 19:09</t>
+        </is>
+      </c>
+      <c r="B59" s="10" t="inlineStr">
+        <is>
+          <t>24.04</t>
+        </is>
+      </c>
+      <c r="C59" s="10" t="inlineStr">
+        <is>
+          <t>5a47978</t>
+        </is>
+      </c>
+      <c r="D59" s="10" t="inlineStr">
+        <is>
+          <t>release-upgrade-to-26.04/updates</t>
+        </is>
+      </c>
+      <c r="E59" s="10" t="inlineStr">
+        <is>
+          <t>healed</t>
+        </is>
+      </c>
+      <c r="F59" s="10" t="inlineStr">
+        <is>
+          <t>Run H (tests/procedure-proof): visit 4 again, on the VM as visit 4's restore left it. The 18 updates were installed by hand first, so that step 1 would be skipped. A second session took dpkg's frontend lock when the snapshot ended (2026-10-14_13-38-21, 64 s, incremental) and held it 100 s. Security updates published since (openssh, bind9) were fetched by the apt check, so step 1's check read 6 and it ran. Its full-upgrade found the lock held twice; the engine waited 60 s each time, then installed the 6 and rebooted (fix_attempts 3). Check after: 0. The first step retry seen on a VM. The box before the y had said step 1 was done: it is worked out before the apt check.</t>
+        </is>
+      </c>
+      <c r="G59" s="10" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-22.10-2026-10-14-2.jsonl, line 10; the step's log and apt-check.log, copied off</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="56" customHeight="1">
+      <c r="A60" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-14 19:12</t>
+        </is>
+      </c>
+      <c r="B60" s="10" t="inlineStr">
+        <is>
+          <t>24.04 → 26.04</t>
+        </is>
+      </c>
+      <c r="C60" s="10" t="inlineStr">
+        <is>
+          <t>5a47978</t>
+        </is>
+      </c>
+      <c r="D60" s="10" t="inlineStr">
+        <is>
+          <t>release-upgrade-to-26.04/to-26.04</t>
+        </is>
+      </c>
+      <c r="E60" s="10" t="inlineStr">
+        <is>
+          <t>healed</t>
+        </is>
+      </c>
+      <c r="F60" s="10" t="inlineStr">
+        <is>
+          <t>Run H's upgrade, at the boot after step 1, with the holder gone. do-release-upgrade (26.04.27) at its first attempt: 9 min of download, 14 of install, then the engine's reboot. Check after: 2604 (kernel 7.0.0-38, Python 3.14). Visit 4 healed at its second try, so all four upgrades have healed on this VM. The lock never reached the upgrader, so the part of the step that prints the upgrader's log on a failure (DESIGN §16, 2026-10-14) did not run.</t>
+        </is>
+      </c>
+      <c r="G60" s="10" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-22.10-2026-10-14-2.jsonl, line 11; the upgrader's logs (logs/kinetic-run-h-dist-upgrade) and the step's log, copied off</t>
+        </is>
+      </c>
+    </row>
+    <row r="61"/>
+    <row r="62" ht="165" customHeight="1">
+      <c r="A62" s="19" t="inlineStr">
+        <is>
+          <t>Times are IST (UTC+05:30). The logs themselves record UTC. Rows from 2026-09-07 23:35 to 2026-09-10 are records in evidence/ubuntu-26.04-2026-09-10.jsonl, copied off the VM on 2026-10-03; rows from 2026-10-04 are in evidence/ubuntu-26.04-2026-10-04.jsonl, rows from 2026-10-06 in evidence/ubuntu-26.04-2026-10-06.jsonl, and rows from 2026-10-07 in evidence/ubuntu-22.10-2026-10-07.jsonl and, from 12:13, evidence/ubuntu-22.10-2026-10-07-2.jsonl (the 22.10 VM, KineticServer). Rows from 2026-10-08 19:56 are the procedure runs, in evidence/ubuntu-22.10-2026-10-09.jsonl, copied from the service's own log, /var/log/sf3000/runs.jsonl. Rows from 2026-10-10 15:15 and 15:16 are lines 10 to 12 of evidence/ubuntu-22.10-2026-10-10.jsonl, whose first nine lines are the 2026-10-09 file again. Rows from 2026-10-10 16:33 are visit 1 of the upgrade, in evidence/ubuntu-22.10-2026-10-10-2.jsonl. The row from 18:40 is visit 2, line 3 of evidence/ubuntu-22.10-2026-10-10-3.jsonl, whose first two lines are visit 1's file again. The row from 20:00 is visit 3, line 4 of evidence/ubuntu-22.10-2026-10-10-4.jsonl, whose first three lines are visit 2's file again. The rows from 23:26 and 23:42 are Runs E and F, lines 5 and 6 of evidence/ubuntu-22.10-2026-10-10-5.jsonl, whose first four lines are visit 3's file again. The row from 2026-10-11 01:13 is Run G, line 7 of evidence/ubuntu-22.10-2026-10-11.jsonl, whose first six lines are the 2026-10-10 -5 file again. The rows from 2026-10-14 17:09 and 17:13 are visit 4, lines 8 and 9 of evidence/ubuntu-22.10-2026-10-14.jsonl, whose first seven lines are the 2026-10-11 file again. The rows from 2026-10-14 19:09 and 19:12 are Run H, lines 10 and 11 of evidence/ubuntu-22.10-2026-10-14-2.jsonl, whose first nine lines are the 2026-10-14 file again. Rows whose Evidence says 'Terminal output' have no record: the engine refuses before it logs anything, or the row is a sweep, which never logs. The six rows before 2026-09-07 23:35 come from commit messages: the VM's log was reset on the evening of 2026-09-07, before anyone copied it. Add one row per run from now on, pointing at its evidence file and line.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A60:G60"/>
+    <mergeCell ref="A62:G62"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/sf3000-tracker.xlsx
+++ b/docs/sf3000-tracker.xlsx
@@ -2143,7 +2143,7 @@
       </c>
       <c r="N18" s="12" t="inlineStr">
         <is>
-          <t>Runs under the engine's procedure service: one y/N, then the upgrade, a reboot and the check. Since 2026-10-08: one upgrade per procedure and per visit (2-2.5 h lab slots, the person there); apt checked before the y/N; Timeshift installed by the engine if missing; /boot/efi left out of the snapshot (Windows' EFI partition on the lab's dual-boot machines); a step cut off by a power-off waits for the person (--run again offers the restore). Needs a snapshot: --take-snapshot (Timeshift; restored by itself if the upgrade fails, then checked) or --snapshot &lt;name&gt;. Precondition: apt works (eos-release-dead-repos healed). Written from the upgraders' source; plain do-release-upgrade would skip 23.04/23.10 and offer 24.04 directly from 22.10, which its upgrader is not built for. Timeshift 22.06.5 to 24.01.1 refuse '--tags O', so the engine passes no tags (2b09c29). Since 2026-10-09: dpkg's lock is held around the snapshot and the restore, and the snapshot is synced to disk (74340e2). Since 2026-10-10: /var/log/dist-upgrade is left out of the snapshot, so a failed upgrade's own logs survive the restore (main.log is the only place the non-interactive upgrader writes why it failed). Also since 2026-10-10: the engine keeps 256 MB set aside while a procedure runs and frees it first when a step fails, so a full disk cannot stop the restore (seen in Run F); and -26.04 is two steps, updates + reboot, then do-release-upgrade, which refuses while a kernel or libc6 update waits for a reboot. Run F found: the upgrader can exit while a dpkg it started still runs, and the engine, which then waited only for dpkg's frontend lock, started the restore with that dpkg running. Since 2026-10-11 (seen in Run G): before a restore the engine kills every other process in its service's cgroup (named in the record, leftovers_stopped), and it holds dpkg's own lock as well as the frontend's. Visit 4 (2026-10-14) found: the non-interactive upgrader says why it stopped only in its main.log, so a held dpkg lock read as a failed upgrade and was restored. Since then each upgrade step prints the end of that log when the upgrader fails, so the engine waits and retries instead (DESIGN §16; offline only). Run H (2026-10-14) found: the box before the y is worked out before the apt check, from apt's lists as they were, so on 24.04 it can say step 1 is done when new updates wait. Step 1 then runs anyway, since its own check finds them, and adds a reboot.</t>
+          <t>Runs under the engine's procedure service: one y/N, then the upgrade, a reboot and the check. Since 2026-10-08: one upgrade per procedure and per visit (2-2.5 h lab slots, the person there); apt checked before the y/N; Timeshift installed by the engine if missing; /boot/efi left out of the snapshot (Windows' EFI partition on the lab's dual-boot machines); a step cut off by a power-off waits for the person (--run again offers the restore). Needs a snapshot: --take-snapshot (Timeshift; restored by itself if the upgrade fails, then checked) or --snapshot &lt;name&gt;. Precondition: apt works (eos-release-dead-repos healed). Written from the upgraders' source; plain do-release-upgrade would skip 23.04/23.10 and offer 24.04 directly from 22.10, which its upgrader is not built for. Timeshift 22.06.5 to 24.01.1 refuse '--tags O', so the engine passes no tags (2b09c29). Since 2026-10-09: dpkg's lock is held around the snapshot and the restore, and the snapshot is synced to disk (74340e2). Since 2026-10-10: /var/log/dist-upgrade is left out of the snapshot, so a failed upgrade's own logs survive the restore (main.log is the only place the non-interactive upgrader writes why it failed). Also since 2026-10-10: the engine keeps 256 MB set aside while a procedure runs and frees it first when a step fails, so a full disk cannot stop the restore (seen in Run F); and -26.04 is two steps, updates + reboot, then do-release-upgrade, which refuses while a kernel or libc6 update waits for a reboot. Run F found: the upgrader can exit while a dpkg it started still runs, and the engine, which then waited only for dpkg's frontend lock, started the restore with that dpkg running. Since 2026-10-11 (seen in Run G): before a restore the engine kills every other process in its service's cgroup (named in the record, leftovers_stopped), and it holds dpkg's own lock as well as the frontend's. Visit 4 (2026-10-14) found: the non-interactive upgrader says why it stopped only in its main.log, so a held dpkg lock read as a failed upgrade and was restored. Since then each upgrade step prints the end of that log when the upgrader fails, so the engine waits and retries instead (DESIGN §16; offline only). Run H (2026-10-14) found: the box before the y is worked out before the apt check, from apt's lists as they were, so on 24.04 it can say step 1 is done when new updates wait. Step 1 then runs anyway, since its own check finds them, and adds a reboot. Since 2026-10-14 the box is worked out again after the apt check, so it shows what the steps will find (DESIGN §16; offline only).</t>
         </is>
       </c>
       <c r="O18" s="12" t="inlineStr">
@@ -5713,7 +5713,6 @@
         </is>
       </c>
     </row>
-    <row r="61"/>
     <row r="62" ht="165" customHeight="1">
       <c r="A62" s="19" t="inlineStr">
         <is>

--- a/docs/sf3000-tracker.xlsx
+++ b/docs/sf3000-tracker.xlsx
@@ -87,7 +87,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -109,11 +109,84 @@
         <color rgb="00D0D0D0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D0D0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D0D0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D0D0D0"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00D0D0D0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D0D0D0"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00D0D0D0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -170,6 +243,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2127,33 +2207,33 @@
       </c>
       <c r="J18" s="12" t="inlineStr">
         <is>
-          <t>Proven for release-upgrade-to-23.04, -23.10 and -24.04 (22.10 VM, 2026-10-10): their requires read kinetic, lunar and mantic, and their detects read 2210 then 2304, 2304 then 2310, and 2310 then 2404. -26.04 ran twice, made to fail (Runs E and F, 2026-10-10): its requires read noble; step 1's check (apt-get -s full-upgrade, plus a waiting reboot) read 0 both times, so step 1 was skipped; step 2's detect read 2404 before. Not yet healed. On 2026-10-14 (visit 4), -26.04's step 1 check read 19 (18 updates and a faked waiting kernel), then 0 after its reboot: the first time it ran. In Run H (2026-10-14), -26.04's step 1 check read 6 (new security updates), then 0 after its reboot; step 2's detect read 2404, then 2604 after its reboot.</t>
+          <t>Proven for release-upgrade-to-23.04, -23.10 and -24.04 (22.10 VM, 2026-10-10): their requires read kinetic, lunar and mantic, and their detects read 2210 then 2304, 2304 then 2310, and 2310 then 2404. -26.04 ran twice, made to fail (Runs E and F, 2026-10-10): its requires read noble; step 1's check (apt-get -s full-upgrade, plus a waiting reboot) read 0 both times, so step 1 was skipped; step 2's detect read 2404 before. Not yet healed. On 2026-10-14 (visit 4), -26.04's step 1 check read 19 (18 updates and a faked waiting kernel), then 0 after its reboot: the first time it ran. In Run H (2026-10-14), -26.04's step 1 check read 6 (new security updates), then 0 after its reboot; step 2's detect read 2404, then 2604 after its reboot. release-upgrade-to-23.04 also on an EFI 22.10 desktop (2026-10-16): 2210 then 2304.</t>
         </is>
       </c>
       <c r="K18" s="12" t="inlineStr">
         <is>
-          <t>Proven for release-upgrade-to-23.04, -23.10 and -24.04 (22.10 VM, 2026-10-10): apt-get update; full-upgrade; then for 23.04 and 23.10 the next release's upgrader from old-releases, checked with gpgv, run as ./lunar or ./mantic --mode=server --frontend=DistUpgradeViewNonInteractive, and for 24.04 do-release-upgrade -f DistUpgradeViewNonInteractive. Healed in 34, 20 and 27 min. -26.04's do-release-upgrade -f DistUpgradeViewNonInteractive ran twice, made to fail (Runs E and F); the engine restored 24.04 both times. Visit 4 (2026-10-14): step 1's apt-get full-upgrade installed 18 updates and healed; step 2's do-release-upgrade stopped at once on unattended-upgrades' lock, and the engine restored 24.04. Run H, visit 4's second try (2026-10-14): step 1's apt-get full-upgrade waited out a dpkg lock held on purpose, twice, then installed 6 updates and healed; step 2's do-release-upgrade, now printing the upgrader's log on a failure, upgraded 24.04 to 26.04 in 24 min and healed. That print has not run on a VM: the upgrader did not fail.</t>
+          <t>Proven for release-upgrade-to-23.04, -23.10 and -24.04 (22.10 VM, 2026-10-10): apt-get update; full-upgrade; then for 23.04 and 23.10 the next release's upgrader from old-releases, checked with gpgv, run as ./lunar or ./mantic --mode=server --frontend=DistUpgradeViewNonInteractive, and for 24.04 do-release-upgrade -f DistUpgradeViewNonInteractive. Healed in 34, 20 and 27 min. -26.04's do-release-upgrade -f DistUpgradeViewNonInteractive ran twice, made to fail (Runs E and F); the engine restored 24.04 both times. Visit 4 (2026-10-14): step 1's apt-get full-upgrade installed 18 updates and healed; step 2's do-release-upgrade stopped at once on unattended-upgrades' lock, and the engine restored 24.04. Run H, visit 4's second try (2026-10-14): step 1's apt-get full-upgrade waited out a dpkg lock held on purpose, twice, then installed 6 updates and healed; step 2's do-release-upgrade, now printing the upgrader's log on a failure, upgraded 24.04 to 26.04 in 24 min and healed. That print has not run on a VM: the upgrader did not fail. release-upgrade-to-23.04 also on an EFI 22.10 desktop (2026-10-16): healed in 48 min; made to fail mid-install, it printed the upgrader's log and was restored.</t>
         </is>
       </c>
       <c r="L18" s="12" t="n"/>
       <c r="M18" s="12" t="inlineStr">
         <is>
-          <t>Ubuntu 22.10 (kinetic) → 23.04 (lunar) → 23.10 (mantic) → 24.04 (noble): visits 1 to 3; 24.04 → 26.04 (resolute) made to fail twice: Runs E and F; visit 4 restored after a held lock (2026-10-14); visit 4 healed at its second try (Run H, 2026-10-14)</t>
+          <t>Ubuntu 22.10 (kinetic) → 23.04 (lunar) → 23.10 (mantic) → 24.04 (noble): visits 1 to 3; 24.04 → 26.04 (resolute) made to fail twice: Runs E and F; visit 4 restored after a held lock (2026-10-14); visit 4 healed at its second try (Run H, 2026-10-14) 22.10 → 23.04 on an EFI 22.10 desktop with stand-in Windows parts (KineticDesktop, 2026-10-16): healed, then failed on purpose and restored.</t>
         </is>
       </c>
       <c r="N18" s="12" t="inlineStr">
         <is>
-          <t>Runs under the engine's procedure service: one y/N, then the upgrade, a reboot and the check. Since 2026-10-08: one upgrade per procedure and per visit (2-2.5 h lab slots, the person there); apt checked before the y/N; Timeshift installed by the engine if missing; /boot/efi left out of the snapshot (Windows' EFI partition on the lab's dual-boot machines); a step cut off by a power-off waits for the person (--run again offers the restore). Needs a snapshot: --take-snapshot (Timeshift; restored by itself if the upgrade fails, then checked) or --snapshot &lt;name&gt;. Precondition: apt works (eos-release-dead-repos healed). Written from the upgraders' source; plain do-release-upgrade would skip 23.04/23.10 and offer 24.04 directly from 22.10, which its upgrader is not built for. Timeshift 22.06.5 to 24.01.1 refuse '--tags O', so the engine passes no tags (2b09c29). Since 2026-10-09: dpkg's lock is held around the snapshot and the restore, and the snapshot is synced to disk (74340e2). Since 2026-10-10: /var/log/dist-upgrade is left out of the snapshot, so a failed upgrade's own logs survive the restore (main.log is the only place the non-interactive upgrader writes why it failed). Also since 2026-10-10: the engine keeps 256 MB set aside while a procedure runs and frees it first when a step fails, so a full disk cannot stop the restore (seen in Run F); and -26.04 is two steps, updates + reboot, then do-release-upgrade, which refuses while a kernel or libc6 update waits for a reboot. Run F found: the upgrader can exit while a dpkg it started still runs, and the engine, which then waited only for dpkg's frontend lock, started the restore with that dpkg running. Since 2026-10-11 (seen in Run G): before a restore the engine kills every other process in its service's cgroup (named in the record, leftovers_stopped), and it holds dpkg's own lock as well as the frontend's. Visit 4 (2026-10-14) found: the non-interactive upgrader says why it stopped only in its main.log, so a held dpkg lock read as a failed upgrade and was restored. Since then each upgrade step prints the end of that log when the upgrader fails, so the engine waits and retries instead (DESIGN §16; offline only). Run H (2026-10-14) found: the box before the y is worked out before the apt check, from apt's lists as they were, so on 24.04 it can say step 1 is done when new updates wait. Step 1 then runs anyway, since its own check finds them, and adds a reboot. Since 2026-10-14 the box is worked out again after the apt check, so it shows what the steps will find (DESIGN §16; offline only).</t>
+          <t>Runs under the engine's procedure service: one y/N, then the upgrade, a reboot and the check. Since 2026-10-08: one upgrade per procedure and per visit (2-2.5 h lab slots, the person there); apt checked before the y/N; Timeshift installed by the engine if missing; /boot/efi left out of the snapshot (Windows' EFI partition on the lab's dual-boot machines); a step cut off by a power-off waits for the person (--run again offers the restore). Needs a snapshot: --take-snapshot (Timeshift; restored by itself if the upgrade fails, then checked) or --snapshot &lt;name&gt;. Precondition: apt works (eos-release-dead-repos healed). Written from the upgraders' source; plain do-release-upgrade would skip 23.04/23.10 and offer 24.04 directly from 22.10, which its upgrader is not built for. Timeshift 22.06.5 to 24.01.1 refuse '--tags O', so the engine passes no tags (2b09c29). Since 2026-10-09: dpkg's lock is held around the snapshot and the restore, and the snapshot is synced to disk (74340e2). Since 2026-10-10: /var/log/dist-upgrade is left out of the snapshot, so a failed upgrade's own logs survive the restore (main.log is the only place the non-interactive upgrader writes why it failed). Also since 2026-10-10: the engine keeps 256 MB set aside while a procedure runs and frees it first when a step fails, so a full disk cannot stop the restore (seen in Run F); and -26.04 is two steps, updates + reboot, then do-release-upgrade, which refuses while a kernel or libc6 update waits for a reboot. Run F found: the upgrader can exit while a dpkg it started still runs, and the engine, which then waited only for dpkg's frontend lock, started the restore with that dpkg running. Since 2026-10-11 (seen in Run G): before a restore the engine kills every other process in its service's cgroup (named in the record, leftovers_stopped), and it holds dpkg's own lock as well as the frontend's. Visit 4 (2026-10-14) found: the non-interactive upgrader says why it stopped only in its main.log, so a held dpkg lock read as a failed upgrade and was restored. Since then each upgrade step prints the end of that log when the upgrader fails, so the engine waits and retries instead (DESIGN §16; offline only). Run H (2026-10-14) found: the box before the y is worked out before the apt check, from apt's lists as they were, so on 24.04 it can say step 1 is done when new updates wait. Step 1 then runs anyway, since its own check finds them, and adds a reboot. Since 2026-10-14 the box is worked out again after the apt check, so it shows what the steps will find (DESIGN §16; offline only). On a desktop the upgrader runs in desktop mode whatever --mode=server says (main.log, 2026-10-16). Windows' parts unchanged by visit 1 and by its restore (check-windows.sh).</t>
         </is>
       </c>
       <c r="O18" s="12" t="inlineStr">
         <is>
-          <t>2026-10-14 · 24.04 → 26.04 · Run H, visit 4's second try: step 1 found 6 new security updates, waited out a dpkg lock held on purpose twice (the first step retry seen on a VM), installed them and rebooted (healed); step 2 upgraded to 26.04 in 24 min (healed). The lock never reached the upgrader. Before it: 2026-10-14 · 24.04 → 26.04 · Visit 4: step 1 installed 18 updates and rebooted (healed); step 2 stopped at once because unattended-upgrades held dpkg's lock, and the engine restored 24.04 (rolled_back), needlessly. Its snapshot was the first incremental one (52 s). Before it: 2026-10-11 · 24.04 · Run G (a test procedure): a failed step's leftover, holding dpkg's own lock, was stopped before the restore and named in the record; the engine waited for dpkg's own lock before its snapshot; rolled_back. Before it: 2026-10-10 · 24.04 → 26.04 · Runs E and F made the upgrade fail with a filled disk: first at the upgrader's space check, then mid-install. Both rolled_back to 24.04, the second on a full disk, from a half-upgraded machine. Before them, visits 1 to 3 healed (34, 20 and 27 min, one after the other, from repos-fixed, automatic updates on), after the machinery passed tests/procedure-proof Runs A-D.</t>
+          <t>2026-10-16 · 22.10 → 23.04 on an EFI desktop · Run 1 healed in 48 min; Run 2 filled the disk mid-install and the engine restored 22.10 in about 1.5 min; nothing of Windows' changed either time</t>
         </is>
       </c>
       <c r="P18" s="12" t="inlineStr">
         <is>
-          <t>An EFI desktop VM (22.10 desktop): the upgrades as the lab will run them. Still offline only: a lock that only the upgrader's log names.</t>
+          <t>Visit 1 on lab computer 03 (2026-10-21). Unseen on any VM: an NVIDIA driver through the upgrade; a lock that only the upgrader's log names.</t>
         </is>
       </c>
     </row>
@@ -3079,20 +3159,22 @@
       </c>
       <c r="E3" s="10" t="inlineStr">
         <is>
-          <t>Have it</t>
-        </is>
-      </c>
-      <c r="F3" s="18" t="n">
-        <v>2223</v>
+          <t>Have it (two)</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>2223 (server), 2228 (EFI desktop)</t>
+        </is>
       </c>
       <c r="G3" s="10" t="inlineStr">
         <is>
-          <t>The lab's release. The real end-of-life case for eos-release-dead-repos. Older one-line sources.list format.</t>
+          <t>The lab's release. The real end-of-life case for eos-release-dead-repos. Older one-line sources.list format. The EFI desktop VM (KineticDesktop, built 2026-10-16) is the lab's machines as they are: EFI, GNOME, the EFI partition on a second disk with stand-in Windows parts (tests/efi-proof).</t>
         </is>
       </c>
       <c r="H3" s="10" t="inlineStr">
         <is>
-          <t>(installed: 'KineticServer', from https://old-releases.ubuntu.com/releases/22.10/ubuntu-22.10-live-server-amd64.iso)</t>
+          <t>(installed: 'KineticServer', from https://old-releases.ubuntu.com/releases/22.10/ubuntu-22.10-live-server-amd64.iso); desktop: (installed: 'KineticDesktop', from ubuntu-22.10-desktop-amd64.iso, old-releases)</t>
         </is>
       </c>
       <c r="I3" s="10" t="inlineStr">
@@ -3497,7 +3579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -5713,16 +5795,244 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="165" customHeight="1">
-      <c r="A62" s="19" t="inlineStr">
-        <is>
-          <t>Times are IST (UTC+05:30). The logs themselves record UTC. Rows from 2026-09-07 23:35 to 2026-09-10 are records in evidence/ubuntu-26.04-2026-09-10.jsonl, copied off the VM on 2026-10-03; rows from 2026-10-04 are in evidence/ubuntu-26.04-2026-10-04.jsonl, rows from 2026-10-06 in evidence/ubuntu-26.04-2026-10-06.jsonl, and rows from 2026-10-07 in evidence/ubuntu-22.10-2026-10-07.jsonl and, from 12:13, evidence/ubuntu-22.10-2026-10-07-2.jsonl (the 22.10 VM, KineticServer). Rows from 2026-10-08 19:56 are the procedure runs, in evidence/ubuntu-22.10-2026-10-09.jsonl, copied from the service's own log, /var/log/sf3000/runs.jsonl. Rows from 2026-10-10 15:15 and 15:16 are lines 10 to 12 of evidence/ubuntu-22.10-2026-10-10.jsonl, whose first nine lines are the 2026-10-09 file again. Rows from 2026-10-10 16:33 are visit 1 of the upgrade, in evidence/ubuntu-22.10-2026-10-10-2.jsonl. The row from 18:40 is visit 2, line 3 of evidence/ubuntu-22.10-2026-10-10-3.jsonl, whose first two lines are visit 1's file again. The row from 20:00 is visit 3, line 4 of evidence/ubuntu-22.10-2026-10-10-4.jsonl, whose first three lines are visit 2's file again. The rows from 23:26 and 23:42 are Runs E and F, lines 5 and 6 of evidence/ubuntu-22.10-2026-10-10-5.jsonl, whose first four lines are visit 3's file again. The row from 2026-10-11 01:13 is Run G, line 7 of evidence/ubuntu-22.10-2026-10-11.jsonl, whose first six lines are the 2026-10-10 -5 file again. The rows from 2026-10-14 17:09 and 17:13 are visit 4, lines 8 and 9 of evidence/ubuntu-22.10-2026-10-14.jsonl, whose first seven lines are the 2026-10-11 file again. The rows from 2026-10-14 19:09 and 19:12 are Run H, lines 10 and 11 of evidence/ubuntu-22.10-2026-10-14-2.jsonl, whose first nine lines are the 2026-10-14 file again. Rows whose Evidence says 'Terminal output' have no record: the engine refuses before it logs anything, or the row is a sweep, which never logs. The six rows before 2026-09-07 23:35 come from commit messages: the VM's log was reset on the evening of 2026-09-07, before anyone copied it. Add one row per run from now on, pointing at its evidence file and line.</t>
-        </is>
-      </c>
+    <row r="61" ht="56" customHeight="1">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 17:10</t>
+        </is>
+      </c>
+      <c r="B61" s="10" t="inlineStr">
+        <is>
+          <t>22.10</t>
+        </is>
+      </c>
+      <c r="C61" s="10" t="inlineStr">
+        <is>
+          <t>2415fcd</t>
+        </is>
+      </c>
+      <c r="D61" s="10" t="inlineStr">
+        <is>
+          <t>engine/install</t>
+        </is>
+      </c>
+      <c r="E61" s="10" t="inlineStr">
+        <is>
+          <t>installed</t>
+        </is>
+      </c>
+      <c r="F61" s="10" t="inlineStr">
+        <is>
+          <t>Run 1 of tests/efi-proof, on KineticDesktop: an EFI 22.10 desktop VM (SSH 2228) with stand-in Windows parts on its EFI partition, from its efi-ready snapshot. The engine needed python3-jsonschema, which the desktop lacks, and installed it with apt after a y. The first such record from a VM (the server VMs ship it). A first pass answered n at the box, so the clone's logs/ also has a declined record.</t>
+        </is>
+      </c>
+      <c r="G61" s="10" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-22.10-2026-10-16.jsonl, line 1; install.log, copied off</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="56" customHeight="1">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 17:11</t>
+        </is>
+      </c>
+      <c r="B62" s="10" t="inlineStr">
+        <is>
+          <t>22.10</t>
+        </is>
+      </c>
+      <c r="C62" s="10" t="inlineStr">
+        <is>
+          <t>2415fcd</t>
+        </is>
+      </c>
+      <c r="D62" s="10" t="inlineStr">
+        <is>
+          <t>release-upgrade-to-23.04/install</t>
+        </is>
+      </c>
+      <c r="E62" s="10" t="inlineStr">
+        <is>
+          <t>installed</t>
+        </is>
+      </c>
+      <c r="F62" s="10" t="inlineStr">
+        <is>
+          <t>Run 1: Timeshift installed after the y at the box.</t>
+        </is>
+      </c>
+      <c r="G62" s="10" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-22.10-2026-10-16.jsonl, line 2; install.log, copied off</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="56" customHeight="1">
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 17:17</t>
+        </is>
+      </c>
+      <c r="B63" s="10" t="inlineStr">
+        <is>
+          <t>22.10 → 23.04</t>
+        </is>
+      </c>
+      <c r="C63" s="10" t="inlineStr">
+        <is>
+          <t>2415fcd</t>
+        </is>
+      </c>
+      <c r="D63" s="10" t="inlineStr">
+        <is>
+          <t>release-upgrade-to-23.04/to-23.04</t>
+        </is>
+      </c>
+      <c r="E63" s="10" t="inlineStr">
+        <is>
+          <t>healed</t>
+        </is>
+      </c>
+      <c r="F63" s="10" t="inlineStr">
+        <is>
+          <t>Run 1: visit 1 on an EFI desktop. Snapshot 2026-10-16_17-11-46 (5 min 14 s, a full copy of 13 GB, of 22.10 packages:af890f897a40621d). The upgrader ran in desktop mode whatever --mode=server said (main.log). Download about 13 min, install 26, then the reboot; check after: 2304. 48 min from the y. GNOME's login screen on 23.04, kernel 6.2.0-39. check-windows.sh: only EFI/ubuntu/grubx64.efi and GRUB's menu (a memtest entry) changed; every Windows part kept its hash, the boot order too.</t>
+        </is>
+      </c>
+      <c r="G63" s="10" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-22.10-2026-10-16.jsonl, line 3; the upgrader's logs, the step's log and the check-windows files (logs/kinetic-desktop-run-1), copied off</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="56" customHeight="1">
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 18:03</t>
+        </is>
+      </c>
+      <c r="B64" s="10" t="inlineStr">
+        <is>
+          <t>22.10</t>
+        </is>
+      </c>
+      <c r="C64" s="10" t="inlineStr">
+        <is>
+          <t>2415fcd</t>
+        </is>
+      </c>
+      <c r="D64" s="10" t="inlineStr">
+        <is>
+          <t>engine/install</t>
+        </is>
+      </c>
+      <c r="E64" s="10" t="inlineStr">
+        <is>
+          <t>installed</t>
+        </is>
+      </c>
+      <c r="F64" s="10" t="inlineStr">
+        <is>
+          <t>Run 2 of tests/efi-proof, on KineticDesktop back at efi-ready: python3-jsonschema installed after a y, as in Run 1.</t>
+        </is>
+      </c>
+      <c r="G64" s="10" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-22.10-2026-10-16-2.jsonl, line 1; install.log, copied off</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="56" customHeight="1">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 18:04</t>
+        </is>
+      </c>
+      <c r="B65" s="10" t="inlineStr">
+        <is>
+          <t>22.10</t>
+        </is>
+      </c>
+      <c r="C65" s="10" t="inlineStr">
+        <is>
+          <t>2415fcd</t>
+        </is>
+      </c>
+      <c r="D65" s="10" t="inlineStr">
+        <is>
+          <t>release-upgrade-to-23.04/install</t>
+        </is>
+      </c>
+      <c r="E65" s="10" t="inlineStr">
+        <is>
+          <t>installed</t>
+        </is>
+      </c>
+      <c r="F65" s="10" t="inlineStr">
+        <is>
+          <t>Run 2: Timeshift installed after the y at the box.</t>
+        </is>
+      </c>
+      <c r="G65" s="10" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-22.10-2026-10-16-2.jsonl, line 2; install.log, copied off</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="56" customHeight="1">
+      <c r="A66" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 18:10</t>
+        </is>
+      </c>
+      <c r="B66" s="10" t="inlineStr">
+        <is>
+          <t>22.10 → 23.04</t>
+        </is>
+      </c>
+      <c r="C66" s="10" t="inlineStr">
+        <is>
+          <t>2415fcd</t>
+        </is>
+      </c>
+      <c r="D66" s="10" t="inlineStr">
+        <is>
+          <t>release-upgrade-to-23.04/to-23.04</t>
+        </is>
+      </c>
+      <c r="E66" s="10" t="inlineStr">
+        <is>
+          <t>rolled_back</t>
+        </is>
+      </c>
+      <c r="F66" s="10" t="inlineStr">
+        <is>
+          <t>Run 2: visit 1 made to fail. fill-disk.py mid-install to-23.04 filled / a minute after dpkg began unpacking. dpkg failed (locales' script, then its own status), the upgrader exited 1, and the step printed the upgrader's log: the first time on a VM, with no lock in it. The engine restored at 18:28:07: Timeshift, then GRUB for x86_64-efi with no error, and update-grub found Windows. Back at 18:29:43, check: 'ok: back to 22.10 packages:af890f897a40621d'. No leftovers. check-windows.sh matched before in every line, EFI/ubuntu too.</t>
+        </is>
+      </c>
+      <c r="G66" s="10" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-22.10-2026-10-16-2.jsonl, line 3; the step's log, restore.log and the check-windows files (logs/kinetic-desktop-run-2), copied off</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="190" customHeight="1">
+      <c r="A68" s="22" t="inlineStr">
+        <is>
+          <t>Times are IST (UTC+05:30). The logs themselves record UTC. Rows from 2026-09-07 23:35 to 2026-09-10 are records in evidence/ubuntu-26.04-2026-09-10.jsonl, copied off the VM on 2026-10-03; rows from 2026-10-04 are in evidence/ubuntu-26.04-2026-10-04.jsonl, rows from 2026-10-06 in evidence/ubuntu-26.04-2026-10-06.jsonl, and rows from 2026-10-07 in evidence/ubuntu-22.10-2026-10-07.jsonl and, from 12:13, evidence/ubuntu-22.10-2026-10-07-2.jsonl (the 22.10 VM, KineticServer). Rows from 2026-10-08 19:56 are the procedure runs, in evidence/ubuntu-22.10-2026-10-09.jsonl, copied from the service's own log, /var/log/sf3000/runs.jsonl. Rows from 2026-10-10 15:15 and 15:16 are lines 10 to 12 of evidence/ubuntu-22.10-2026-10-10.jsonl, whose first nine lines are the 2026-10-09 file again. Rows from 2026-10-10 16:33 are visit 1 of the upgrade, in evidence/ubuntu-22.10-2026-10-10-2.jsonl. The row from 18:40 is visit 2, line 3 of evidence/ubuntu-22.10-2026-10-10-3.jsonl, whose first two lines are visit 1's file again. The row from 20:00 is visit 3, line 4 of evidence/ubuntu-22.10-2026-10-10-4.jsonl, whose first three lines are visit 2's file again. The rows from 23:26 and 23:42 are Runs E and F, lines 5 and 6 of evidence/ubuntu-22.10-2026-10-10-5.jsonl, whose first four lines are visit 3's file again. The row from 2026-10-11 01:13 is Run G, line 7 of evidence/ubuntu-22.10-2026-10-11.jsonl, whose first six lines are the 2026-10-10 -5 file again. The rows from 2026-10-14 17:09 and 17:13 are visit 4, lines 8 and 9 of evidence/ubuntu-22.10-2026-10-14.jsonl, whose first seven lines are the 2026-10-11 file again. The rows from 2026-10-14 19:09 and 19:12 are Run H, lines 10 and 11 of evidence/ubuntu-22.10-2026-10-14-2.jsonl, whose first nine lines are the 2026-10-14 file again. Rows whose Evidence says 'Terminal output' have no record: the engine refuses before it logs anything, or the row is a sweep, which never logs. The six rows before 2026-09-07 23:35 come from commit messages: the VM's log was reset on the evening of 2026-09-07, before anyone copied it. Add one row per run from now on, pointing at its evidence file and line. The rows from 2026-10-16 17:10 to 17:17 are Run 1 of tests/efi-proof on KineticDesktop, an EFI 22.10 desktop VM, lines 1 to 3 of evidence/ubuntu-22.10-2026-10-16.jsonl. The rows from 18:03 to 18:10 are Run 2, lines 1 to 3 of evidence/ubuntu-22.10-2026-10-16-2.jsonl: a file of its own, because the VM went back to its efi-ready snapshot between the runs.</t>
+        </is>
+      </c>
+      <c r="B68" s="23" t="n"/>
+      <c r="C68" s="23" t="n"/>
+      <c r="D68" s="23" t="n"/>
+      <c r="E68" s="23" t="n"/>
+      <c r="F68" s="23" t="n"/>
+      <c r="G68" s="24" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A62:G62"/>
+    <mergeCell ref="A68:G68"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/sf3000-tracker.xlsx
+++ b/docs/sf3000-tracker.xlsx
@@ -2218,22 +2218,22 @@
       <c r="L18" s="12" t="n"/>
       <c r="M18" s="12" t="inlineStr">
         <is>
-          <t>Ubuntu 22.10 (kinetic) → 23.04 (lunar) → 23.10 (mantic) → 24.04 (noble): visits 1 to 3; 24.04 → 26.04 (resolute) made to fail twice: Runs E and F; visit 4 restored after a held lock (2026-10-14); visit 4 healed at its second try (Run H, 2026-10-14) 22.10 → 23.04 on an EFI 22.10 desktop with stand-in Windows parts (KineticDesktop, 2026-10-16): healed, then failed on purpose and restored.</t>
+          <t>Ubuntu 22.10 (kinetic) → 23.04 (lunar) → 23.10 (mantic) → 24.04 (noble): visits 1 to 3; 24.04 → 26.04 (resolute) made to fail twice: Runs E and F; visit 4 restored after a held lock (2026-10-14); visit 4 healed at its second try (Run H, 2026-10-14) 22.10 → 23.04 on an EFI 22.10 desktop with stand-in Windows parts (KineticDesktop, 2026-10-16): healed, then failed on purpose and restored. With 03's NVIDIA 535 packages too (Run 3, 2026-10-16): healed; apt built the driver with dkms.</t>
         </is>
       </c>
       <c r="N18" s="12" t="inlineStr">
         <is>
-          <t>Runs under the engine's procedure service: one y/N, then the upgrade, a reboot and the check. Since 2026-10-08: one upgrade per procedure and per visit (2-2.5 h lab slots, the person there); apt checked before the y/N; Timeshift installed by the engine if missing; /boot/efi left out of the snapshot (Windows' EFI partition on the lab's dual-boot machines); a step cut off by a power-off waits for the person (--run again offers the restore). Needs a snapshot: --take-snapshot (Timeshift; restored by itself if the upgrade fails, then checked) or --snapshot &lt;name&gt;. Precondition: apt works (eos-release-dead-repos healed). Written from the upgraders' source; plain do-release-upgrade would skip 23.04/23.10 and offer 24.04 directly from 22.10, which its upgrader is not built for. Timeshift 22.06.5 to 24.01.1 refuse '--tags O', so the engine passes no tags (2b09c29). Since 2026-10-09: dpkg's lock is held around the snapshot and the restore, and the snapshot is synced to disk (74340e2). Since 2026-10-10: /var/log/dist-upgrade is left out of the snapshot, so a failed upgrade's own logs survive the restore (main.log is the only place the non-interactive upgrader writes why it failed). Also since 2026-10-10: the engine keeps 256 MB set aside while a procedure runs and frees it first when a step fails, so a full disk cannot stop the restore (seen in Run F); and -26.04 is two steps, updates + reboot, then do-release-upgrade, which refuses while a kernel or libc6 update waits for a reboot. Run F found: the upgrader can exit while a dpkg it started still runs, and the engine, which then waited only for dpkg's frontend lock, started the restore with that dpkg running. Since 2026-10-11 (seen in Run G): before a restore the engine kills every other process in its service's cgroup (named in the record, leftovers_stopped), and it holds dpkg's own lock as well as the frontend's. Visit 4 (2026-10-14) found: the non-interactive upgrader says why it stopped only in its main.log, so a held dpkg lock read as a failed upgrade and was restored. Since then each upgrade step prints the end of that log when the upgrader fails, so the engine waits and retries instead (DESIGN §16; offline only). Run H (2026-10-14) found: the box before the y is worked out before the apt check, from apt's lists as they were, so on 24.04 it can say step 1 is done when new updates wait. Step 1 then runs anyway, since its own check finds them, and adds a reboot. Since 2026-10-14 the box is worked out again after the apt check, so it shows what the steps will find (DESIGN §16; offline only). On a desktop the upgrader runs in desktop mode whatever --mode=server says (main.log, 2026-10-16). Windows' parts unchanged by visit 1 and by its restore (check-windows.sh).</t>
+          <t>Runs under the engine's procedure service: one y/N, then the upgrade, a reboot and the check. Since 2026-10-08: one upgrade per procedure and per visit (2-2.5 h lab slots, the person there); apt checked before the y/N; Timeshift installed by the engine if missing; /boot/efi left out of the snapshot (Windows' EFI partition on the lab's dual-boot machines); a step cut off by a power-off waits for the person (--run again offers the restore). Needs a snapshot: --take-snapshot (Timeshift; restored by itself if the upgrade fails, then checked) or --snapshot &lt;name&gt;. Precondition: apt works (eos-release-dead-repos healed). Written from the upgraders' source; plain do-release-upgrade would skip 23.04/23.10 and offer 24.04 directly from 22.10, which its upgrader is not built for. Timeshift 22.06.5 to 24.01.1 refuse '--tags O', so the engine passes no tags (2b09c29). Since 2026-10-09: dpkg's lock is held around the snapshot and the restore, and the snapshot is synced to disk (74340e2). Since 2026-10-10: /var/log/dist-upgrade is left out of the snapshot, so a failed upgrade's own logs survive the restore (main.log is the only place the non-interactive upgrader writes why it failed). Also since 2026-10-10: the engine keeps 256 MB set aside while a procedure runs and frees it first when a step fails, so a full disk cannot stop the restore (seen in Run F); and -26.04 is two steps, updates + reboot, then do-release-upgrade, which refuses while a kernel or libc6 update waits for a reboot. Run F found: the upgrader can exit while a dpkg it started still runs, and the engine, which then waited only for dpkg's frontend lock, started the restore with that dpkg running. Since 2026-10-11 (seen in Run G): before a restore the engine kills every other process in its service's cgroup (named in the record, leftovers_stopped), and it holds dpkg's own lock as well as the frontend's. Visit 4 (2026-10-14) found: the non-interactive upgrader says why it stopped only in its main.log, so a held dpkg lock read as a failed upgrade and was restored. Since then each upgrade step prints the end of that log when the upgrader fails, so the engine waits and retries instead (DESIGN §16; offline only). Run H (2026-10-14) found: the box before the y is worked out before the apt check, from apt's lists as they were, so on 24.04 it can say step 1 is done when new updates wait. Step 1 then runs anyway, since its own check finds them, and adds a reboot. Since 2026-10-14 the box is worked out again after the apt check, so it shows what the steps will find (DESIGN §16; offline only). On a desktop the upgrader runs in desktop mode whatever --mode=server says (main.log, 2026-10-16). Windows' parts unchanged by visit 1 and by its restore (check-windows.sh). NVIDIA 535 on 23.04: the last prebuilt module needs 535.154.05, never released for 23.04, so the upgrade installs nvidia-dkms-535 535.146.02 and builds the module (needs kernel headers); 23.10 fits together again.</t>
         </is>
       </c>
       <c r="O18" s="12" t="inlineStr">
         <is>
-          <t>2026-10-16 · 22.10 → 23.04 on an EFI desktop · Run 1 healed in 48 min; Run 2 filled the disk mid-install and the engine restored 22.10 in about 1.5 min; nothing of Windows' changed either time</t>
+          <t>2026-10-16 · 22.10 → 23.04 on an EFI desktop · Run 1 healed in 48 min; Run 2 failed on purpose and was restored; Run 3, with 03's NVIDIA packages, healed in 74 min with the driver built by dkms; nothing of Windows' changed</t>
         </is>
       </c>
       <c r="P18" s="12" t="inlineStr">
         <is>
-          <t>Visit 1 on lab computer 03 (2026-10-21). Unseen on any VM: an NVIDIA driver through the upgrade; a lock that only the upgrader's log names.</t>
+          <t>Visit 1 on lab computer 03 (2026-10-21): check headers and Secure Boot first; after, nvidia-smi and dkms status. Unseen on any VM: the module loading on a real NVIDIA card; a lock that only the upgrader's log names.</t>
         </is>
       </c>
     </row>
@@ -3661,7 +3661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -6321,31 +6321,142 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="10" t="n"/>
-      <c r="B73" s="10" t="n"/>
-      <c r="C73" s="10" t="n"/>
-      <c r="D73" s="10" t="n"/>
-      <c r="E73" s="10" t="n"/>
-      <c r="F73" s="10" t="n"/>
-      <c r="G73" s="10" t="n"/>
-    </row>
-    <row r="74" ht="210" customHeight="1">
-      <c r="A74" s="22" t="inlineStr">
-        <is>
-          <t>Times are IST (UTC+05:30). The logs themselves record UTC. Rows from 2026-09-07 23:35 to 2026-09-10 are records in evidence/ubuntu-26.04-2026-09-10.jsonl, copied off the VM on 2026-10-03; rows from 2026-10-04 are in evidence/ubuntu-26.04-2026-10-04.jsonl, rows from 2026-10-06 in evidence/ubuntu-26.04-2026-10-06.jsonl, and rows from 2026-10-07 in evidence/ubuntu-22.10-2026-10-07.jsonl and, from 12:13, evidence/ubuntu-22.10-2026-10-07-2.jsonl (the 22.10 VM, KineticServer). Rows from 2026-10-08 19:56 are the procedure runs, in evidence/ubuntu-22.10-2026-10-09.jsonl, copied from the service's own log, /var/log/sf3000/runs.jsonl. Rows from 2026-10-10 15:15 and 15:16 are lines 10 to 12 of evidence/ubuntu-22.10-2026-10-10.jsonl, whose first nine lines are the 2026-10-09 file again. Rows from 2026-10-10 16:33 are visit 1 of the upgrade, in evidence/ubuntu-22.10-2026-10-10-2.jsonl. The row from 18:40 is visit 2, line 3 of evidence/ubuntu-22.10-2026-10-10-3.jsonl, whose first two lines are visit 1's file again. The row from 20:00 is visit 3, line 4 of evidence/ubuntu-22.10-2026-10-10-4.jsonl, whose first three lines are visit 2's file again. The rows from 23:26 and 23:42 are Runs E and F, lines 5 and 6 of evidence/ubuntu-22.10-2026-10-10-5.jsonl, whose first four lines are visit 3's file again. The row from 2026-10-11 01:13 is Run G, line 7 of evidence/ubuntu-22.10-2026-10-11.jsonl, whose first six lines are the 2026-10-10 -5 file again. The rows from 2026-10-14 17:09 and 17:13 are visit 4, lines 8 and 9 of evidence/ubuntu-22.10-2026-10-14.jsonl, whose first seven lines are the 2026-10-11 file again. The rows from 2026-10-14 19:09 and 19:12 are Run H, lines 10 and 11 of evidence/ubuntu-22.10-2026-10-14-2.jsonl, whose first nine lines are the 2026-10-14 file again. Rows whose Evidence says 'Terminal output' have no record: the engine refuses before it logs anything, or the row is a sweep, which never logs. The six rows before 2026-09-07 23:35 come from commit messages: the VM's log was reset on the evening of 2026-09-07, before anyone copied it. Add one row per run from now on, pointing at its evidence file and line. The rows from 2026-10-16 17:10 to 17:17 are Run 1 of tests/efi-proof on KineticDesktop, an EFI 22.10 desktop VM, lines 1 to 3 of evidence/ubuntu-22.10-2026-10-16.jsonl. The rows from 18:03 to 18:10 are Run 2, lines 1 to 3 of evidence/ubuntu-22.10-2026-10-16-2.jsonl: a file of its own, because the VM went back to its efi-ready snapshot between the runs. The rows from 2026-10-16 19:29 to 19:46 are tests/grub-windows-proof on KineticDesktop, one record each in evidence/ubuntu-22.10-2026-10-16-3.jsonl to -8.jsonl: each run began from a snapshot restore, which deletes the clone's run log.</t>
-        </is>
-      </c>
-      <c r="B74" s="23" t="n"/>
-      <c r="C74" s="23" t="n"/>
-      <c r="D74" s="23" t="n"/>
-      <c r="E74" s="23" t="n"/>
-      <c r="F74" s="23" t="n"/>
-      <c r="G74" s="24" t="n"/>
+    <row r="73" ht="56" customHeight="1">
+      <c r="A73" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 20:02</t>
+        </is>
+      </c>
+      <c r="B73" s="10" t="inlineStr">
+        <is>
+          <t>22.10</t>
+        </is>
+      </c>
+      <c r="C73" s="10" t="inlineStr">
+        <is>
+          <t>2415fcd</t>
+        </is>
+      </c>
+      <c r="D73" s="10" t="inlineStr">
+        <is>
+          <t>engine/install</t>
+        </is>
+      </c>
+      <c r="E73" s="10" t="inlineStr">
+        <is>
+          <t>installed</t>
+        </is>
+      </c>
+      <c r="F73" s="10" t="inlineStr">
+        <is>
+          <t>Run 3 of tests/efi-proof, on KineticDesktop from VBox snapshot efi-nvidia: efi-ready plus lab computer 03's NVIDIA packages at 03's versions (nvidia-driver-535 535.54.03, prebuilt linux-modules-nvidia-535-generic-hwe-22.04 5.19.0-46, no dkms). python3-jsonschema installed after a y.</t>
+        </is>
+      </c>
+      <c r="G73" s="10" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-22.10-2026-10-16-9.jsonl, line 1; install.log, copied off</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="56" customHeight="1">
+      <c r="A74" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 20:03</t>
+        </is>
+      </c>
+      <c r="B74" s="10" t="inlineStr">
+        <is>
+          <t>22.10</t>
+        </is>
+      </c>
+      <c r="C74" s="10" t="inlineStr">
+        <is>
+          <t>2415fcd</t>
+        </is>
+      </c>
+      <c r="D74" s="10" t="inlineStr">
+        <is>
+          <t>release-upgrade-to-23.04/install</t>
+        </is>
+      </c>
+      <c r="E74" s="10" t="inlineStr">
+        <is>
+          <t>installed</t>
+        </is>
+      </c>
+      <c r="F74" s="10" t="inlineStr">
+        <is>
+          <t>Run 3: Timeshift installed after the y at the box.</t>
+        </is>
+      </c>
+      <c r="G74" s="10" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-22.10-2026-10-16-9.jsonl, line 2; install.log, copied off</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="56" customHeight="1">
+      <c r="A75" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 20:08</t>
+        </is>
+      </c>
+      <c r="B75" s="10" t="inlineStr">
+        <is>
+          <t>22.10 → 23.04</t>
+        </is>
+      </c>
+      <c r="C75" s="10" t="inlineStr">
+        <is>
+          <t>2415fcd</t>
+        </is>
+      </c>
+      <c r="D75" s="10" t="inlineStr">
+        <is>
+          <t>release-upgrade-to-23.04/to-23.04</t>
+        </is>
+      </c>
+      <c r="E75" s="10" t="inlineStr">
+        <is>
+          <t>healed</t>
+        </is>
+      </c>
+      <c r="F75" s="10" t="inlineStr">
+        <is>
+          <t>Run 3: visit 1 with 03's NVIDIA packages. Snapshot 2026-10-16_20-03-04 (6 min, of 22.10 packages:758d752e41e5d906). 23.04's last prebuilt module needs driver 535.154.05, which 23.04 never got, so apt installed nvidia-dkms-535 535.146.02 with dkms and a compiler; dkms built the module for 6.2.0-39 and 5.19.0-46, matching the driver. Main install pass 34 min (17 in Run 1). Check after: 2304; 74 min from the y. GNOME's login screen; the VM has no NVIDIA card. check-windows.sh: the same two Ubuntu changes as Run 1, nothing else.</t>
+        </is>
+      </c>
+      <c r="G75" s="10" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-22.10-2026-10-16-9.jsonl, line 3; the upgrader's logs, dkms status and the check-windows files (logs/kinetic-desktop-run-3), copied off</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="10" t="n"/>
+      <c r="B76" s="10" t="n"/>
+      <c r="C76" s="10" t="n"/>
+      <c r="D76" s="10" t="n"/>
+      <c r="E76" s="10" t="n"/>
+      <c r="F76" s="10" t="n"/>
+      <c r="G76" s="10" t="n"/>
+    </row>
+    <row r="77" ht="225" customHeight="1">
+      <c r="A77" s="22" t="inlineStr">
+        <is>
+          <t>Times are IST (UTC+05:30). The logs themselves record UTC. Rows from 2026-09-07 23:35 to 2026-09-10 are records in evidence/ubuntu-26.04-2026-09-10.jsonl, copied off the VM on 2026-10-03; rows from 2026-10-04 are in evidence/ubuntu-26.04-2026-10-04.jsonl, rows from 2026-10-06 in evidence/ubuntu-26.04-2026-10-06.jsonl, and rows from 2026-10-07 in evidence/ubuntu-22.10-2026-10-07.jsonl and, from 12:13, evidence/ubuntu-22.10-2026-10-07-2.jsonl (the 22.10 VM, KineticServer). Rows from 2026-10-08 19:56 are the procedure runs, in evidence/ubuntu-22.10-2026-10-09.jsonl, copied from the service's own log, /var/log/sf3000/runs.jsonl. Rows from 2026-10-10 15:15 and 15:16 are lines 10 to 12 of evidence/ubuntu-22.10-2026-10-10.jsonl, whose first nine lines are the 2026-10-09 file again. Rows from 2026-10-10 16:33 are visit 1 of the upgrade, in evidence/ubuntu-22.10-2026-10-10-2.jsonl. The row from 18:40 is visit 2, line 3 of evidence/ubuntu-22.10-2026-10-10-3.jsonl, whose first two lines are visit 1's file again. The row from 20:00 is visit 3, line 4 of evidence/ubuntu-22.10-2026-10-10-4.jsonl, whose first three lines are visit 2's file again. The rows from 23:26 and 23:42 are Runs E and F, lines 5 and 6 of evidence/ubuntu-22.10-2026-10-10-5.jsonl, whose first four lines are visit 3's file again. The row from 2026-10-11 01:13 is Run G, line 7 of evidence/ubuntu-22.10-2026-10-11.jsonl, whose first six lines are the 2026-10-10 -5 file again. The rows from 2026-10-14 17:09 and 17:13 are visit 4, lines 8 and 9 of evidence/ubuntu-22.10-2026-10-14.jsonl, whose first seven lines are the 2026-10-11 file again. The rows from 2026-10-14 19:09 and 19:12 are Run H, lines 10 and 11 of evidence/ubuntu-22.10-2026-10-14-2.jsonl, whose first nine lines are the 2026-10-14 file again. Rows whose Evidence says 'Terminal output' have no record: the engine refuses before it logs anything, or the row is a sweep, which never logs. The six rows before 2026-09-07 23:35 come from commit messages: the VM's log was reset on the evening of 2026-09-07, before anyone copied it. Add one row per run from now on, pointing at its evidence file and line. The rows from 2026-10-16 17:10 to 17:17 are Run 1 of tests/efi-proof on KineticDesktop, an EFI 22.10 desktop VM, lines 1 to 3 of evidence/ubuntu-22.10-2026-10-16.jsonl. The rows from 18:03 to 18:10 are Run 2, lines 1 to 3 of evidence/ubuntu-22.10-2026-10-16-2.jsonl: a file of its own, because the VM went back to its efi-ready snapshot between the runs. The rows from 2026-10-16 19:29 to 19:46 are tests/grub-windows-proof on KineticDesktop, one record each in evidence/ubuntu-22.10-2026-10-16-3.jsonl to -8.jsonl: each run began from a snapshot restore, which deletes the clone's run log. The rows from 2026-10-16 20:02 to 20:08 are Run 3 of tests/efi-proof, with 03's NVIDIA packages, lines 1 to 3 of evidence/ubuntu-22.10-2026-10-16-9.jsonl.</t>
+        </is>
+      </c>
+      <c r="B77" s="23" t="n"/>
+      <c r="C77" s="23" t="n"/>
+      <c r="D77" s="23" t="n"/>
+      <c r="E77" s="23" t="n"/>
+      <c r="F77" s="23" t="n"/>
+      <c r="G77" s="24" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A74:G74"/>
+    <mergeCell ref="A77:G77"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/sf3000-tracker.xlsx
+++ b/docs/sf3000-tracker.xlsx
@@ -3661,7 +3661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -6432,31 +6432,142 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="10" t="n"/>
-      <c r="B76" s="10" t="n"/>
-      <c r="C76" s="10" t="n"/>
-      <c r="D76" s="10" t="n"/>
-      <c r="E76" s="10" t="n"/>
-      <c r="F76" s="10" t="n"/>
-      <c r="G76" s="10" t="n"/>
-    </row>
-    <row r="77" ht="225" customHeight="1">
-      <c r="A77" s="22" t="inlineStr">
-        <is>
-          <t>Times are IST (UTC+05:30). The logs themselves record UTC. Rows from 2026-09-07 23:35 to 2026-09-10 are records in evidence/ubuntu-26.04-2026-09-10.jsonl, copied off the VM on 2026-10-03; rows from 2026-10-04 are in evidence/ubuntu-26.04-2026-10-04.jsonl, rows from 2026-10-06 in evidence/ubuntu-26.04-2026-10-06.jsonl, and rows from 2026-10-07 in evidence/ubuntu-22.10-2026-10-07.jsonl and, from 12:13, evidence/ubuntu-22.10-2026-10-07-2.jsonl (the 22.10 VM, KineticServer). Rows from 2026-10-08 19:56 are the procedure runs, in evidence/ubuntu-22.10-2026-10-09.jsonl, copied from the service's own log, /var/log/sf3000/runs.jsonl. Rows from 2026-10-10 15:15 and 15:16 are lines 10 to 12 of evidence/ubuntu-22.10-2026-10-10.jsonl, whose first nine lines are the 2026-10-09 file again. Rows from 2026-10-10 16:33 are visit 1 of the upgrade, in evidence/ubuntu-22.10-2026-10-10-2.jsonl. The row from 18:40 is visit 2, line 3 of evidence/ubuntu-22.10-2026-10-10-3.jsonl, whose first two lines are visit 1's file again. The row from 20:00 is visit 3, line 4 of evidence/ubuntu-22.10-2026-10-10-4.jsonl, whose first three lines are visit 2's file again. The rows from 23:26 and 23:42 are Runs E and F, lines 5 and 6 of evidence/ubuntu-22.10-2026-10-10-5.jsonl, whose first four lines are visit 3's file again. The row from 2026-10-11 01:13 is Run G, line 7 of evidence/ubuntu-22.10-2026-10-11.jsonl, whose first six lines are the 2026-10-10 -5 file again. The rows from 2026-10-14 17:09 and 17:13 are visit 4, lines 8 and 9 of evidence/ubuntu-22.10-2026-10-14.jsonl, whose first seven lines are the 2026-10-11 file again. The rows from 2026-10-14 19:09 and 19:12 are Run H, lines 10 and 11 of evidence/ubuntu-22.10-2026-10-14-2.jsonl, whose first nine lines are the 2026-10-14 file again. Rows whose Evidence says 'Terminal output' have no record: the engine refuses before it logs anything, or the row is a sweep, which never logs. The six rows before 2026-09-07 23:35 come from commit messages: the VM's log was reset on the evening of 2026-09-07, before anyone copied it. Add one row per run from now on, pointing at its evidence file and line. The rows from 2026-10-16 17:10 to 17:17 are Run 1 of tests/efi-proof on KineticDesktop, an EFI 22.10 desktop VM, lines 1 to 3 of evidence/ubuntu-22.10-2026-10-16.jsonl. The rows from 18:03 to 18:10 are Run 2, lines 1 to 3 of evidence/ubuntu-22.10-2026-10-16-2.jsonl: a file of its own, because the VM went back to its efi-ready snapshot between the runs. The rows from 2026-10-16 19:29 to 19:46 are tests/grub-windows-proof on KineticDesktop, one record each in evidence/ubuntu-22.10-2026-10-16-3.jsonl to -8.jsonl: each run began from a snapshot restore, which deletes the clone's run log. The rows from 2026-10-16 20:02 to 20:08 are Run 3 of tests/efi-proof, with 03's NVIDIA packages, lines 1 to 3 of evidence/ubuntu-22.10-2026-10-16-9.jsonl.</t>
-        </is>
-      </c>
-      <c r="B77" s="23" t="n"/>
-      <c r="C77" s="23" t="n"/>
-      <c r="D77" s="23" t="n"/>
-      <c r="E77" s="23" t="n"/>
-      <c r="F77" s="23" t="n"/>
-      <c r="G77" s="24" t="n"/>
+    <row r="76" ht="56" customHeight="1">
+      <c r="A76" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 22:07</t>
+        </is>
+      </c>
+      <c r="B76" s="10" t="inlineStr">
+        <is>
+          <t>22.10</t>
+        </is>
+      </c>
+      <c r="C76" s="10" t="inlineStr">
+        <is>
+          <t>d4a34a0</t>
+        </is>
+      </c>
+      <c r="D76" s="10" t="inlineStr">
+        <is>
+          <t>engine/install</t>
+        </is>
+      </c>
+      <c r="E76" s="10" t="inlineStr">
+        <is>
+          <t>installed</t>
+        </is>
+      </c>
+      <c r="F76" s="10" t="inlineStr">
+        <is>
+          <t>The lab kit's new scripts on KineticDesktop from efi-nvidia, in visit day's order: 2-get-engine (pulled to d4a34a0), 6-before-visit (STOP: no jsonschema), then 3-sweep installed python3-jsonschema after a y.</t>
+        </is>
+      </c>
+      <c r="G76" s="10" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-22.10-2026-10-16-10.jsonl, line 1; the kit's out folder, copied off</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="56" customHeight="1">
+      <c r="A77" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 22:10</t>
+        </is>
+      </c>
+      <c r="B77" s="10" t="inlineStr">
+        <is>
+          <t>22.10</t>
+        </is>
+      </c>
+      <c r="C77" s="10" t="inlineStr">
+        <is>
+          <t>d4a34a0</t>
+        </is>
+      </c>
+      <c r="D77" s="10" t="inlineStr">
+        <is>
+          <t>cut-off-proof/install</t>
+        </is>
+      </c>
+      <c r="E77" s="10" t="inlineStr">
+        <is>
+          <t>installed</t>
+        </is>
+      </c>
+      <c r="F77" s="10" t="inlineStr">
+        <is>
+          <t>Before the real cut-off: Timeshift installed for cut-off-proof --take-snapshot.</t>
+        </is>
+      </c>
+      <c r="G77" s="10" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-22.10-2026-10-16-10.jsonl, line 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="56" customHeight="1">
+      <c r="A78" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-16 22:15</t>
+        </is>
+      </c>
+      <c r="B78" s="10" t="inlineStr">
+        <is>
+          <t>22.10</t>
+        </is>
+      </c>
+      <c r="C78" s="10" t="inlineStr">
+        <is>
+          <t>d4a34a0</t>
+        </is>
+      </c>
+      <c r="D78" s="10" t="inlineStr">
+        <is>
+          <t>cut-off-proof/long</t>
+        </is>
+      </c>
+      <c r="E78" s="10" t="inlineStr">
+        <is>
+          <t>interrupted</t>
+        </is>
+      </c>
+      <c r="F78" s="10" t="inlineStr">
+        <is>
+          <t>--cancel after a real cut-off, the first on a VM: the VM powered off a minute into step long; the boot after held it (cut_off) and the kit's 6-before-visit said STOP. sudo python3 engine/runner.py --cancel asked nothing and recorded 'not attempted: cancelled by hand; Timeshift snapshot 2026-10-16_22-10-13 kept'. Nothing restored; the snapshot kept. Then 6 said READY. Lab computer 03's first step on 2026-10-21. (The timestamp is the step's start.)</t>
+        </is>
+      </c>
+      <c r="G78" s="10" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-22.10-2026-10-16-10.jsonl, line 3; journal and kit output (logs/kinetic-desktop-cancel), copied off</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="10" t="n"/>
+      <c r="B79" s="10" t="n"/>
+      <c r="C79" s="10" t="n"/>
+      <c r="D79" s="10" t="n"/>
+      <c r="E79" s="10" t="n"/>
+      <c r="F79" s="10" t="n"/>
+      <c r="G79" s="10" t="n"/>
+    </row>
+    <row r="80" ht="240" customHeight="1">
+      <c r="A80" s="22" t="inlineStr">
+        <is>
+          <t>Times are IST (UTC+05:30). The logs themselves record UTC. Rows from 2026-09-07 23:35 to 2026-09-10 are records in evidence/ubuntu-26.04-2026-09-10.jsonl, copied off the VM on 2026-10-03; rows from 2026-10-04 are in evidence/ubuntu-26.04-2026-10-04.jsonl, rows from 2026-10-06 in evidence/ubuntu-26.04-2026-10-06.jsonl, and rows from 2026-10-07 in evidence/ubuntu-22.10-2026-10-07.jsonl and, from 12:13, evidence/ubuntu-22.10-2026-10-07-2.jsonl (the 22.10 VM, KineticServer). Rows from 2026-10-08 19:56 are the procedure runs, in evidence/ubuntu-22.10-2026-10-09.jsonl, copied from the service's own log, /var/log/sf3000/runs.jsonl. Rows from 2026-10-10 15:15 and 15:16 are lines 10 to 12 of evidence/ubuntu-22.10-2026-10-10.jsonl, whose first nine lines are the 2026-10-09 file again. Rows from 2026-10-10 16:33 are visit 1 of the upgrade, in evidence/ubuntu-22.10-2026-10-10-2.jsonl. The row from 18:40 is visit 2, line 3 of evidence/ubuntu-22.10-2026-10-10-3.jsonl, whose first two lines are visit 1's file again. The row from 20:00 is visit 3, line 4 of evidence/ubuntu-22.10-2026-10-10-4.jsonl, whose first three lines are visit 2's file again. The rows from 23:26 and 23:42 are Runs E and F, lines 5 and 6 of evidence/ubuntu-22.10-2026-10-10-5.jsonl, whose first four lines are visit 3's file again. The row from 2026-10-11 01:13 is Run G, line 7 of evidence/ubuntu-22.10-2026-10-11.jsonl, whose first six lines are the 2026-10-10 -5 file again. The rows from 2026-10-14 17:09 and 17:13 are visit 4, lines 8 and 9 of evidence/ubuntu-22.10-2026-10-14.jsonl, whose first seven lines are the 2026-10-11 file again. The rows from 2026-10-14 19:09 and 19:12 are Run H, lines 10 and 11 of evidence/ubuntu-22.10-2026-10-14-2.jsonl, whose first nine lines are the 2026-10-14 file again. Rows whose Evidence says 'Terminal output' have no record: the engine refuses before it logs anything, or the row is a sweep, which never logs. The six rows before 2026-09-07 23:35 come from commit messages: the VM's log was reset on the evening of 2026-09-07, before anyone copied it. Add one row per run from now on, pointing at its evidence file and line. The rows from 2026-10-16 17:10 to 17:17 are Run 1 of tests/efi-proof on KineticDesktop, an EFI 22.10 desktop VM, lines 1 to 3 of evidence/ubuntu-22.10-2026-10-16.jsonl. The rows from 18:03 to 18:10 are Run 2, lines 1 to 3 of evidence/ubuntu-22.10-2026-10-16-2.jsonl: a file of its own, because the VM went back to its efi-ready snapshot between the runs. The rows from 2026-10-16 19:29 to 19:46 are tests/grub-windows-proof on KineticDesktop, one record each in evidence/ubuntu-22.10-2026-10-16-3.jsonl to -8.jsonl: each run began from a snapshot restore, which deletes the clone's run log. The rows from 2026-10-16 20:02 to 20:08 are Run 3 of tests/efi-proof, with 03's NVIDIA packages, lines 1 to 3 of evidence/ubuntu-22.10-2026-10-16-9.jsonl. The rows from 2026-10-16 22:07 to 22:15 are the lab kit's test and --cancel after a real cut-off, lines 1 to 3 of evidence/ubuntu-22.10-2026-10-16-10.jsonl.</t>
+        </is>
+      </c>
+      <c r="B80" s="23" t="n"/>
+      <c r="C80" s="23" t="n"/>
+      <c r="D80" s="23" t="n"/>
+      <c r="E80" s="23" t="n"/>
+      <c r="F80" s="23" t="n"/>
+      <c r="G80" s="24" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A77:G77"/>
+    <mergeCell ref="A80:G80"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/sf3000-tracker.xlsx
+++ b/docs/sf3000-tracker.xlsx
@@ -2207,18 +2207,18 @@
       </c>
       <c r="J18" s="12" t="inlineStr">
         <is>
-          <t>Proven for release-upgrade-to-23.04, -23.10 and -24.04 (22.10 VM, 2026-10-10): their requires read kinetic, lunar and mantic, and their detects read 2210 then 2304, 2304 then 2310, and 2310 then 2404. -26.04 ran twice, made to fail (Runs E and F, 2026-10-10): its requires read noble; step 1's check (apt-get -s full-upgrade, plus a waiting reboot) read 0 both times, so step 1 was skipped; step 2's detect read 2404 before. Not yet healed. On 2026-10-14 (visit 4), -26.04's step 1 check read 19 (18 updates and a faked waiting kernel), then 0 after its reboot: the first time it ran. In Run H (2026-10-14), -26.04's step 1 check read 6 (new security updates), then 0 after its reboot; step 2's detect read 2404, then 2604 after its reboot. release-upgrade-to-23.04 also on an EFI 22.10 desktop (2026-10-16): 2210 then 2304.</t>
+          <t>Proven for release-upgrade-to-23.04, -23.10 and -24.04 (22.10 VM, 2026-10-10): their requires read kinetic, lunar and mantic, and their detects read 2210 then 2304, 2304 then 2310, and 2310 then 2404. -26.04 ran twice, made to fail (Runs E and F, 2026-10-10): its requires read noble; step 1's check (apt-get -s full-upgrade, plus a waiting reboot) read 0 both times, so step 1 was skipped; step 2's detect read 2404 before. Not yet healed. On 2026-10-14 (visit 4), -26.04's step 1 check read 19 (18 updates and a faked waiting kernel), then 0 after its reboot: the first time it ran. In Run H (2026-10-14), -26.04's step 1 check read 6 (new security updates), then 0 after its reboot; step 2's detect read 2404, then 2604 after its reboot. release-upgrade-to-23.04 also on an EFI 22.10 desktop (2026-10-16): 2210 then 2304. On lab computer MITB-IT-406-03 (2026-10-21): release-upgrade-to-23.04's detect read 2210, then 2304 after its reboot.</t>
         </is>
       </c>
       <c r="K18" s="12" t="inlineStr">
         <is>
-          <t>Proven for release-upgrade-to-23.04, -23.10 and -24.04 (22.10 VM, 2026-10-10): apt-get update; full-upgrade; then for 23.04 and 23.10 the next release's upgrader from old-releases, checked with gpgv, run as ./lunar or ./mantic --mode=server --frontend=DistUpgradeViewNonInteractive, and for 24.04 do-release-upgrade -f DistUpgradeViewNonInteractive. Healed in 34, 20 and 27 min. -26.04's do-release-upgrade -f DistUpgradeViewNonInteractive ran twice, made to fail (Runs E and F); the engine restored 24.04 both times. Visit 4 (2026-10-14): step 1's apt-get full-upgrade installed 18 updates and healed; step 2's do-release-upgrade stopped at once on unattended-upgrades' lock, and the engine restored 24.04. Run H, visit 4's second try (2026-10-14): step 1's apt-get full-upgrade waited out a dpkg lock held on purpose, twice, then installed 6 updates and healed; step 2's do-release-upgrade, now printing the upgrader's log on a failure, upgraded 24.04 to 26.04 in 24 min and healed. That print has not run on a VM: the upgrader did not fail. release-upgrade-to-23.04 also on an EFI 22.10 desktop (2026-10-16): healed in 48 min; made to fail mid-install, it printed the upgrader's log and was restored.</t>
+          <t>Proven for release-upgrade-to-23.04, -23.10 and -24.04 (22.10 VM, 2026-10-10): apt-get update; full-upgrade; then for 23.04 and 23.10 the next release's upgrader from old-releases, checked with gpgv, run as ./lunar or ./mantic --mode=server --frontend=DistUpgradeViewNonInteractive, and for 24.04 do-release-upgrade -f DistUpgradeViewNonInteractive. Healed in 34, 20 and 27 min. -26.04's do-release-upgrade -f DistUpgradeViewNonInteractive ran twice, made to fail (Runs E and F); the engine restored 24.04 both times. Visit 4 (2026-10-14): step 1's apt-get full-upgrade installed 18 updates and healed; step 2's do-release-upgrade stopped at once on unattended-upgrades' lock, and the engine restored 24.04. Run H, visit 4's second try (2026-10-14): step 1's apt-get full-upgrade waited out a dpkg lock held on purpose, twice, then installed 6 updates and healed; step 2's do-release-upgrade, now printing the upgrader's log on a failure, upgraded 24.04 to 26.04 in 24 min and healed. That print has not run on a VM: the upgrader did not fail. release-upgrade-to-23.04 also on an EFI 22.10 desktop (2026-10-16): healed in 48 min; made to fail mid-install, it printed the upgrader's log and was restored. On lab computer MITB-IT-406-03 (2026-10-21): release-upgrade-to-23.04 healed in about 70 min, with the driver built by dkms and loaded on its RTX 3060.</t>
         </is>
       </c>
       <c r="L18" s="12" t="n"/>
       <c r="M18" s="12" t="inlineStr">
         <is>
-          <t>Ubuntu 22.10 (kinetic) → 23.04 (lunar) → 23.10 (mantic) → 24.04 (noble): visits 1 to 3; 24.04 → 26.04 (resolute) made to fail twice: Runs E and F; visit 4 restored after a held lock (2026-10-14); visit 4 healed at its second try (Run H, 2026-10-14) 22.10 → 23.04 on an EFI 22.10 desktop with stand-in Windows parts (KineticDesktop, 2026-10-16): healed, then failed on purpose and restored. With 03's NVIDIA 535 packages too (Run 3, 2026-10-16): healed; apt built the driver with dkms.</t>
+          <t>Ubuntu 22.10 (kinetic) → 23.04 (lunar) → 23.10 (mantic) → 24.04 (noble): visits 1 to 3; 24.04 → 26.04 (resolute) made to fail twice: Runs E and F; visit 4 restored after a held lock (2026-10-14); visit 4 healed at its second try (Run H, 2026-10-14) 22.10 → 23.04 on an EFI 22.10 desktop with stand-in Windows parts (KineticDesktop, 2026-10-16): healed, then failed on purpose and restored. With 03's NVIDIA 535 packages too (Run 3, 2026-10-16): healed; apt built the driver with dkms. Lab computer MITB-IT-406-03, a real EFI dual-boot desktop with NVIDIA 535 (2026-10-21): 22.10 → 23.04 healed; nothing of Windows' changed.</t>
         </is>
       </c>
       <c r="N18" s="12" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="O18" s="12" t="inlineStr">
         <is>
-          <t>2026-10-16 · 22.10 → 23.04 on an EFI desktop · Run 1 healed in 48 min; Run 2 failed on purpose and was restored; Run 3, with 03's NVIDIA packages, healed in 74 min with the driver built by dkms; nothing of Windows' changed</t>
+          <t>2026-10-21 · lab computer MITB-IT-406-03 (a real machine) · visit 1, 22.10 → 23.04, healed in about 70 min; NVIDIA module built by dkms and loaded on the RTX 3060; nothing of Windows' changed. Last VM run: 2026-10-16, Run 3 on KineticDesktop.</t>
         </is>
       </c>
       <c r="P18" s="12" t="inlineStr">
         <is>
-          <t>Visit 1 on lab computer 03 (2026-10-21): check headers and Secure Boot first; after, nvidia-smi and dkms status. Unseen on any VM: the module loading on a real NVIDIA card; a lock that only the upgrader's log names.</t>
+          <t>Visit 2 (23.04 → 23.10) on KineticDesktop with the dkms NVIDIA driver first, then a kit with visit 2's checks. Unseen anywhere: a lock that only the upgrader's log names.</t>
         </is>
       </c>
     </row>
@@ -3661,7 +3661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -6543,31 +6543,208 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="10" t="n"/>
-      <c r="B79" s="10" t="n"/>
-      <c r="C79" s="10" t="n"/>
-      <c r="D79" s="10" t="n"/>
-      <c r="E79" s="10" t="n"/>
-      <c r="F79" s="10" t="n"/>
-      <c r="G79" s="10" t="n"/>
-    </row>
-    <row r="80" ht="240" customHeight="1">
-      <c r="A80" s="22" t="inlineStr">
-        <is>
-          <t>Times are IST (UTC+05:30). The logs themselves record UTC. Rows from 2026-09-07 23:35 to 2026-09-10 are records in evidence/ubuntu-26.04-2026-09-10.jsonl, copied off the VM on 2026-10-03; rows from 2026-10-04 are in evidence/ubuntu-26.04-2026-10-04.jsonl, rows from 2026-10-06 in evidence/ubuntu-26.04-2026-10-06.jsonl, and rows from 2026-10-07 in evidence/ubuntu-22.10-2026-10-07.jsonl and, from 12:13, evidence/ubuntu-22.10-2026-10-07-2.jsonl (the 22.10 VM, KineticServer). Rows from 2026-10-08 19:56 are the procedure runs, in evidence/ubuntu-22.10-2026-10-09.jsonl, copied from the service's own log, /var/log/sf3000/runs.jsonl. Rows from 2026-10-10 15:15 and 15:16 are lines 10 to 12 of evidence/ubuntu-22.10-2026-10-10.jsonl, whose first nine lines are the 2026-10-09 file again. Rows from 2026-10-10 16:33 are visit 1 of the upgrade, in evidence/ubuntu-22.10-2026-10-10-2.jsonl. The row from 18:40 is visit 2, line 3 of evidence/ubuntu-22.10-2026-10-10-3.jsonl, whose first two lines are visit 1's file again. The row from 20:00 is visit 3, line 4 of evidence/ubuntu-22.10-2026-10-10-4.jsonl, whose first three lines are visit 2's file again. The rows from 23:26 and 23:42 are Runs E and F, lines 5 and 6 of evidence/ubuntu-22.10-2026-10-10-5.jsonl, whose first four lines are visit 3's file again. The row from 2026-10-11 01:13 is Run G, line 7 of evidence/ubuntu-22.10-2026-10-11.jsonl, whose first six lines are the 2026-10-10 -5 file again. The rows from 2026-10-14 17:09 and 17:13 are visit 4, lines 8 and 9 of evidence/ubuntu-22.10-2026-10-14.jsonl, whose first seven lines are the 2026-10-11 file again. The rows from 2026-10-14 19:09 and 19:12 are Run H, lines 10 and 11 of evidence/ubuntu-22.10-2026-10-14-2.jsonl, whose first nine lines are the 2026-10-14 file again. Rows whose Evidence says 'Terminal output' have no record: the engine refuses before it logs anything, or the row is a sweep, which never logs. The six rows before 2026-09-07 23:35 come from commit messages: the VM's log was reset on the evening of 2026-09-07, before anyone copied it. Add one row per run from now on, pointing at its evidence file and line. The rows from 2026-10-16 17:10 to 17:17 are Run 1 of tests/efi-proof on KineticDesktop, an EFI 22.10 desktop VM, lines 1 to 3 of evidence/ubuntu-22.10-2026-10-16.jsonl. The rows from 18:03 to 18:10 are Run 2, lines 1 to 3 of evidence/ubuntu-22.10-2026-10-16-2.jsonl: a file of its own, because the VM went back to its efi-ready snapshot between the runs. The rows from 2026-10-16 19:29 to 19:46 are tests/grub-windows-proof on KineticDesktop, one record each in evidence/ubuntu-22.10-2026-10-16-3.jsonl to -8.jsonl: each run began from a snapshot restore, which deletes the clone's run log. The rows from 2026-10-16 20:02 to 20:08 are Run 3 of tests/efi-proof, with 03's NVIDIA packages, lines 1 to 3 of evidence/ubuntu-22.10-2026-10-16-9.jsonl. The rows from 2026-10-16 22:07 to 22:15 are the lab kit's test and --cancel after a real cut-off, lines 1 to 3 of evidence/ubuntu-22.10-2026-10-16-10.jsonl.</t>
-        </is>
-      </c>
-      <c r="B80" s="23" t="n"/>
-      <c r="C80" s="23" t="n"/>
-      <c r="D80" s="23" t="n"/>
-      <c r="E80" s="23" t="n"/>
-      <c r="F80" s="23" t="n"/>
-      <c r="G80" s="24" t="n"/>
+    <row r="79" ht="56" customHeight="1">
+      <c r="A79" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-14 14:07</t>
+        </is>
+      </c>
+      <c r="B79" s="10" t="inlineStr">
+        <is>
+          <t>22.10</t>
+        </is>
+      </c>
+      <c r="C79" s="10" t="inlineStr">
+        <is>
+          <t>01df9d9</t>
+        </is>
+      </c>
+      <c r="D79" s="10" t="inlineStr">
+        <is>
+          <t>engine/install</t>
+        </is>
+      </c>
+      <c r="E79" s="10" t="inlineStr">
+        <is>
+          <t>installed</t>
+        </is>
+      </c>
+      <c r="F79" s="10" t="inlineStr">
+        <is>
+          <t>Lab computer MITB-IT-406-03 (EFI, Windows on NVMe, RTX 3060 with NVIDIA 535). A --run started by accident, before the lab kit's runs that day: python3-jsonschema installed after a y. 03's clock is 5 h 28 min fast; times here are corrected, the records are not.</t>
+        </is>
+      </c>
+      <c r="G79" s="10" t="inlineStr">
+        <is>
+          <t>evidence/lab-MITB-IT-406-03-ubuntu-22.10-2026-10-21.jsonl, line 1; the kit's out folder (logs/lab-2026-10-21/03-5c60ba31b8c6), copied off the stick</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-14 14:10</t>
+        </is>
+      </c>
+      <c r="B80" s="10" t="inlineStr">
+        <is>
+          <t>22.10</t>
+        </is>
+      </c>
+      <c r="C80" s="10" t="inlineStr">
+        <is>
+          <t>01df9d9</t>
+        </is>
+      </c>
+      <c r="D80" s="10" t="inlineStr">
+        <is>
+          <t>release-upgrade-to-23.04/install</t>
+        </is>
+      </c>
+      <c r="E80" s="10" t="inlineStr">
+        <is>
+          <t>installed</t>
+        </is>
+      </c>
+      <c r="F80" s="10" t="inlineStr">
+        <is>
+          <t>The same accidental run: Timeshift installed. Its snapshot, 2026-10-14_19-40-01, a full copy, took 22 min.</t>
+        </is>
+      </c>
+      <c r="G80" s="10" t="inlineStr">
+        <is>
+          <t>evidence/lab-MITB-IT-406-03-ubuntu-22.10-2026-10-21.jsonl, line 2; snapshot.log</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="84" customHeight="1">
+      <c r="A81" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-14 14:34</t>
+        </is>
+      </c>
+      <c r="B81" s="10" t="inlineStr">
+        <is>
+          <t>22.10</t>
+        </is>
+      </c>
+      <c r="C81" s="10" t="inlineStr">
+        <is>
+          <t>01df9d9</t>
+        </is>
+      </c>
+      <c r="D81" s="10" t="inlineStr">
+        <is>
+          <t>release-upgrade-to-23.04/to-23.04</t>
+        </is>
+      </c>
+      <c r="E81" s="10" t="inlineStr">
+        <is>
+          <t>interrupted</t>
+        </is>
+      </c>
+      <c r="F81" s="10" t="inlineStr">
+        <is>
+          <t>The same run, cut off: the machine went down during 22.10's full-upgrade, before the upgrader started. The kit's 5-save then read cut_off. On 2026-10-21, before visit 1, --cancel wrote this record: 'not attempted: cancelled by hand; Timeshift snapshot 2026-10-14_19-40-01 kept'. Nothing restored. The first --cancel on a lab machine. (The timestamp is the step's start.)</t>
+        </is>
+      </c>
+      <c r="G81" s="10" t="inlineStr">
+        <is>
+          <t>evidence/lab-MITB-IT-406-03-ubuntu-22.10-2026-10-21.jsonl, line 3; 05-save and 07-before-visit.txt</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="56" customHeight="1">
+      <c r="A82" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-14 15:45</t>
+        </is>
+      </c>
+      <c r="B82" s="10" t="inlineStr">
+        <is>
+          <t>22.10</t>
+        </is>
+      </c>
+      <c r="C82" s="10" t="inlineStr">
+        <is>
+          <t>01df9d9</t>
+        </is>
+      </c>
+      <c r="D82" s="10" t="inlineStr">
+        <is>
+          <t>release-upgrade-to-23.04</t>
+        </is>
+      </c>
+      <c r="E82" s="10" t="inlineStr">
+        <is>
+          <t>declined</t>
+        </is>
+      </c>
+      <c r="F82" s="10" t="inlineStr">
+        <is>
+          <t>A --run after the cut-off, answered n at the restore it offered. Logged in the clone's own logs/.</t>
+        </is>
+      </c>
+      <c r="G82" s="10" t="inlineStr">
+        <is>
+          <t>evidence/lab-MITB-IT-406-03-ubuntu-22.10-2026-10-14.jsonl, line 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="84" customHeight="1">
+      <c r="A83" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-21 13:52</t>
+        </is>
+      </c>
+      <c r="B83" s="10" t="inlineStr">
+        <is>
+          <t>22.10 → 23.04</t>
+        </is>
+      </c>
+      <c r="C83" s="10" t="inlineStr">
+        <is>
+          <t>d4a34a0</t>
+        </is>
+      </c>
+      <c r="D83" s="10" t="inlineStr">
+        <is>
+          <t>release-upgrade-to-23.04/to-23.04</t>
+        </is>
+      </c>
+      <c r="E83" s="10" t="inlineStr">
+        <is>
+          <t>healed</t>
+        </is>
+      </c>
+      <c r="F83" s="10" t="inlineStr">
+        <is>
+          <t>Visit 1 on lab computer MITB-IT-406-03, the first upgrade on a lab machine. Kit v3: 6-before-visit READY, 7-visit-1 answered y at 13:50. Snapshot 2026-10-21_19-19-58 in 51 s (only the changes since 10-14). Step 1's full-upgrade had 2 packages; the upgrader downloaded the rest. apt installed nvidia-dkms-535 535.146.02 and built the module for 6.2.0-39 and 5.19.0-46. Check after: 2304; about 70 min from the y until the machine was back up. After: the module loaded on the RTX 3060, nvidia-smi works, both sweeps HEALTHY, the desktop came up. check-windows: only EFI/ubuntu/grubx64.efi and two memory test menu entries changed; Windows still in the menu.</t>
+        </is>
+      </c>
+      <c r="G83" s="10" t="inlineStr">
+        <is>
+          <t>evidence/lab-MITB-IT-406-03-ubuntu-22.10-2026-10-21.jsonl, line 4; the upgrader's output, 08-visit-1.txt, 09-after-visit.txt and the Windows checks (logs/lab-2026-10-21/03-5c60ba31b8c6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84"/>
+    <row r="85" ht="270" customHeight="1">
+      <c r="A85" s="22" t="inlineStr">
+        <is>
+          <t>Times are IST (UTC+05:30). The logs themselves record UTC. Rows from 2026-09-07 23:35 to 2026-09-10 are records in evidence/ubuntu-26.04-2026-09-10.jsonl, copied off the VM on 2026-10-03; rows from 2026-10-04 are in evidence/ubuntu-26.04-2026-10-04.jsonl, rows from 2026-10-06 in evidence/ubuntu-26.04-2026-10-06.jsonl, and rows from 2026-10-07 in evidence/ubuntu-22.10-2026-10-07.jsonl and, from 12:13, evidence/ubuntu-22.10-2026-10-07-2.jsonl (the 22.10 VM, KineticServer). Rows from 2026-10-08 19:56 are the procedure runs, in evidence/ubuntu-22.10-2026-10-09.jsonl, copied from the service's own log, /var/log/sf3000/runs.jsonl. Rows from 2026-10-10 15:15 and 15:16 are lines 10 to 12 of evidence/ubuntu-22.10-2026-10-10.jsonl, whose first nine lines are the 2026-10-09 file again. Rows from 2026-10-10 16:33 are visit 1 of the upgrade, in evidence/ubuntu-22.10-2026-10-10-2.jsonl. The row from 18:40 is visit 2, line 3 of evidence/ubuntu-22.10-2026-10-10-3.jsonl, whose first two lines are visit 1's file again. The row from 20:00 is visit 3, line 4 of evidence/ubuntu-22.10-2026-10-10-4.jsonl, whose first three lines are visit 2's file again. The rows from 23:26 and 23:42 are Runs E and F, lines 5 and 6 of evidence/ubuntu-22.10-2026-10-10-5.jsonl, whose first four lines are visit 3's file again. The row from 2026-10-11 01:13 is Run G, line 7 of evidence/ubuntu-22.10-2026-10-11.jsonl, whose first six lines are the 2026-10-10 -5 file again. The rows from 2026-10-14 17:09 and 17:13 are visit 4, lines 8 and 9 of evidence/ubuntu-22.10-2026-10-14.jsonl, whose first seven lines are the 2026-10-11 file again. The rows from 2026-10-14 19:09 and 19:12 are Run H, lines 10 and 11 of evidence/ubuntu-22.10-2026-10-14-2.jsonl, whose first nine lines are the 2026-10-14 file again. Rows whose Evidence says 'Terminal output' have no record: the engine refuses before it logs anything, or the row is a sweep, which never logs. The six rows before 2026-09-07 23:35 come from commit messages: the VM's log was reset on the evening of 2026-09-07, before anyone copied it. Add one row per run from now on, pointing at its evidence file and line. The rows from 2026-10-16 17:10 to 17:17 are Run 1 of tests/efi-proof on KineticDesktop, an EFI 22.10 desktop VM, lines 1 to 3 of evidence/ubuntu-22.10-2026-10-16.jsonl. The rows from 18:03 to 18:10 are Run 2, lines 1 to 3 of evidence/ubuntu-22.10-2026-10-16-2.jsonl: a file of its own, because the VM went back to its efi-ready snapshot between the runs. The rows from 2026-10-16 19:29 to 19:46 are tests/grub-windows-proof on KineticDesktop, one record each in evidence/ubuntu-22.10-2026-10-16-3.jsonl to -8.jsonl: each run began from a snapshot restore, which deletes the clone's run log. The rows from 2026-10-16 20:02 to 20:08 are Run 3 of tests/efi-proof, with 03's NVIDIA packages, lines 1 to 3 of evidence/ubuntu-22.10-2026-10-16-9.jsonl. The rows from 2026-10-16 22:07 to 22:15 are the lab kit's test and --cancel after a real cut-off, lines 1 to 3 of evidence/ubuntu-22.10-2026-10-16-10.jsonl. The rows from 2026-10-14 14:07 to 2026-10-21 13:52 are lab computer MITB-IT-406-03, a real lab machine: lines 1 to 4 of evidence/lab-MITB-IT-406-03-ubuntu-22.10-2026-10-21.jsonl (its /var/log/sf3000/runs.jsonl) and line 1 of evidence/lab-MITB-IT-406-03-ubuntu-22.10-2026-10-14.jsonl (its clone's logs/runs.jsonl). Its clock is 5 h 28 min fast; their times are corrected to the real time.</t>
+        </is>
+      </c>
+      <c r="B85" s="23" t="n"/>
+      <c r="C85" s="23" t="n"/>
+      <c r="D85" s="23" t="n"/>
+      <c r="E85" s="23" t="n"/>
+      <c r="F85" s="23" t="n"/>
+      <c r="G85" s="24" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A80:G80"/>
+    <mergeCell ref="A85:G85"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/sf3000-tracker.xlsx
+++ b/docs/sf3000-tracker.xlsx
@@ -2290,7 +2290,7 @@
       </c>
       <c r="K19" s="12" t="inlineStr">
         <is>
-          <t>Proven on the EFI 22.10 desktop VM (2026-10-16): healed 3 times (twice at aff2c9c, once at 279952d, about 5 s each)</t>
+          <t>Proven on the EFI 22.10 desktop VM (2026-10-16): healed 3 times (twice at aff2c9c, once at 279952d, about 5 s each); healed again on 2026-10-25 at a298fc9 (4.9 s), with its summary in the box</t>
         </is>
       </c>
       <c r="L19" s="12" t="inlineStr">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="N19" s="12" t="inlineStr">
         <is>
-          <t>Ubuntu's 'auto' hides Windows for good after one rebuild without it. A stale Windows entry reads PROBLEM; the verify then undoes the fix. grub.cfg at 0600 (GRUB password): ERROR for a user. A cold start straight after a VBox restore skipped the menu on this host: demo with a warm reboot.</t>
+          <t>Ubuntu's 'auto' hides Windows for good after one rebuild without it. A stale Windows entry reads PROBLEM; the verify then undoes the fix. grub.cfg at 0600 (GRUB password): ERROR for a user. A cold start straight after a VBox restore skipped the menu on this host: demo with a warm reboot. On 2026-10-25 a warm reboot showed the menu for only about 3 s (the countdown ran fast): press an arrow key to hold it.</t>
         </is>
       </c>
       <c r="O19" s="12" t="inlineStr">
         <is>
-          <t>2026-10-16 · 22.10 · healed in 5.1 s; undone when it could not work and when it stopped early (Runs 4-6, 279952d)</t>
+          <t>2026-10-25 · 22.10 · the box with a summary: v then n declined; y healed in 4.9 s (a298fc9)</t>
         </is>
       </c>
       <c r="P19" s="12" t="inlineStr">
@@ -3661,7 +3661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -6728,23 +6728,97 @@
         </is>
       </c>
     </row>
-    <row r="84"/>
-    <row r="85" ht="270" customHeight="1">
-      <c r="A85" s="22" t="inlineStr">
-        <is>
-          <t>Times are IST (UTC+05:30). The logs themselves record UTC. Rows from 2026-09-07 23:35 to 2026-09-10 are records in evidence/ubuntu-26.04-2026-09-10.jsonl, copied off the VM on 2026-10-03; rows from 2026-10-04 are in evidence/ubuntu-26.04-2026-10-04.jsonl, rows from 2026-10-06 in evidence/ubuntu-26.04-2026-10-06.jsonl, and rows from 2026-10-07 in evidence/ubuntu-22.10-2026-10-07.jsonl and, from 12:13, evidence/ubuntu-22.10-2026-10-07-2.jsonl (the 22.10 VM, KineticServer). Rows from 2026-10-08 19:56 are the procedure runs, in evidence/ubuntu-22.10-2026-10-09.jsonl, copied from the service's own log, /var/log/sf3000/runs.jsonl. Rows from 2026-10-10 15:15 and 15:16 are lines 10 to 12 of evidence/ubuntu-22.10-2026-10-10.jsonl, whose first nine lines are the 2026-10-09 file again. Rows from 2026-10-10 16:33 are visit 1 of the upgrade, in evidence/ubuntu-22.10-2026-10-10-2.jsonl. The row from 18:40 is visit 2, line 3 of evidence/ubuntu-22.10-2026-10-10-3.jsonl, whose first two lines are visit 1's file again. The row from 20:00 is visit 3, line 4 of evidence/ubuntu-22.10-2026-10-10-4.jsonl, whose first three lines are visit 2's file again. The rows from 23:26 and 23:42 are Runs E and F, lines 5 and 6 of evidence/ubuntu-22.10-2026-10-10-5.jsonl, whose first four lines are visit 3's file again. The row from 2026-10-11 01:13 is Run G, line 7 of evidence/ubuntu-22.10-2026-10-11.jsonl, whose first six lines are the 2026-10-10 -5 file again. The rows from 2026-10-14 17:09 and 17:13 are visit 4, lines 8 and 9 of evidence/ubuntu-22.10-2026-10-14.jsonl, whose first seven lines are the 2026-10-11 file again. The rows from 2026-10-14 19:09 and 19:12 are Run H, lines 10 and 11 of evidence/ubuntu-22.10-2026-10-14-2.jsonl, whose first nine lines are the 2026-10-14 file again. Rows whose Evidence says 'Terminal output' have no record: the engine refuses before it logs anything, or the row is a sweep, which never logs. The six rows before 2026-09-07 23:35 come from commit messages: the VM's log was reset on the evening of 2026-09-07, before anyone copied it. Add one row per run from now on, pointing at its evidence file and line. The rows from 2026-10-16 17:10 to 17:17 are Run 1 of tests/efi-proof on KineticDesktop, an EFI 22.10 desktop VM, lines 1 to 3 of evidence/ubuntu-22.10-2026-10-16.jsonl. The rows from 18:03 to 18:10 are Run 2, lines 1 to 3 of evidence/ubuntu-22.10-2026-10-16-2.jsonl: a file of its own, because the VM went back to its efi-ready snapshot between the runs. The rows from 2026-10-16 19:29 to 19:46 are tests/grub-windows-proof on KineticDesktop, one record each in evidence/ubuntu-22.10-2026-10-16-3.jsonl to -8.jsonl: each run began from a snapshot restore, which deletes the clone's run log. The rows from 2026-10-16 20:02 to 20:08 are Run 3 of tests/efi-proof, with 03's NVIDIA packages, lines 1 to 3 of evidence/ubuntu-22.10-2026-10-16-9.jsonl. The rows from 2026-10-16 22:07 to 22:15 are the lab kit's test and --cancel after a real cut-off, lines 1 to 3 of evidence/ubuntu-22.10-2026-10-16-10.jsonl. The rows from 2026-10-14 14:07 to 2026-10-21 13:52 are lab computer MITB-IT-406-03, a real lab machine: lines 1 to 4 of evidence/lab-MITB-IT-406-03-ubuntu-22.10-2026-10-21.jsonl (its /var/log/sf3000/runs.jsonl) and line 1 of evidence/lab-MITB-IT-406-03-ubuntu-22.10-2026-10-14.jsonl (its clone's logs/runs.jsonl). Its clock is 5 h 28 min fast; their times are corrected to the real time.</t>
-        </is>
-      </c>
-      <c r="B85" s="23" t="n"/>
-      <c r="C85" s="23" t="n"/>
-      <c r="D85" s="23" t="n"/>
-      <c r="E85" s="23" t="n"/>
-      <c r="F85" s="23" t="n"/>
-      <c r="G85" s="24" t="n"/>
+    <row r="84" ht="70" customHeight="1">
+      <c r="A84" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-25 14:59</t>
+        </is>
+      </c>
+      <c r="B84" s="10" t="inlineStr">
+        <is>
+          <t>22.10</t>
+        </is>
+      </c>
+      <c r="C84" s="10" t="inlineStr">
+        <is>
+          <t>a298fc9</t>
+        </is>
+      </c>
+      <c r="D84" s="10" t="inlineStr">
+        <is>
+          <t>windows-missing-from-grub</t>
+        </is>
+      </c>
+      <c r="E84" s="10" t="inlineStr">
+        <is>
+          <t>declined</t>
+        </is>
+      </c>
+      <c r="F84" s="10" t="inlineStr">
+        <is>
+          <t>Run 7 (tests/grub-windows-proof), on KineticDesktop from grub-trap: the box with a summary. The sweep and the box showed the summary, not the command; the box was 14 lines. v printed the command and the source, then asked again; answered n. /etc/default/grub unchanged (e7e2c4ab...), no backup made.</t>
+        </is>
+      </c>
+      <c r="G84" s="10" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-22.10-2026-10-25.jsonl, line 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="70" customHeight="1">
+      <c r="A85" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-25 14:59</t>
+        </is>
+      </c>
+      <c r="B85" s="10" t="inlineStr">
+        <is>
+          <t>22.10</t>
+        </is>
+      </c>
+      <c r="C85" s="10" t="inlineStr">
+        <is>
+          <t>a298fc9</t>
+        </is>
+      </c>
+      <c r="D85" s="10" t="inlineStr">
+        <is>
+          <t>windows-missing-from-grub</t>
+        </is>
+      </c>
+      <c r="E85" s="10" t="inlineStr">
+        <is>
+          <t>healed</t>
+        </is>
+      </c>
+      <c r="F85" s="10" t="inlineStr">
+        <is>
+          <t>Run 8: answered y at the box. The engine printed 'running the fix', not the command. 1 → 0 in 4.9 s. check-windows after the fix matched the record from before the trap. A warm reboot showed the menu with Windows, but its 10 s countdown passed in about 3 s (the host's virtual clock).</t>
+        </is>
+      </c>
+      <c r="G85" s="10" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-22.10-2026-10-25.jsonl, line 2; console, screenshots and Windows checks in logs/confirm-summary-run-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="86"/>
+    <row r="87" ht="270" customHeight="1">
+      <c r="A87" s="22" t="inlineStr">
+        <is>
+          <t>Times are IST (UTC+05:30). The logs themselves record UTC. Rows from 2026-09-07 23:35 to 2026-09-10 are records in evidence/ubuntu-26.04-2026-09-10.jsonl, copied off the VM on 2026-10-03; rows from 2026-10-04 are in evidence/ubuntu-26.04-2026-10-04.jsonl, rows from 2026-10-06 in evidence/ubuntu-26.04-2026-10-06.jsonl, and rows from 2026-10-07 in evidence/ubuntu-22.10-2026-10-07.jsonl and, from 12:13, evidence/ubuntu-22.10-2026-10-07-2.jsonl (the 22.10 VM, KineticServer). Rows from 2026-10-08 19:56 are the procedure runs, in evidence/ubuntu-22.10-2026-10-09.jsonl, copied from the service's own log, /var/log/sf3000/runs.jsonl. Rows from 2026-10-10 15:15 and 15:16 are lines 10 to 12 of evidence/ubuntu-22.10-2026-10-10.jsonl, whose first nine lines are the 2026-10-09 file again. Rows from 2026-10-10 16:33 are visit 1 of the upgrade, in evidence/ubuntu-22.10-2026-10-10-2.jsonl. The row from 18:40 is visit 2, line 3 of evidence/ubuntu-22.10-2026-10-10-3.jsonl, whose first two lines are visit 1's file again. The row from 20:00 is visit 3, line 4 of evidence/ubuntu-22.10-2026-10-10-4.jsonl, whose first three lines are visit 2's file again. The rows from 23:26 and 23:42 are Runs E and F, lines 5 and 6 of evidence/ubuntu-22.10-2026-10-10-5.jsonl, whose first four lines are visit 3's file again. The row from 2026-10-11 01:13 is Run G, line 7 of evidence/ubuntu-22.10-2026-10-11.jsonl, whose first six lines are the 2026-10-10 -5 file again. The rows from 2026-10-14 17:09 and 17:13 are visit 4, lines 8 and 9 of evidence/ubuntu-22.10-2026-10-14.jsonl, whose first seven lines are the 2026-10-11 file again. The rows from 2026-10-14 19:09 and 19:12 are Run H, lines 10 and 11 of evidence/ubuntu-22.10-2026-10-14-2.jsonl, whose first nine lines are the 2026-10-14 file again. Rows whose Evidence says 'Terminal output' have no record: the engine refuses before it logs anything, or the row is a sweep, which never logs. The six rows before 2026-09-07 23:35 come from commit messages: the VM's log was reset on the evening of 2026-09-07, before anyone copied it. Add one row per run from now on, pointing at its evidence file and line. The rows from 2026-10-16 17:10 to 17:17 are Run 1 of tests/efi-proof on KineticDesktop, an EFI 22.10 desktop VM, lines 1 to 3 of evidence/ubuntu-22.10-2026-10-16.jsonl. The rows from 18:03 to 18:10 are Run 2, lines 1 to 3 of evidence/ubuntu-22.10-2026-10-16-2.jsonl: a file of its own, because the VM went back to its efi-ready snapshot between the runs. The rows from 2026-10-16 19:29 to 19:46 are tests/grub-windows-proof on KineticDesktop, one record each in evidence/ubuntu-22.10-2026-10-16-3.jsonl to -8.jsonl: each run began from a snapshot restore, which deletes the clone's run log. The rows from 2026-10-16 20:02 to 20:08 are Run 3 of tests/efi-proof, with 03's NVIDIA packages, lines 1 to 3 of evidence/ubuntu-22.10-2026-10-16-9.jsonl. The rows from 2026-10-16 22:07 to 22:15 are the lab kit's test and --cancel after a real cut-off, lines 1 to 3 of evidence/ubuntu-22.10-2026-10-16-10.jsonl. The rows from 2026-10-14 14:07 to 2026-10-21 13:52 are lab computer MITB-IT-406-03, a real lab machine: lines 1 to 4 of evidence/lab-MITB-IT-406-03-ubuntu-22.10-2026-10-21.jsonl (its /var/log/sf3000/runs.jsonl) and line 1 of evidence/lab-MITB-IT-406-03-ubuntu-22.10-2026-10-14.jsonl (its clone's logs/runs.jsonl). Its clock is 5 h 28 min fast; their times are corrected to the real time. The rows from 2026-10-25 14:59 are Runs 7 and 8 of tests/grub-windows-proof, the box with a summary (branch confirm-summary, a298fc9), lines 1 and 2 of evidence/ubuntu-22.10-2026-10-25.jsonl.</t>
+        </is>
+      </c>
+      <c r="B87" s="23" t="n"/>
+      <c r="C87" s="23" t="n"/>
+      <c r="D87" s="23" t="n"/>
+      <c r="E87" s="23" t="n"/>
+      <c r="F87" s="23" t="n"/>
+      <c r="G87" s="24" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A85:G85"/>
+    <mergeCell ref="A87:G87"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/sf3000-tracker.xlsx
+++ b/docs/sf3000-tracker.xlsx
@@ -2305,7 +2305,7 @@
       </c>
       <c r="N19" s="12" t="inlineStr">
         <is>
-          <t>Ubuntu's 'auto' hides Windows for good after one rebuild without it. A stale Windows entry reads PROBLEM; the verify then undoes the fix. grub.cfg at 0600 (GRUB password): ERROR for a user. A cold start straight after a VBox restore skipped the menu on this host: demo with a warm reboot. On 2026-10-25 a warm reboot showed the menu for only about 3 s (the countdown ran fast): press an arrow key to hold it.</t>
+          <t>Ubuntu's 'auto' hides Windows for good after one rebuild without it. A stale Windows entry reads PROBLEM; the verify then undoes the fix. grub.cfg at 0600 (GRUB password): ERROR for a user. A cold start straight after a VBox restore skipped the menu on this host: demo with a warm reboot. On 2026-10-25 a warm reboot showed the menu for only about 0.6 s (the host's clock): tap Up from the VirtualBox logo on to hold it.</t>
         </is>
       </c>
       <c r="O19" s="12" t="inlineStr">
@@ -2315,7 +2315,7 @@
       </c>
       <c r="P19" s="12" t="inlineStr">
         <is>
-          <t>A real dual-boot machine; another release. The demo on 2026-11-03 starts from VBox snapshot grub-trap.</t>
+          <t>A real dual-boot machine; another release. The live demo on 2026-11-03 starts from VBox snapshot demo-start.</t>
         </is>
       </c>
     </row>
@@ -3661,7 +3661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -6802,23 +6802,60 @@
         </is>
       </c>
     </row>
-    <row r="86"/>
-    <row r="87" ht="270" customHeight="1">
-      <c r="A87" s="22" t="inlineStr">
-        <is>
-          <t>Times are IST (UTC+05:30). The logs themselves record UTC. Rows from 2026-09-07 23:35 to 2026-09-10 are records in evidence/ubuntu-26.04-2026-09-10.jsonl, copied off the VM on 2026-10-03; rows from 2026-10-04 are in evidence/ubuntu-26.04-2026-10-04.jsonl, rows from 2026-10-06 in evidence/ubuntu-26.04-2026-10-06.jsonl, and rows from 2026-10-07 in evidence/ubuntu-22.10-2026-10-07.jsonl and, from 12:13, evidence/ubuntu-22.10-2026-10-07-2.jsonl (the 22.10 VM, KineticServer). Rows from 2026-10-08 19:56 are the procedure runs, in evidence/ubuntu-22.10-2026-10-09.jsonl, copied from the service's own log, /var/log/sf3000/runs.jsonl. Rows from 2026-10-10 15:15 and 15:16 are lines 10 to 12 of evidence/ubuntu-22.10-2026-10-10.jsonl, whose first nine lines are the 2026-10-09 file again. Rows from 2026-10-10 16:33 are visit 1 of the upgrade, in evidence/ubuntu-22.10-2026-10-10-2.jsonl. The row from 18:40 is visit 2, line 3 of evidence/ubuntu-22.10-2026-10-10-3.jsonl, whose first two lines are visit 1's file again. The row from 20:00 is visit 3, line 4 of evidence/ubuntu-22.10-2026-10-10-4.jsonl, whose first three lines are visit 2's file again. The rows from 23:26 and 23:42 are Runs E and F, lines 5 and 6 of evidence/ubuntu-22.10-2026-10-10-5.jsonl, whose first four lines are visit 3's file again. The row from 2026-10-11 01:13 is Run G, line 7 of evidence/ubuntu-22.10-2026-10-11.jsonl, whose first six lines are the 2026-10-10 -5 file again. The rows from 2026-10-14 17:09 and 17:13 are visit 4, lines 8 and 9 of evidence/ubuntu-22.10-2026-10-14.jsonl, whose first seven lines are the 2026-10-11 file again. The rows from 2026-10-14 19:09 and 19:12 are Run H, lines 10 and 11 of evidence/ubuntu-22.10-2026-10-14-2.jsonl, whose first nine lines are the 2026-10-14 file again. Rows whose Evidence says 'Terminal output' have no record: the engine refuses before it logs anything, or the row is a sweep, which never logs. The six rows before 2026-09-07 23:35 come from commit messages: the VM's log was reset on the evening of 2026-09-07, before anyone copied it. Add one row per run from now on, pointing at its evidence file and line. The rows from 2026-10-16 17:10 to 17:17 are Run 1 of tests/efi-proof on KineticDesktop, an EFI 22.10 desktop VM, lines 1 to 3 of evidence/ubuntu-22.10-2026-10-16.jsonl. The rows from 18:03 to 18:10 are Run 2, lines 1 to 3 of evidence/ubuntu-22.10-2026-10-16-2.jsonl: a file of its own, because the VM went back to its efi-ready snapshot between the runs. The rows from 2026-10-16 19:29 to 19:46 are tests/grub-windows-proof on KineticDesktop, one record each in evidence/ubuntu-22.10-2026-10-16-3.jsonl to -8.jsonl: each run began from a snapshot restore, which deletes the clone's run log. The rows from 2026-10-16 20:02 to 20:08 are Run 3 of tests/efi-proof, with 03's NVIDIA packages, lines 1 to 3 of evidence/ubuntu-22.10-2026-10-16-9.jsonl. The rows from 2026-10-16 22:07 to 22:15 are the lab kit's test and --cancel after a real cut-off, lines 1 to 3 of evidence/ubuntu-22.10-2026-10-16-10.jsonl. The rows from 2026-10-14 14:07 to 2026-10-21 13:52 are lab computer MITB-IT-406-03, a real lab machine: lines 1 to 4 of evidence/lab-MITB-IT-406-03-ubuntu-22.10-2026-10-21.jsonl (its /var/log/sf3000/runs.jsonl) and line 1 of evidence/lab-MITB-IT-406-03-ubuntu-22.10-2026-10-14.jsonl (its clone's logs/runs.jsonl). Its clock is 5 h 28 min fast; their times are corrected to the real time. The rows from 2026-10-25 14:59 are Runs 7 and 8 of tests/grub-windows-proof, the box with a summary (branch confirm-summary, a298fc9), lines 1 and 2 of evidence/ubuntu-22.10-2026-10-25.jsonl.</t>
-        </is>
-      </c>
-      <c r="B87" s="23" t="n"/>
-      <c r="C87" s="23" t="n"/>
-      <c r="D87" s="23" t="n"/>
-      <c r="E87" s="23" t="n"/>
-      <c r="F87" s="23" t="n"/>
-      <c r="G87" s="24" t="n"/>
+    <row r="86" ht="70" customHeight="1">
+      <c r="A86" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-25 15:24</t>
+        </is>
+      </c>
+      <c r="B86" s="10" t="inlineStr">
+        <is>
+          <t>22.10</t>
+        </is>
+      </c>
+      <c r="C86" s="10" t="inlineStr">
+        <is>
+          <t>c4d67cc</t>
+        </is>
+      </c>
+      <c r="D86" s="10" t="inlineStr">
+        <is>
+          <t>windows-missing-from-grub</t>
+        </is>
+      </c>
+      <c r="E86" s="10" t="inlineStr">
+        <is>
+          <t>healed</t>
+        </is>
+      </c>
+      <c r="F86" s="10" t="inlineStr">
+        <is>
+          <t>A timed rehearsal of the live demo from VBox snapshot demo-start (grub-trap with the clone at c4d67cc), scripted over SSH. Reboot with the fault 50 s (no menu); sweep 3 s; --fix to healed 14 s; reboot after 44 s; check-windows 47 s, no difference. GRUB's menu is up only about 0.6 s on this host; tapping Up from the VirtualBox logo on held it.</t>
+        </is>
+      </c>
+      <c r="G86" s="10" t="inlineStr">
+        <is>
+          <t>evidence/ubuntu-22.10-2026-10-25-2.jsonl, line 1; timeline and screenshots in logs/demo-rehearsal-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="87"/>
+    <row r="88" ht="270" customHeight="1">
+      <c r="A88" s="22" t="inlineStr">
+        <is>
+          <t>Times are IST (UTC+05:30). The logs themselves record UTC. Rows from 2026-09-07 23:35 to 2026-09-10 are records in evidence/ubuntu-26.04-2026-09-10.jsonl, copied off the VM on 2026-10-03; rows from 2026-10-04 are in evidence/ubuntu-26.04-2026-10-04.jsonl, rows from 2026-10-06 in evidence/ubuntu-26.04-2026-10-06.jsonl, and rows from 2026-10-07 in evidence/ubuntu-22.10-2026-10-07.jsonl and, from 12:13, evidence/ubuntu-22.10-2026-10-07-2.jsonl (the 22.10 VM, KineticServer). Rows from 2026-10-08 19:56 are the procedure runs, in evidence/ubuntu-22.10-2026-10-09.jsonl, copied from the service's own log, /var/log/sf3000/runs.jsonl. Rows from 2026-10-10 15:15 and 15:16 are lines 10 to 12 of evidence/ubuntu-22.10-2026-10-10.jsonl, whose first nine lines are the 2026-10-09 file again. Rows from 2026-10-10 16:33 are visit 1 of the upgrade, in evidence/ubuntu-22.10-2026-10-10-2.jsonl. The row from 18:40 is visit 2, line 3 of evidence/ubuntu-22.10-2026-10-10-3.jsonl, whose first two lines are visit 1's file again. The row from 20:00 is visit 3, line 4 of evidence/ubuntu-22.10-2026-10-10-4.jsonl, whose first three lines are visit 2's file again. The rows from 23:26 and 23:42 are Runs E and F, lines 5 and 6 of evidence/ubuntu-22.10-2026-10-10-5.jsonl, whose first four lines are visit 3's file again. The row from 2026-10-11 01:13 is Run G, line 7 of evidence/ubuntu-22.10-2026-10-11.jsonl, whose first six lines are the 2026-10-10 -5 file again. The rows from 2026-10-14 17:09 and 17:13 are visit 4, lines 8 and 9 of evidence/ubuntu-22.10-2026-10-14.jsonl, whose first seven lines are the 2026-10-11 file again. The rows from 2026-10-14 19:09 and 19:12 are Run H, lines 10 and 11 of evidence/ubuntu-22.10-2026-10-14-2.jsonl, whose first nine lines are the 2026-10-14 file again. Rows whose Evidence says 'Terminal output' have no record: the engine refuses before it logs anything, or the row is a sweep, which never logs. The six rows before 2026-09-07 23:35 come from commit messages: the VM's log was reset on the evening of 2026-09-07, before anyone copied it. Add one row per run from now on, pointing at its evidence file and line. The rows from 2026-10-16 17:10 to 17:17 are Run 1 of tests/efi-proof on KineticDesktop, an EFI 22.10 desktop VM, lines 1 to 3 of evidence/ubuntu-22.10-2026-10-16.jsonl. The rows from 18:03 to 18:10 are Run 2, lines 1 to 3 of evidence/ubuntu-22.10-2026-10-16-2.jsonl: a file of its own, because the VM went back to its efi-ready snapshot between the runs. The rows from 2026-10-16 19:29 to 19:46 are tests/grub-windows-proof on KineticDesktop, one record each in evidence/ubuntu-22.10-2026-10-16-3.jsonl to -8.jsonl: each run began from a snapshot restore, which deletes the clone's run log. The rows from 2026-10-16 20:02 to 20:08 are Run 3 of tests/efi-proof, with 03's NVIDIA packages, lines 1 to 3 of evidence/ubuntu-22.10-2026-10-16-9.jsonl. The rows from 2026-10-16 22:07 to 22:15 are the lab kit's test and --cancel after a real cut-off, lines 1 to 3 of evidence/ubuntu-22.10-2026-10-16-10.jsonl. The rows from 2026-10-14 14:07 to 2026-10-21 13:52 are lab computer MITB-IT-406-03, a real lab machine: lines 1 to 4 of evidence/lab-MITB-IT-406-03-ubuntu-22.10-2026-10-21.jsonl (its /var/log/sf3000/runs.jsonl) and line 1 of evidence/lab-MITB-IT-406-03-ubuntu-22.10-2026-10-14.jsonl (its clone's logs/runs.jsonl). Its clock is 5 h 28 min fast; their times are corrected to the real time. The rows from 2026-10-25 14:59 are Runs 7 and 8 of tests/grub-windows-proof, the box with a summary (branch confirm-summary, a298fc9), lines 1 and 2 of evidence/ubuntu-22.10-2026-10-25.jsonl. The row from 2026-10-25 15:24 is a timed demo rehearsal, line 1 of evidence/ubuntu-22.10-2026-10-25-2.jsonl.</t>
+        </is>
+      </c>
+      <c r="B88" s="23" t="n"/>
+      <c r="C88" s="23" t="n"/>
+      <c r="D88" s="23" t="n"/>
+      <c r="E88" s="23" t="n"/>
+      <c r="F88" s="23" t="n"/>
+      <c r="G88" s="24" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A87:G87"/>
+    <mergeCell ref="A88:G88"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
